--- a/reports/ADANIPORTS/Adani_Ports_and_Special_Economic_Zone_Ltd_ERIP_Model.xlsx
+++ b/reports/ADANIPORTS/Adani_Ports_and_Special_Economic_Zone_Ltd_ERIP_Model.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="346">
   <si>
     <t xml:space="preserve">Adani Ports and Special Economic Zone Ltd - Dashboard</t>
   </si>
@@ -104,12 +104,15 @@
     <t xml:space="preserve">EPS (INR)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Target basis: DCF with an exit EV/EBITDA of</t>
+    <t xml:space="preserve">    Target basis</t>
   </si>
   <si>
     <t xml:space="preserve">EBITDA margin</t>
   </si>
   <si>
+    <t xml:space="preserve">    Target horizon (months)</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Active scenario</t>
   </si>
   <si>
@@ -155,7 +158,7 @@
     <t xml:space="preserve">    Probability-weighted, perpetuity</t>
   </si>
   <si>
-    <t xml:space="preserve">    DCF at the target exit multiple</t>
+    <t xml:space="preserve">    DCF at the cross-check exit multiple</t>
   </si>
   <si>
     <t xml:space="preserve">    DCF at the alternative exit multiple</t>
@@ -332,6 +335,12 @@
     <t xml:space="preserve">- Scenarios 'base/bull/bear' were each built by financial-model and valued by model.py; the Scenarios sheet checks this workbook against those values.</t>
   </si>
   <si>
+    <t xml:space="preserve">Explained check failures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- EXPLAINED  Reserves roll-forward residual (history) (Mar-26, INR 22,583 Cr): Share-funded NQXT acquisition (December 2025): 143,820,153 shares issued to the promoter-group vendor. Share capital rose INR 28.76 Cr (14.38 Cr shares at INR 2 face value) and the premium, about INR 1,560 a share, went to reserves. Screener records no equity issuance. Moves the valuation: no. Source: kb/annual_report/pages/page_0659.md (Consolidated Balance Sheet: Equity Share Capital 460.79 vs 432.03, AR p.660); data/financials.json</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adani Ports and Special Economic Zone Ltd - Summary</t>
   </si>
   <si>
@@ -914,6 +923,18 @@
     <t xml:space="preserve">assumptions.json net_debt, as at the balance-sheet date</t>
   </si>
   <si>
+    <t xml:space="preserve">    Lease liabilities (Ind AS 116, debt-like)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assumptions.json lease_liabilities (annual report)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Minority interest (book value)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assumptions.json minority_interest (annual report)</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Non-operating assets</t>
   </si>
   <si>
@@ -944,7 +965,52 @@
     <t xml:space="preserve">    Upside / (downside)</t>
   </si>
   <si>
-    <t xml:space="preserve">Exit-multiple cross-check and target</t>
+    <t xml:space="preserve">Target price (12-month forward)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Target method  (Perpetuity DCF or Exit multiple)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perpetuity DCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assumptions.json target_policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Horizon (months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Value per share today, on the target method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dividend per share, next 12 months (first forecast year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedules: dividends declared / shares, first forecast year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Forward value  (value x (1 + ke)^(h/12) - DPS x h/12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Rounding step (INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target price (INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    BUY above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House rating policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SELL below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit-multiple cross-check (not the target unless chosen above)</t>
   </si>
   <si>
     <t xml:space="preserve">    Terminal-year EBITDA</t>
@@ -953,10 +1019,7 @@
     <t xml:space="preserve">    Exit EV/EBITDA implied by the perpetuity TV</t>
   </si>
   <si>
-    <t xml:space="preserve">    Exit multiple (house convention)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target anchor: DCF with an exit multiple</t>
+    <t xml:space="preserve">    Exit multiple</t>
   </si>
   <si>
     <t xml:space="preserve">    Terminal value at exit multiple</t>
@@ -966,24 +1029,6 @@
   </si>
   <si>
     <t xml:space="preserve">Value per share at exit multiple (INR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Rounding step (INR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target price (INR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    BUY above</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House rating policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    SELL below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating</t>
   </si>
   <si>
     <t xml:space="preserve">    Alternative exit multiple</t>
@@ -1061,16 +1106,16 @@
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
     <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\)"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
-    <numFmt numFmtId="171" formatCode="0.0\x"/>
+    <numFmt numFmtId="171" formatCode="0"/>
     <numFmt numFmtId="172" formatCode="0.00%"/>
     <numFmt numFmtId="173" formatCode="0.00\x"/>
-    <numFmt numFmtId="174" formatCode="0"/>
-    <numFmt numFmtId="175" formatCode="0%"/>
-    <numFmt numFmtId="176" formatCode="#,##0.0"/>
-    <numFmt numFmtId="177" formatCode="#,##0.000;\(#,##0.000\)"/>
-    <numFmt numFmtId="178" formatCode="dd\-mmm\-yyyy"/>
-    <numFmt numFmtId="179" formatCode="0.000"/>
-    <numFmt numFmtId="180" formatCode="0.0000"/>
+    <numFmt numFmtId="174" formatCode="0%"/>
+    <numFmt numFmtId="175" formatCode="#,##0.0"/>
+    <numFmt numFmtId="176" formatCode="#,##0.000;\(#,##0.000\)"/>
+    <numFmt numFmtId="177" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="178" formatCode="0.000"/>
+    <numFmt numFmtId="179" formatCode="0.0000"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1333,7 +1378,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1390,7 +1435,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1398,7 +1443,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1486,7 +1531,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="171" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1502,7 +1547,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="174" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1510,7 +1555,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1534,11 +1579,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="175" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1594,15 +1639,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1642,7 +1687,19 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="177" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="178" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1650,11 +1707,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="168" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="165" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1662,23 +1719,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="180" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1871,7 +1920,7 @@
                   <c:v>    Probability-weighted, perpetuity</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>    DCF at the target exit multiple</c:v>
+                  <c:v>    DCF at the cross-check exit multiple</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>    DCF at the alternative exit multiple</c:v>
@@ -1889,22 +1938,22 @@
                 <c:formatCode>#,##0;\(#,##0\)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>563</c:v>
+                  <c:v>513</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>741</c:v>
+                  <c:v>691</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>268</c:v>
+                  <c:v>217</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>533.75</c:v>
+                  <c:v>483.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1195.23423599497</c:v>
+                  <c:v>1144.63376284308</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1666.61240482071</c:v>
+                  <c:v>1616.01193166881</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1695</c:v>
@@ -1915,11 +1964,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="32224135"/>
-        <c:axId val="13008187"/>
+        <c:axId val="70133606"/>
+        <c:axId val="44563335"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="32224135"/>
+        <c:axId val="70133606"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1952,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13008187"/>
+        <c:crossAx val="44563335"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1960,7 +2009,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13008187"/>
+        <c:axId val="44563335"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1993,7 +2042,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32224135"/>
+        <c:crossAx val="70133606"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2499,7 +2548,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="7" t="str">
-        <f aca="false">DCF!B59</f>
+        <f aca="false">DCF!B60</f>
         <v>SELL</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -2523,8 +2572,8 @@
         <v>10</v>
       </c>
       <c r="B6" s="10" t="n">
-        <f aca="false">DCF!B55</f>
-        <v>1195</v>
+        <f aca="false">DCF!B56</f>
+        <v>575</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>11</v>
@@ -2547,7 +2596,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="11" t="n">
-        <f aca="false">DCF!B44</f>
+        <f aca="false">DCF!B46</f>
         <v>1695</v>
       </c>
       <c r="D7" s="8" t="s">
@@ -2571,8 +2620,8 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="n">
-        <f aca="false">DCF!B56</f>
-        <v>-0.294985250737463</v>
+        <f aca="false">DCF!B57</f>
+        <v>-0.660766961651917</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>15</v>
@@ -2594,9 +2643,9 @@
       <c r="A9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="14" t="str">
         <f aca="false">DCF!B50</f>
-        <v>10</v>
+        <v>Perpetuity DCF</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>17</v>
@@ -2618,14 +2667,23 @@
       <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="16" t="str">
+      <c r="B10" s="16" t="n">
+        <f aca="false">DCF!B51</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="14" t="str">
         <f aca="false">Scenarios!B5</f>
         <v>Base</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>3</v>
@@ -2633,16 +2691,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="17" t="n">
-        <f aca="false">DCF!B43</f>
-        <v>563.380162903272</v>
+        <f aca="false">DCF!B45</f>
+        <v>512.779689751377</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="18" t="n">
         <f aca="false">DCF!B27</f>
@@ -2651,7 +2709,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">DCF!B28</f>
@@ -2660,7 +2718,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">DCF!B29</f>
@@ -2669,7 +2727,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="19" t="n">
         <f aca="false">DCF!B35</f>
@@ -2678,7 +2736,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">DCF!B34</f>
@@ -2687,87 +2745,87 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="9" t="n">
-        <f aca="false">DCF!B41</f>
-        <v>129800.479674246</v>
+        <f aca="false">DCF!B43</f>
+        <v>118142.338121989</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="17" t="n">
         <f aca="false">Scenarios!C44</f>
-        <v>563</v>
+        <v>513</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="17" t="n">
         <f aca="false">Scenarios!C45</f>
-        <v>741</v>
+        <v>691</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="17" t="n">
         <f aca="false">Scenarios!C46</f>
-        <v>268</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="17" t="n">
         <f aca="false">Scenarios!D47</f>
-        <v>533.75</v>
+        <v>483.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="17" t="n">
-        <f aca="false">DCF!B53</f>
-        <v>1195.23423599497</v>
+        <f aca="false">DCF!B68</f>
+        <v>1144.63376284308</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="17" t="n">
-        <f aca="false">DCF!B62</f>
-        <v>1666.61240482071</v>
+        <f aca="false">DCF!B70</f>
+        <v>1616.01193166881</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="17" t="n">
-        <f aca="false">DCF!B44</f>
+        <f aca="false">DCF!B46</f>
         <v>1695</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2798,12 +2856,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2812,50 +2870,50 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B6" s="41" t="n">
         <v>0.0678</v>
       </c>
       <c r="C6" s="71" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B7" s="41" t="n">
         <v>0.055</v>
       </c>
       <c r="C7" s="71" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B8" s="72" t="n">
         <v>1.3</v>
       </c>
       <c r="C8" s="71" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B9" s="73" t="n">
         <f aca="false">0.67*B8+0.33</f>
@@ -2864,7 +2922,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B10" s="74" t="n">
         <f aca="false">B6+B9*B7</f>
@@ -2873,35 +2931,35 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B13" s="41" t="n">
         <v>0.08</v>
       </c>
       <c r="C13" s="71" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">Scenarios!B39</f>
         <v>0.185</v>
       </c>
       <c r="C14" s="71" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B15" s="15" t="n">
         <f aca="false">B13*(1-B14)</f>
@@ -2910,18 +2968,18 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B16" s="41" t="n">
         <v>0.12</v>
       </c>
       <c r="C16" s="71" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B18" s="75" t="n">
         <f aca="false">B10*(1-B16)+B15*B16</f>
@@ -2930,7 +2988,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B19" s="19" t="n">
         <f aca="false">Scenarios!$B$40</f>
@@ -2939,7 +2997,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B20" s="76" t="str">
         <f aca="false">IF(B19&lt;WACC!$B$18,"OK","FAIL")</f>
@@ -2963,7 +3021,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -2972,17 +3030,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>6</v>
@@ -2991,18 +3049,18 @@
         <v>7</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3057,7 +3115,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Income Statement'!L12</f>
@@ -3082,7 +3140,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">Drivers!L22</f>
@@ -3107,7 +3165,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B10" s="52" t="n">
         <f aca="false">B8*(1-B9)</f>
@@ -3132,7 +3190,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">'Income Statement'!L11</f>
@@ -3157,7 +3215,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">-Schedules!L7</f>
@@ -3182,7 +3240,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">-Schedules!L12</f>
@@ -3207,7 +3265,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B14" s="63" t="n">
         <f aca="false">B10+B11+B12+B13</f>
@@ -3232,23 +3290,23 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B17" s="77" t="n">
         <v>46112</v>
       </c>
       <c r="C17" s="71" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B18" s="77" t="n">
         <v>46477</v>
@@ -3256,7 +3314,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B19" s="77" t="n">
         <v>46241</v>
@@ -3264,7 +3322,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B20" s="78" t="n">
         <f aca="false">MIN(1,MAX(0,(B18-B17)/365.25))</f>
@@ -3273,7 +3331,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B21" s="78" t="n">
         <f aca="false">$B$20</f>
@@ -3294,7 +3352,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B22" s="73" t="n">
         <f aca="false">$B$20*0.5</f>
@@ -3319,7 +3377,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B23" s="78" t="n">
         <f aca="false">1/(1+WACC!$B$18)^B22</f>
@@ -3344,7 +3402,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B24" s="52" t="n">
         <f aca="false">B14*B21*B23</f>
@@ -3369,12 +3427,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="40" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B27" s="18" t="n">
         <f aca="false">WACC!$B$18</f>
@@ -3383,7 +3441,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B28" s="19" t="n">
         <f aca="false">Scenarios!$B$40</f>
@@ -3392,18 +3450,18 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B29" s="41" t="n">
         <v>0.105</v>
       </c>
       <c r="C29" s="71" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B30" s="15" t="n">
         <f aca="false">$B$28/$B$29</f>
@@ -3412,7 +3470,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B31" s="52" t="n">
         <f aca="false">SUM(B24:F24)</f>
@@ -3421,7 +3479,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B32" s="52" t="n">
         <f aca="false">F10*(1+$B$28)*(1-$B$28/$B$29)/($B$27-$B$28)</f>
@@ -3430,7 +3488,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B33" s="52" t="n">
         <f aca="false">$B$32/(1+$B$27)^F22</f>
@@ -3439,7 +3497,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B34" s="63" t="n">
         <f aca="false">$B$31+$B$33</f>
@@ -3448,7 +3506,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B35" s="15" t="n">
         <f aca="false">$B$33/$B$34</f>
@@ -3457,236 +3515,309 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B36" s="80" t="n">
         <v>42910</v>
       </c>
       <c r="C36" s="71" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B37" s="80" t="n">
-        <v>3340.86</v>
+        <v>8296.02</v>
       </c>
       <c r="C37" s="71" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="B38" s="52" t="n">
-        <f aca="false">$B$34-$B$36+$B$37</f>
-        <v>124167.381476244</v>
+        <v>291</v>
+      </c>
+      <c r="B38" s="80" t="n">
+        <v>2856.18</v>
+      </c>
+      <c r="C38" s="71" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="B39" s="19" t="n">
+        <v>293</v>
+      </c>
+      <c r="B39" s="80" t="n">
+        <v>3340.86</v>
+      </c>
+      <c r="C39" s="71" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B40" s="52" t="n">
+        <f aca="false">$B$34-$B$36-$B$37-$B$38+$B$39</f>
+        <v>113015.181476244</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B41" s="19" t="n">
         <f aca="false">WACC!$B$10</f>
         <v>0.133855</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="B40" s="81" t="n">
-        <f aca="false">(1+$B$39)^((B19-B17)/365.25)</f>
-        <v>1.0453669726383</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B41" s="63" t="n">
-        <f aca="false">$B$38*$B$40</f>
-        <v>129800.479674246</v>
-      </c>
-    </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B42" s="13" t="n">
+        <v>297</v>
+      </c>
+      <c r="B42" s="81" t="n">
+        <f aca="false">(1+$B$41)^((B19-B17)/365.25)</f>
+        <v>1.0453669726383</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B43" s="63" t="n">
+        <f aca="false">$B$40*$B$42</f>
+        <v>118142.338121989</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B44" s="13" t="n">
         <f aca="false">Schedules!K23</f>
         <v>230.3959</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="B43" s="47" t="n">
-        <f aca="false">$B$41/$B$42</f>
-        <v>563.380162903272</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B45" s="47" t="n">
+        <f aca="false">$B$43/$B$44</f>
+        <v>512.779689751377</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B44" s="82" t="n">
+      <c r="B46" s="82" t="n">
         <v>1695</v>
       </c>
-      <c r="C44" s="71" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="B45" s="15" t="n">
-        <f aca="false">$B$43/$B$44-1</f>
-        <v>-0.667622322770931</v>
+      <c r="C46" s="71" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="40" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="B48" s="52" t="n">
+      <c r="A47" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B47" s="15" t="n">
+        <f aca="false">$B$45/$B$46-1</f>
+        <v>-0.697475109291223</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="40" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B50" s="83" t="s">
+        <v>305</v>
+      </c>
+      <c r="C50" s="71" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B51" s="38" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B52" s="46" t="n">
+        <f aca="false">IF($B$50="Exit multiple",$B$68,$B$45)</f>
+        <v>512.779689751377</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B53" s="13" t="n">
+        <f aca="false">IFERROR(Schedules!L22/Schedules!L23,0)</f>
+        <v>8.54922515313609</v>
+      </c>
+      <c r="C53" s="71" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="B54" s="46" t="n">
+        <f aca="false">$B$52*(1+$B$41)^($B$51/12)-$B$53*$B$51/12</f>
+        <v>572.868589969911</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="B55" s="38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B56" s="47" t="n">
+        <f aca="false">ROUND($B$54/$B$55,0)*$B$55</f>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="15" t="n">
+        <f aca="false">$B$56/$B$46-1</f>
+        <v>-0.660766961651917</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B58" s="41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C58" s="71" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B59" s="41" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C59" s="71" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B60" s="39" t="str">
+        <f aca="false">IF($B$57&gt;$B$58,"BUY",IF($B$57&lt;$B$59,"SELL","HOLD"))</f>
+        <v>SELL</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="40" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B63" s="52" t="n">
         <f aca="false">F7</f>
         <v>44232.0557729482</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="B49" s="83" t="n">
-        <f aca="false">$B$32/$B$48</f>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="B64" s="84" t="n">
+        <f aca="false">$B$32/$B$63</f>
         <v>4.63824067486421</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="B50" s="84" t="n">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B65" s="85" t="n">
         <v>10</v>
       </c>
-      <c r="C50" s="71" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="B51" s="52" t="n">
-        <f aca="false">$B$50*$B$48</f>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B66" s="52" t="n">
+        <f aca="false">$B$65*$B$63</f>
         <v>442320.557729482</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="B52" s="52" t="n">
-        <f aca="false">$B$51/(1+$B$27)^F22</f>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B67" s="52" t="n">
+        <f aca="false">$B$66/(1+$B$27)^F22</f>
         <v>259726.010792323</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B53" s="47" t="n">
-        <f aca="false">($B$31+$B$52-$B$36+$B$37)*$B$40/$B$42</f>
-        <v>1195.23423599497</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="B54" s="38" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="B55" s="47" t="n">
-        <f aca="false">ROUND($B$53/$B$54,0)*$B$54</f>
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B68" s="47" t="n">
+        <f aca="false">($B$31+$B$67-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
+        <v>1144.63376284308</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B69" s="85" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="15" t="n">
-        <f aca="false">$B$55/$B$44-1</f>
-        <v>-0.294985250737463</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="B57" s="41" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C57" s="71" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B58" s="41" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C58" s="71" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B59" s="39" t="str">
-        <f aca="false">IF($B$56&gt;$B$57,"BUY",IF($B$56&lt;$B$58,"SELL","HOLD"))</f>
-        <v>SELL</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="B61" s="84" t="n">
-        <v>14</v>
-      </c>
-      <c r="C61" s="71" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="B62" s="46" t="n">
-        <f aca="false">($B$31+$B$61*$B$48/(1+$B$27)^F22-$B$36+$B$37)*$B$40/$B$42</f>
-        <v>1666.61240482071</v>
+      <c r="C69" s="71" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="B70" s="46" t="n">
+        <f aca="false">($B$31+$B$69*$B$63/(1+$B$27)^F22-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
+        <v>1616.01193166881</v>
       </c>
     </row>
   </sheetData>
@@ -3715,17 +3846,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B4" s="41" t="n">
         <v>0.005</v>
@@ -3733,20 +3864,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="B5" s="84" t="n">
+        <v>331</v>
+      </c>
+      <c r="B5" s="85" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="39" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B8" s="74" t="n">
         <f aca="false">DCF!$B$28+(-2)*$B$4</f>
@@ -3775,24 +3906,24 @@
         <v>0.1156164</v>
       </c>
       <c r="B9" s="46" t="n">
-        <f aca="false">IF(B$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A9-B$8)/(1+$A9)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>687.551523042434</v>
+        <f aca="false">IF(B$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A9-B$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>636.951049890538</v>
       </c>
       <c r="C9" s="46" t="n">
-        <f aca="false">IF(C$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A9-C$8)/(1+$A9)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>683.014220557598</v>
+        <f aca="false">IF(C$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A9-C$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>632.413747405703</v>
       </c>
       <c r="D9" s="46" t="n">
-        <f aca="false">IF(D$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A9-D$8)/(1+$A9)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>677.217725490675</v>
+        <f aca="false">IF(D$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A9-D$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>626.617252338779</v>
       </c>
       <c r="E9" s="46" t="n">
-        <f aca="false">IF(E$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A9-E$8)/(1+$A9)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>669.850440836045</v>
+        <f aca="false">IF(E$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A9-E$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>619.249967684149</v>
       </c>
       <c r="F9" s="46" t="n">
-        <f aca="false">IF(F$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A9-F$8)/(1+$A9)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>660.48871738564</v>
+        <f aca="false">IF(F$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A9-F$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>609.888244233744</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3801,24 +3932,24 @@
         <v>0.1206164</v>
       </c>
       <c r="B10" s="46" t="n">
-        <f aca="false">IF(B$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A10-B$8)/(1+$A10)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>631.410116586815</v>
+        <f aca="false">IF(B$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A10-B$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>580.809643434919</v>
       </c>
       <c r="C10" s="46" t="n">
-        <f aca="false">IF(C$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A10-C$8)/(1+$A10)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>624.580183206379</v>
+        <f aca="false">IF(C$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A10-C$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>573.979710054484</v>
       </c>
       <c r="D10" s="46" t="n">
-        <f aca="false">IF(D$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A10-D$8)/(1+$A10)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>616.266062078821</v>
+        <f aca="false">IF(D$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A10-D$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>565.665588926925</v>
       </c>
       <c r="E10" s="46" t="n">
-        <f aca="false">IF(E$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A10-E$8)/(1+$A10)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>606.128465827708</v>
+        <f aca="false">IF(E$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A10-E$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>555.527992675812</v>
       </c>
       <c r="F10" s="46" t="n">
-        <f aca="false">IF(F$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A10-F$8)/(1+$A10)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>593.716161340329</v>
+        <f aca="false">IF(F$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A10-F$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>543.115688188434</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3827,24 +3958,24 @@
         <v>0.1256164</v>
       </c>
       <c r="B11" s="46" t="n">
-        <f aca="false">IF(B$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A11-B$8)/(1+$A11)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>581.877348560157</v>
+        <f aca="false">IF(B$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A11-B$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>531.276875408261</v>
       </c>
       <c r="C11" s="46" t="n">
-        <f aca="false">IF(C$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A11-C$8)/(1+$A11)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>573.42431704247</v>
+        <f aca="false">IF(C$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A11-C$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>522.823843890574</v>
       </c>
       <c r="D11" s="47" t="n">
-        <f aca="false">IF(D$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A11-D$8)/(1+$A11)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>563.380162903272</v>
+        <f aca="false">IF(D$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A11-D$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>512.779689751377</v>
       </c>
       <c r="E11" s="46" t="n">
-        <f aca="false">IF(E$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A11-E$8)/(1+$A11)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>551.406907438996</v>
+        <f aca="false">IF(E$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A11-E$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>500.806434287101</v>
       </c>
       <c r="F11" s="46" t="n">
-        <f aca="false">IF(F$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A11-F$8)/(1+$A11)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>537.063555412534</v>
+        <f aca="false">IF(F$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A11-F$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>486.463082260638</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3853,24 +3984,24 @@
         <v>0.1306164</v>
       </c>
       <c r="B12" s="46" t="n">
-        <f aca="false">IF(B$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A12-B$8)/(1+$A12)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>537.858131158963</v>
+        <f aca="false">IF(B$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A12-B$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>487.257658007067</v>
       </c>
       <c r="C12" s="46" t="n">
-        <f aca="false">IF(C$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A12-C$8)/(1+$A12)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>528.270933570473</v>
+        <f aca="false">IF(C$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A12-C$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>477.670460418578</v>
       </c>
       <c r="D12" s="46" t="n">
-        <f aca="false">IF(D$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A12-D$8)/(1+$A12)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>517.059375615685</v>
+        <f aca="false">IF(D$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A12-D$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>466.458902463789</v>
       </c>
       <c r="E12" s="46" t="n">
-        <f aca="false">IF(E$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A12-E$8)/(1+$A12)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>503.901233471531</v>
+        <f aca="false">IF(E$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A12-E$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>453.300760319635</v>
       </c>
       <c r="F12" s="46" t="n">
-        <f aca="false">IF(F$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A12-F$8)/(1+$A12)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>488.383022977952</v>
+        <f aca="false">IF(F$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A12-F$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>437.782549826056</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3879,53 +4010,53 @@
         <v>0.1356164</v>
       </c>
       <c r="B13" s="46" t="n">
-        <f aca="false">IF(B$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A13-B$8)/(1+$A13)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>498.486465566933</v>
+        <f aca="false">IF(B$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A13-B$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>447.885992415038</v>
       </c>
       <c r="C13" s="46" t="n">
-        <f aca="false">IF(C$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A13-C$8)/(1+$A13)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>488.125914275365</v>
+        <f aca="false">IF(C$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A13-C$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>437.525441123469</v>
       </c>
       <c r="D13" s="46" t="n">
-        <f aca="false">IF(D$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A13-D$8)/(1+$A13)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>476.153591666771</v>
+        <f aca="false">IF(D$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A13-D$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>425.553118514876</v>
       </c>
       <c r="E13" s="46" t="n">
-        <f aca="false">IF(E$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A13-E$8)/(1+$A13)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>462.269601321126</v>
+        <f aca="false">IF(E$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A13-E$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>411.66912816923</v>
       </c>
       <c r="F13" s="46" t="n">
-        <f aca="false">IF(F$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A13-F$8)/(1+$A13)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>446.094726348234</v>
+        <f aca="false">IF(F$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A13-F$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>395.494253196338</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="B16" s="85" t="n">
-        <f aca="false">DCF!$B$50+(-2)*$B$5</f>
+        <v>335</v>
+      </c>
+      <c r="B16" s="86" t="n">
+        <f aca="false">DCF!$B$65+(-2)*$B$5</f>
         <v>6</v>
       </c>
-      <c r="C16" s="85" t="n">
-        <f aca="false">DCF!$B$50+(-1)*$B$5</f>
+      <c r="C16" s="86" t="n">
+        <f aca="false">DCF!$B$65+(-1)*$B$5</f>
         <v>8</v>
       </c>
-      <c r="D16" s="85" t="n">
-        <f aca="false">DCF!$B$50+(0)*$B$5</f>
+      <c r="D16" s="86" t="n">
+        <f aca="false">DCF!$B$65+(0)*$B$5</f>
         <v>10</v>
       </c>
-      <c r="E16" s="85" t="n">
-        <f aca="false">DCF!$B$50+(1)*$B$5</f>
+      <c r="E16" s="86" t="n">
+        <f aca="false">DCF!$B$65+(1)*$B$5</f>
         <v>12</v>
       </c>
-      <c r="F16" s="85" t="n">
-        <f aca="false">DCF!$B$50+(2)*$B$5</f>
+      <c r="F16" s="86" t="n">
+        <f aca="false">DCF!$B$65+(2)*$B$5</f>
         <v>14</v>
       </c>
     </row>
@@ -3935,24 +4066,24 @@
         <v>0.1156164</v>
       </c>
       <c r="B17" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+B$16*DCF!$B$48/(1+$A17)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>757.554269683199</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>706.953796531303</v>
       </c>
       <c r="C17" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+C$16*DCF!$B$48/(1+$A17)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1002.89896147829</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>952.298488326392</v>
       </c>
       <c r="D17" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+D$16*DCF!$B$48/(1+$A17)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1248.24365327338</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1197.64318012148</v>
       </c>
       <c r="E17" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+E$16*DCF!$B$48/(1+$A17)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1493.58834506846</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1442.98787191657</v>
       </c>
       <c r="F17" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+F$16*DCF!$B$48/(1+$A17)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1738.93303686355</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1688.33256371166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3961,24 +4092,24 @@
         <v>0.1206164</v>
       </c>
       <c r="B18" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+B$16*DCF!$B$48/(1+$A18)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>740.504320979706</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>689.90384782781</v>
       </c>
       <c r="C18" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+C$16*DCF!$B$48/(1+$A18)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>980.961981380639</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>930.361508228743</v>
       </c>
       <c r="D18" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+D$16*DCF!$B$48/(1+$A18)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1221.41964178157</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1170.81916862968</v>
       </c>
       <c r="E18" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+E$16*DCF!$B$48/(1+$A18)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1461.8773021825</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1411.27682903061</v>
       </c>
       <c r="F18" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+F$16*DCF!$B$48/(1+$A18)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1702.33496258344</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1651.73448943154</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3987,24 +4118,24 @@
         <v>0.1256164</v>
       </c>
       <c r="B19" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+B$16*DCF!$B$48/(1+$A19)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>723.856067169241</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>673.255594017346</v>
       </c>
       <c r="C19" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+C$16*DCF!$B$48/(1+$A19)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>959.545151582108</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>908.944678430213</v>
       </c>
       <c r="D19" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+D$16*DCF!$B$48/(1+$A19)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1195.23423599497</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1144.63376284308</v>
       </c>
       <c r="E19" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+E$16*DCF!$B$48/(1+$A19)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1430.92332040784</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1380.32284725595</v>
       </c>
       <c r="F19" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+F$16*DCF!$B$48/(1+$A19)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1666.61240482071</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1616.01193166881</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4013,24 +4144,24 @@
         <v>0.1306164</v>
       </c>
       <c r="B20" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+B$16*DCF!$B$48/(1+$A20)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>707.598216854462</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>656.997743702566</v>
       </c>
       <c r="C20" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+C$16*DCF!$B$48/(1+$A20)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>938.633802284313</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>888.033329132418</v>
       </c>
       <c r="D20" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+D$16*DCF!$B$48/(1+$A20)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1169.66938771416</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1119.06891456227</v>
       </c>
       <c r="E20" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+E$16*DCF!$B$48/(1+$A20)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1400.70497314402</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1350.10449999212</v>
       </c>
       <c r="F20" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+F$16*DCF!$B$48/(1+$A20)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1631.74055857387</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1581.14008542197</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4039,24 +4170,24 @@
         <v>0.1356164</v>
       </c>
       <c r="B21" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+B$16*DCF!$B$48/(1+$A21)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>691.719845330306</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>641.119372178411</v>
       </c>
       <c r="C21" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+C$16*DCF!$B$48/(1+$A21)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>918.213741073476</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>867.613267921581</v>
       </c>
       <c r="D21" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+D$16*DCF!$B$48/(1+$A21)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1144.70763681665</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1094.10716366475</v>
       </c>
       <c r="E21" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+E$16*DCF!$B$48/(1+$A21)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1371.20153255982</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1320.60105940792</v>
       </c>
       <c r="F21" s="46" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+F$16*DCF!$B$48/(1+$A21)^DCF!$F$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>1597.69542830299</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>1547.09495515109</v>
       </c>
     </row>
   </sheetData>
@@ -4085,44 +4216,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -4134,18 +4265,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -4165,267 +4296,267 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B6" s="86" t="n">
+        <v>338</v>
+      </c>
+      <c r="B6" s="87" t="n">
         <f aca="false">('Balance Sheet'!B13-'Balance Sheet'!B22)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="86" t="n">
+      <c r="C6" s="87" t="n">
         <f aca="false">('Balance Sheet'!C13-'Balance Sheet'!C22)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="86" t="n">
+      <c r="D6" s="87" t="n">
         <f aca="false">('Balance Sheet'!D13-'Balance Sheet'!D22)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="86" t="n">
+      <c r="E6" s="87" t="n">
         <f aca="false">('Balance Sheet'!E13-'Balance Sheet'!E22)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="86" t="n">
+      <c r="F6" s="87" t="n">
         <f aca="false">('Balance Sheet'!F13-'Balance Sheet'!F22)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="86" t="n">
+      <c r="G6" s="87" t="n">
         <f aca="false">('Balance Sheet'!G13-'Balance Sheet'!G22)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="86" t="n">
+      <c r="H6" s="87" t="n">
         <f aca="false">('Balance Sheet'!H13-'Balance Sheet'!H22)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="86" t="n">
+      <c r="I6" s="87" t="n">
         <f aca="false">('Balance Sheet'!I13-'Balance Sheet'!I22)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="86" t="n">
+      <c r="J6" s="87" t="n">
         <f aca="false">('Balance Sheet'!J13-'Balance Sheet'!J22)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="86" t="n">
+      <c r="K6" s="87" t="n">
         <f aca="false">('Balance Sheet'!K13-'Balance Sheet'!K22)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="86" t="n">
+      <c r="L6" s="87" t="n">
         <f aca="false">('Balance Sheet'!L13-'Balance Sheet'!L22)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">('Balance Sheet'!M13-'Balance Sheet'!M22)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="86" t="n">
+      <c r="N6" s="87" t="n">
         <f aca="false">('Balance Sheet'!N13-'Balance Sheet'!N22)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="86" t="n">
+      <c r="O6" s="87" t="n">
         <f aca="false">('Balance Sheet'!O13-'Balance Sheet'!O22)</f>
         <v>0</v>
       </c>
-      <c r="P6" s="86" t="n">
+      <c r="P6" s="87" t="n">
         <f aca="false">('Balance Sheet'!P13-'Balance Sheet'!P22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="B7" s="86" t="n">
+        <v>339</v>
+      </c>
+      <c r="B7" s="87" t="n">
         <f aca="false">('Balance Sheet'!B6-'Cash Flow'!B23)</f>
         <v>-8330.01</v>
       </c>
-      <c r="C7" s="86" t="n">
+      <c r="C7" s="87" t="n">
         <f aca="false">('Balance Sheet'!C6-'Cash Flow'!C23)</f>
         <v>117.539999999997</v>
       </c>
-      <c r="D7" s="86" t="n">
+      <c r="D7" s="87" t="n">
         <f aca="false">('Balance Sheet'!D6-'Cash Flow'!D23)</f>
         <v>-479.429999999999</v>
       </c>
-      <c r="E7" s="86" t="n">
+      <c r="E7" s="87" t="n">
         <f aca="false">('Balance Sheet'!E6-'Cash Flow'!E23)</f>
         <v>-2028.33</v>
       </c>
-      <c r="F7" s="86" t="n">
+      <c r="F7" s="87" t="n">
         <f aca="false">('Balance Sheet'!F6-'Cash Flow'!F23)</f>
         <v>1006.35</v>
       </c>
-      <c r="G7" s="86" t="n">
+      <c r="G7" s="87" t="n">
         <f aca="false">('Balance Sheet'!G6-'Cash Flow'!G23)</f>
         <v>7550.11</v>
       </c>
-      <c r="H7" s="86" t="n">
+      <c r="H7" s="87" t="n">
         <f aca="false">('Balance Sheet'!H6-'Cash Flow'!H23)</f>
         <v>-661.070000000001</v>
       </c>
-      <c r="I7" s="86" t="n">
+      <c r="I7" s="87" t="n">
         <f aca="false">('Balance Sheet'!I6-'Cash Flow'!I23)</f>
         <v>574.300000000003</v>
       </c>
-      <c r="J7" s="86" t="n">
+      <c r="J7" s="87" t="n">
         <f aca="false">('Balance Sheet'!J6-'Cash Flow'!J23)</f>
         <v>-89.5900000000102</v>
       </c>
-      <c r="K7" s="86" t="n">
+      <c r="K7" s="87" t="n">
         <f aca="false">('Balance Sheet'!K6-'Cash Flow'!K23)</f>
         <v>22611.66</v>
       </c>
-      <c r="L7" s="86" t="n">
+      <c r="L7" s="87" t="n">
         <f aca="false">('Balance Sheet'!L6-'Cash Flow'!L23)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="86" t="n">
+      <c r="M7" s="87" t="n">
         <f aca="false">('Balance Sheet'!M6-'Cash Flow'!M23)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="86" t="n">
+      <c r="N7" s="87" t="n">
         <f aca="false">('Balance Sheet'!N6-'Cash Flow'!N23)</f>
         <v>0</v>
       </c>
-      <c r="O7" s="86" t="n">
+      <c r="O7" s="87" t="n">
         <f aca="false">('Balance Sheet'!O6-'Cash Flow'!O23)</f>
         <v>0</v>
       </c>
-      <c r="P7" s="86" t="n">
+      <c r="P7" s="87" t="n">
         <f aca="false">('Balance Sheet'!P6-'Cash Flow'!P23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="B8" s="86" t="n">
+        <v>340</v>
+      </c>
+      <c r="B8" s="87" t="n">
         <f aca="false">('Balance Sheet'!B16-(((0+'Income Statement'!B18)-Schedules!B22)+Drivers!B27))</f>
         <v>13469.49</v>
       </c>
-      <c r="C8" s="86" t="n">
+      <c r="C8" s="87" t="n">
         <f aca="false">('Balance Sheet'!C16-((('Balance Sheet'!B16+'Income Statement'!C18)-Schedules!C22)+Drivers!C27))</f>
         <v>117.539999999997</v>
       </c>
-      <c r="D8" s="86" t="n">
+      <c r="D8" s="87" t="n">
         <f aca="false">('Balance Sheet'!D16-((('Balance Sheet'!C16+'Income Statement'!D18)-Schedules!D22)+Drivers!D27))</f>
         <v>-479.43</v>
       </c>
-      <c r="E8" s="86" t="n">
+      <c r="E8" s="87" t="n">
         <f aca="false">('Balance Sheet'!E16-((('Balance Sheet'!D16+'Income Statement'!E18)-Schedules!E22)+Drivers!E27))</f>
         <v>-2020.49</v>
       </c>
-      <c r="F8" s="86" t="n">
+      <c r="F8" s="87" t="n">
         <f aca="false">('Balance Sheet'!F16-((('Balance Sheet'!E16+'Income Statement'!F18)-Schedules!F22)+Drivers!F27))</f>
         <v>1006.35</v>
       </c>
-      <c r="G8" s="86" t="n">
+      <c r="G8" s="87" t="n">
         <f aca="false">('Balance Sheet'!G16-((('Balance Sheet'!F16+'Income Statement'!G18)-Schedules!G22)+Drivers!G27))</f>
         <v>7533.99</v>
       </c>
-      <c r="H8" s="86" t="n">
+      <c r="H8" s="87" t="n">
         <f aca="false">('Balance Sheet'!H16-((('Balance Sheet'!G16+'Income Statement'!H18)-Schedules!H22)+Drivers!H27))</f>
         <v>-670.629999999997</v>
       </c>
-      <c r="I8" s="86" t="n">
+      <c r="I8" s="87" t="n">
         <f aca="false">('Balance Sheet'!I16-((('Balance Sheet'!H16+'Income Statement'!I18)-Schedules!I22)+Drivers!I27))</f>
         <v>574.299999999996</v>
       </c>
-      <c r="J8" s="86" t="n">
+      <c r="J8" s="87" t="n">
         <f aca="false">('Balance Sheet'!J16-((('Balance Sheet'!I16+'Income Statement'!J18)-Schedules!J22)+Drivers!J27))</f>
         <v>-89.5899999999965</v>
       </c>
-      <c r="K8" s="86" t="n">
+      <c r="K8" s="87" t="n">
         <f aca="false">('Balance Sheet'!K16-((('Balance Sheet'!J16+'Income Statement'!K18)-Schedules!K22)+Drivers!K27))</f>
         <v>22582.9</v>
       </c>
-      <c r="L8" s="86" t="n">
+      <c r="L8" s="87" t="n">
         <f aca="false">('Balance Sheet'!L16-((('Balance Sheet'!K16+'Income Statement'!L18)-Schedules!L22)+Drivers!L27))</f>
         <v>0</v>
       </c>
-      <c r="M8" s="86" t="n">
+      <c r="M8" s="87" t="n">
         <f aca="false">('Balance Sheet'!M16-((('Balance Sheet'!L16+'Income Statement'!M18)-Schedules!M22)+Drivers!M27))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="86" t="n">
+      <c r="N8" s="87" t="n">
         <f aca="false">('Balance Sheet'!N16-((('Balance Sheet'!M16+'Income Statement'!N18)-Schedules!N22)+Drivers!N27))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="86" t="n">
+      <c r="O8" s="87" t="n">
         <f aca="false">('Balance Sheet'!O16-((('Balance Sheet'!N16+'Income Statement'!O18)-Schedules!O22)+Drivers!O27))</f>
         <v>0</v>
       </c>
-      <c r="P8" s="86" t="n">
+      <c r="P8" s="87" t="n">
         <f aca="false">('Balance Sheet'!P16-((('Balance Sheet'!O16+'Income Statement'!P18)-Schedules!P22)+Drivers!P27))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="B9" s="86" t="n">
+        <v>341</v>
+      </c>
+      <c r="B9" s="87" t="n">
         <f aca="false">('Balance Sheet'!B10-Schedules!B9)</f>
         <v>22213.69</v>
       </c>
-      <c r="C9" s="86" t="n">
+      <c r="C9" s="87" t="n">
         <f aca="false">('Balance Sheet'!C10-Schedules!C9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="86" t="n">
+      <c r="D9" s="87" t="n">
         <f aca="false">('Balance Sheet'!D10-Schedules!D9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="86" t="n">
+      <c r="E9" s="87" t="n">
         <f aca="false">('Balance Sheet'!E10-Schedules!E9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="86" t="n">
+      <c r="F9" s="87" t="n">
         <f aca="false">('Balance Sheet'!F10-Schedules!F9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="86" t="n">
+      <c r="G9" s="87" t="n">
         <f aca="false">('Balance Sheet'!G10-Schedules!G9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="86" t="n">
+      <c r="H9" s="87" t="n">
         <f aca="false">('Balance Sheet'!H10-Schedules!H9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="86" t="n">
+      <c r="I9" s="87" t="n">
         <f aca="false">('Balance Sheet'!I10-Schedules!I9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="86" t="n">
+      <c r="J9" s="87" t="n">
         <f aca="false">('Balance Sheet'!J10-Schedules!J9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="86" t="n">
+      <c r="K9" s="87" t="n">
         <f aca="false">('Balance Sheet'!K10-Schedules!K9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="86" t="n">
+      <c r="L9" s="87" t="n">
         <f aca="false">('Balance Sheet'!L10-Schedules!L9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="86" t="n">
+      <c r="M9" s="87" t="n">
         <f aca="false">('Balance Sheet'!M10-Schedules!M9)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="86" t="n">
+      <c r="N9" s="87" t="n">
         <f aca="false">('Balance Sheet'!N10-Schedules!N9)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="86" t="n">
+      <c r="O9" s="87" t="n">
         <f aca="false">('Balance Sheet'!O10-Schedules!O9)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="86" t="n">
+      <c r="P9" s="87" t="n">
         <f aca="false">('Balance Sheet'!P10-Schedules!P9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -4445,260 +4576,260 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="B11" s="86" t="n">
+        <v>343</v>
+      </c>
+      <c r="B11" s="87" t="n">
         <f aca="false">('Balance Sheet'!B6-Drivers!B29)</f>
         <v>1976.8</v>
       </c>
-      <c r="C11" s="86" t="n">
+      <c r="C11" s="87" t="n">
         <f aca="false">('Balance Sheet'!C6-Drivers!C29)</f>
         <v>2967.55</v>
       </c>
-      <c r="D11" s="86" t="n">
+      <c r="D11" s="87" t="n">
         <f aca="false">('Balance Sheet'!D6-Drivers!D29)</f>
         <v>5967.3</v>
       </c>
-      <c r="E11" s="86" t="n">
+      <c r="E11" s="87" t="n">
         <f aca="false">('Balance Sheet'!E6-Drivers!E29)</f>
         <v>7313.86</v>
       </c>
-      <c r="F11" s="86" t="n">
+      <c r="F11" s="87" t="n">
         <f aca="false">('Balance Sheet'!F6-Drivers!F29)</f>
         <v>4700.78</v>
       </c>
-      <c r="G11" s="86" t="n">
+      <c r="G11" s="87" t="n">
         <f aca="false">('Balance Sheet'!G6-Drivers!G29)</f>
         <v>10667.41</v>
       </c>
-      <c r="H11" s="86" t="n">
+      <c r="H11" s="87" t="n">
         <f aca="false">('Balance Sheet'!H6-Drivers!H29)</f>
         <v>4334.31</v>
       </c>
-      <c r="I11" s="86" t="n">
+      <c r="I11" s="87" t="n">
         <f aca="false">('Balance Sheet'!I6-Drivers!I29)</f>
         <v>7631.88</v>
       </c>
-      <c r="J11" s="86" t="n">
+      <c r="J11" s="87" t="n">
         <f aca="false">('Balance Sheet'!J6-Drivers!J29)</f>
         <v>6605.97</v>
       </c>
-      <c r="K11" s="86" t="n">
+      <c r="K11" s="87" t="n">
         <f aca="false">('Balance Sheet'!K6-Drivers!K29)</f>
         <v>8483.51</v>
       </c>
-      <c r="L11" s="86" t="n">
+      <c r="L11" s="87" t="n">
         <f aca="false">('Balance Sheet'!L6-Drivers!L29)</f>
         <v>10550.4783685162</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">('Balance Sheet'!M6-Drivers!M29)</f>
         <v>18171.5525715915</v>
       </c>
-      <c r="N11" s="86" t="n">
+      <c r="N11" s="87" t="n">
         <f aca="false">('Balance Sheet'!N6-Drivers!N29)</f>
         <v>26727.4787849327</v>
       </c>
-      <c r="O11" s="86" t="n">
+      <c r="O11" s="87" t="n">
         <f aca="false">('Balance Sheet'!O6-Drivers!O29)</f>
         <v>36651.5365914683</v>
       </c>
-      <c r="P11" s="86" t="n">
+      <c r="P11" s="87" t="n">
         <f aca="false">('Balance Sheet'!P6-Drivers!P29)</f>
         <v>49620.6086989759</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="B12" s="86" t="n">
+        <v>344</v>
+      </c>
+      <c r="B12" s="87" t="n">
         <f aca="false">'Balance Sheet'!B18</f>
         <v>0</v>
       </c>
-      <c r="C12" s="86" t="n">
+      <c r="C12" s="87" t="n">
         <f aca="false">'Balance Sheet'!C18</f>
         <v>0</v>
       </c>
-      <c r="D12" s="86" t="n">
+      <c r="D12" s="87" t="n">
         <f aca="false">'Balance Sheet'!D18</f>
         <v>0</v>
       </c>
-      <c r="E12" s="86" t="n">
+      <c r="E12" s="87" t="n">
         <f aca="false">'Balance Sheet'!E18</f>
         <v>0</v>
       </c>
-      <c r="F12" s="86" t="n">
+      <c r="F12" s="87" t="n">
         <f aca="false">'Balance Sheet'!F18</f>
         <v>0</v>
       </c>
-      <c r="G12" s="86" t="n">
+      <c r="G12" s="87" t="n">
         <f aca="false">'Balance Sheet'!G18</f>
         <v>0</v>
       </c>
-      <c r="H12" s="86" t="n">
+      <c r="H12" s="87" t="n">
         <f aca="false">'Balance Sheet'!H18</f>
         <v>0</v>
       </c>
-      <c r="I12" s="86" t="n">
+      <c r="I12" s="87" t="n">
         <f aca="false">'Balance Sheet'!I18</f>
         <v>0</v>
       </c>
-      <c r="J12" s="86" t="n">
+      <c r="J12" s="87" t="n">
         <f aca="false">'Balance Sheet'!J18</f>
         <v>0</v>
       </c>
-      <c r="K12" s="86" t="n">
+      <c r="K12" s="87" t="n">
         <f aca="false">'Balance Sheet'!K18</f>
         <v>0</v>
       </c>
-      <c r="L12" s="86" t="n">
+      <c r="L12" s="87" t="n">
         <f aca="false">'Balance Sheet'!L18</f>
         <v>0</v>
       </c>
-      <c r="M12" s="86" t="n">
+      <c r="M12" s="87" t="n">
         <f aca="false">'Balance Sheet'!M18</f>
         <v>0</v>
       </c>
-      <c r="N12" s="86" t="n">
+      <c r="N12" s="87" t="n">
         <f aca="false">'Balance Sheet'!N18</f>
         <v>0</v>
       </c>
-      <c r="O12" s="86" t="n">
+      <c r="O12" s="87" t="n">
         <f aca="false">'Balance Sheet'!O18</f>
         <v>0</v>
       </c>
-      <c r="P12" s="86" t="n">
+      <c r="P12" s="87" t="n">
         <f aca="false">'Balance Sheet'!P18</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="B13" s="86" t="n">
+        <v>345</v>
+      </c>
+      <c r="B13" s="87" t="n">
         <f aca="false">'Balance Sheet'!B10</f>
         <v>21053.5</v>
       </c>
-      <c r="C13" s="86" t="n">
+      <c r="C13" s="87" t="n">
         <f aca="false">'Balance Sheet'!C10</f>
         <v>22670.01</v>
       </c>
-      <c r="D13" s="86" t="n">
+      <c r="D13" s="87" t="n">
         <f aca="false">'Balance Sheet'!D10</f>
         <v>28121.42</v>
       </c>
-      <c r="E13" s="86" t="n">
+      <c r="E13" s="87" t="n">
         <f aca="false">'Balance Sheet'!E10</f>
         <v>32714.51</v>
       </c>
-      <c r="F13" s="86" t="n">
+      <c r="F13" s="87" t="n">
         <f aca="false">'Balance Sheet'!F10</f>
         <v>48290.96</v>
       </c>
-      <c r="G13" s="86" t="n">
+      <c r="G13" s="87" t="n">
         <f aca="false">'Balance Sheet'!G10</f>
         <v>62552.92</v>
       </c>
-      <c r="H13" s="86" t="n">
+      <c r="H13" s="87" t="n">
         <f aca="false">'Balance Sheet'!H10</f>
         <v>72223.73</v>
       </c>
-      <c r="I13" s="86" t="n">
+      <c r="I13" s="87" t="n">
         <f aca="false">'Balance Sheet'!I10</f>
         <v>75147.81</v>
       </c>
-      <c r="J13" s="86" t="n">
+      <c r="J13" s="87" t="n">
         <f aca="false">'Balance Sheet'!J10</f>
         <v>89616.32</v>
       </c>
-      <c r="K13" s="86" t="n">
+      <c r="K13" s="87" t="n">
         <f aca="false">'Balance Sheet'!K10</f>
         <v>131652.5</v>
       </c>
-      <c r="L13" s="86" t="n">
+      <c r="L13" s="87" t="n">
         <f aca="false">'Balance Sheet'!L10</f>
         <v>138607.49234293</v>
       </c>
-      <c r="M13" s="86" t="n">
+      <c r="M13" s="87" t="n">
         <f aca="false">'Balance Sheet'!M10</f>
         <v>146526.286735102</v>
       </c>
-      <c r="N13" s="86" t="n">
+      <c r="N13" s="87" t="n">
         <f aca="false">'Balance Sheet'!N10</f>
         <v>155685.272967819</v>
       </c>
-      <c r="O13" s="86" t="n">
+      <c r="O13" s="87" t="n">
         <f aca="false">'Balance Sheet'!O10</f>
         <v>166228.332603398</v>
       </c>
-      <c r="P13" s="86" t="n">
+      <c r="P13" s="87" t="n">
         <f aca="false">'Balance Sheet'!P10</f>
         <v>176959.616310316</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="B14" s="86" t="n">
+        <v>240</v>
+      </c>
+      <c r="B14" s="87" t="n">
         <f aca="false">Schedules!B24</f>
         <v>17525.98</v>
       </c>
-      <c r="C14" s="86" t="n">
+      <c r="C14" s="87" t="n">
         <f aca="false">Schedules!C24</f>
         <v>20902.95</v>
       </c>
-      <c r="D14" s="86" t="n">
+      <c r="D14" s="87" t="n">
         <f aca="false">Schedules!D24</f>
         <v>24372.32</v>
       </c>
-      <c r="E14" s="86" t="n">
+      <c r="E14" s="87" t="n">
         <f aca="false">Schedules!E24</f>
         <v>25456.96</v>
       </c>
-      <c r="F14" s="86" t="n">
+      <c r="F14" s="87" t="n">
         <f aca="false">Schedules!F24</f>
         <v>30441.73</v>
       </c>
-      <c r="G14" s="86" t="n">
+      <c r="G14" s="87" t="n">
         <f aca="false">Schedules!G24</f>
         <v>41821.69</v>
       </c>
-      <c r="H14" s="86" t="n">
+      <c r="H14" s="87" t="n">
         <f aca="false">Schedules!H24</f>
         <v>45389.39</v>
       </c>
-      <c r="I14" s="86" t="n">
+      <c r="I14" s="87" t="n">
         <f aca="false">Schedules!I24</f>
         <v>52778.24</v>
       </c>
-      <c r="J14" s="86" t="n">
+      <c r="J14" s="87" t="n">
         <f aca="false">Schedules!J24</f>
         <v>62268.86</v>
       </c>
-      <c r="K14" s="86" t="n">
+      <c r="K14" s="87" t="n">
         <f aca="false">Schedules!K24</f>
         <v>95958.77</v>
       </c>
-      <c r="L14" s="86" t="n">
+      <c r="L14" s="87" t="n">
         <f aca="false">Schedules!L24</f>
         <v>107697.663166331</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">Schedules!M24</f>
         <v>121423.251026182</v>
       </c>
-      <c r="N14" s="86" t="n">
+      <c r="N14" s="87" t="n">
         <f aca="false">Schedules!N24</f>
         <v>137717.507009818</v>
       </c>
-      <c r="O14" s="86" t="n">
+      <c r="O14" s="87" t="n">
         <f aca="false">Schedules!O24</f>
         <v>157026.956694116</v>
       </c>
-      <c r="P14" s="86" t="n">
+      <c r="P14" s="87" t="n">
         <f aca="false">Schedules!P24</f>
         <v>178972.789003726</v>
       </c>
@@ -4726,7 +4857,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
@@ -4735,132 +4866,132 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="0" t="s">
         <v>58</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" s="0" t="n">
         <v>22582.9</v>
@@ -4871,38 +5002,38 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>61</v>
-      </c>
       <c r="C17" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>4415.24</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>10550.461</v>
@@ -4913,10 +5044,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>0</v>
@@ -4927,10 +5058,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>138607.4628</v>
@@ -4941,10 +5072,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>107697.64</v>
@@ -4955,10 +5086,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>0</v>
@@ -4969,138 +5100,148 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="0" t="s">
         <v>73</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5129,44 +5270,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -5178,18 +5319,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -5274,7 +5415,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">(IFERROR(('Income Statement'!B6)/(0),0)-1)</f>
@@ -5404,7 +5545,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B10)/('Income Statement'!B6),0)</f>
@@ -5469,7 +5610,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">'Income Statement'!B12</f>
@@ -5599,7 +5740,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B12" s="34" t="n">
         <f aca="false">'Income Statement'!B19</f>
@@ -5664,7 +5805,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
@@ -5684,7 +5825,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B14" s="29" t="n">
         <f aca="false">(((('Income Statement'!B12*(1-Drivers!B22))+'Income Statement'!B11)-Schedules!B7)-Schedules!B12)</f>
@@ -5749,7 +5890,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">(((('Income Statement'!B18+'Income Statement'!B11)-Schedules!B7)-Schedules!B12)+('Balance Sheet'!B19-0))</f>
@@ -5814,7 +5955,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">IFERROR((B14)/('Income Statement'!B10),0)</f>
@@ -5879,7 +6020,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -5899,7 +6040,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">(('Balance Sheet'!B19-'Balance Sheet'!B6)-'Balance Sheet'!B12)</f>
@@ -5964,7 +6105,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B19" s="36" t="n">
         <f aca="false">IFERROR((B18)/('Income Statement'!B10),0)</f>
@@ -6029,7 +6170,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B20" s="36" t="n">
         <f aca="false">IFERROR(('Income Statement'!B12)/('Income Statement'!B14),0)</f>
@@ -6094,7 +6235,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">((('Balance Sheet'!B15+'Balance Sheet'!B16)+'Balance Sheet'!B19)-'Balance Sheet'!B6)</f>
@@ -6159,7 +6300,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">IFERROR((('Income Statement'!B12*(1-Drivers!B22)))/(AVERAGE(0,B21)),0)</f>
@@ -6224,7 +6365,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B23" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B18)/(AVERAGE(0,Schedules!B24)),0)</f>
@@ -6313,17 +6454,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B4" s="38" t="n">
         <v>1</v>
@@ -6331,7 +6472,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B5" s="39" t="str">
         <f aca="false">CHOOSE($B$4,"Base","Bull","Bear")</f>
@@ -6340,7 +6481,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>6</v>
@@ -6349,23 +6490,23 @@
         <v>7</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B9" s="41" t="n">
         <v>0.2139</v>
@@ -6385,7 +6526,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B10" s="41" t="n">
         <v>0.585</v>
@@ -6405,7 +6546,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B11" s="41" t="n">
         <v>0.31</v>
@@ -6425,7 +6566,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B12" s="41" t="n">
         <v>0.185</v>
@@ -6445,7 +6586,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="41" t="n">
         <v>0.05</v>
@@ -6453,7 +6594,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B14" s="42" t="n">
         <v>0.5</v>
@@ -6461,17 +6602,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="43" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B18" s="41" t="n">
         <v>0.24</v>
@@ -6491,7 +6632,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B19" s="41" t="n">
         <v>0.595</v>
@@ -6511,7 +6652,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B20" s="41" t="n">
         <v>0.3</v>
@@ -6531,7 +6672,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B21" s="41" t="n">
         <v>0.16</v>
@@ -6551,7 +6692,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" s="41" t="n">
         <v>0.055</v>
@@ -6559,7 +6700,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B23" s="42" t="n">
         <v>0.25</v>
@@ -6567,17 +6708,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="43" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="40" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B27" s="41" t="n">
         <v>0.16</v>
@@ -6597,7 +6738,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B28" s="41" t="n">
         <v>0.57</v>
@@ -6617,7 +6758,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B29" s="41" t="n">
         <v>0.34</v>
@@ -6637,7 +6778,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B30" s="41" t="n">
         <v>0.23</v>
@@ -6657,7 +6798,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B31" s="41" t="n">
         <v>0.035</v>
@@ -6665,7 +6806,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B32" s="42" t="n">
         <v>0.25</v>
@@ -6673,17 +6814,17 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="43" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="40" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B36" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B9,B18,B27)</f>
@@ -6708,7 +6849,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B37" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B10,B19,B28)</f>
@@ -6733,7 +6874,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B38" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B11,B20,B29)</f>
@@ -6758,7 +6899,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B39" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B12,B21,B30)</f>
@@ -6783,7 +6924,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B40" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B13,B22,B31)</f>
@@ -6792,74 +6933,74 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="40" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B44" s="44" t="n">
         <f aca="false">B14</f>
         <v>0.5</v>
       </c>
       <c r="C44" s="45" t="n">
-        <v>563</v>
+        <v>513</v>
       </c>
       <c r="D44" s="46" t="n">
         <f aca="false">B44*C44</f>
-        <v>281.5</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B45" s="44" t="n">
         <f aca="false">B23</f>
         <v>0.25</v>
       </c>
       <c r="C45" s="45" t="n">
-        <v>741</v>
+        <v>691</v>
       </c>
       <c r="D45" s="46" t="n">
         <f aca="false">B45*C45</f>
-        <v>185.25</v>
+        <v>172.75</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B46" s="44" t="n">
         <f aca="false">B32</f>
         <v>0.25</v>
       </c>
       <c r="C46" s="45" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D46" s="46" t="n">
         <f aca="false">B46*C46</f>
-        <v>67</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B47" s="44" t="n">
         <f aca="false">SUM(B44:B46)</f>
@@ -6867,30 +7008,30 @@
       </c>
       <c r="D47" s="47" t="n">
         <f aca="false">SUM(D44:D46)</f>
-        <v>533.75</v>
+        <v>483.5</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B49" s="48" t="n">
-        <f aca="false">DCF!B43</f>
-        <v>563.380162903272</v>
+        <f aca="false">DCF!B45</f>
+        <v>512.779689751377</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B50" s="46" t="n">
         <f aca="false">INDEX(C44:C46,Scenarios!$B$4)</f>
-        <v>563</v>
+        <v>513</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B51" s="47" t="n">
         <f aca="false">ROUND(B49,0)-B50</f>
@@ -6929,44 +7070,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -6978,18 +7119,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -7009,7 +7150,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" s="19" t="n">
         <f aca="false">(IFERROR(('Income Statement'!B6)/(0),0)-1)</f>
@@ -7074,7 +7215,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B8)/('Income Statement'!B6),0)</f>
@@ -7134,7 +7275,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B10)/('Income Statement'!B6),0)</f>
@@ -7199,7 +7340,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B13)/('Income Statement'!B6),0)</f>
@@ -7259,7 +7400,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -7279,7 +7420,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">IFERROR((Schedules!B7)/('Income Statement'!B6),0)</f>
@@ -7344,7 +7485,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B12" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B11)/(0),0)</f>
@@ -7404,7 +7545,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B11)/('Income Statement'!B6),0)</f>
@@ -7464,7 +7605,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!B11)/('Income Statement'!B6),0)</f>
@@ -7524,7 +7665,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B15" s="28"/>
       <c r="C15" s="28"/>
@@ -7544,7 +7685,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B16" s="50" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B7)/('Income Statement'!B6),0)*365)</f>
@@ -7604,7 +7745,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B17" s="50" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B8)/('Income Statement'!B7),0)*365)</f>
@@ -7664,7 +7805,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B18" s="50" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B20)/('Income Statement'!B7),0)*365)</f>
@@ -7724,7 +7865,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B19" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!B9)/('Income Statement'!B6),0)</f>
@@ -7784,7 +7925,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B20" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!B21)/('Income Statement'!B6),0)</f>
@@ -7844,7 +7985,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
@@ -7864,7 +8005,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B17)/('Income Statement'!B16),0)</f>
@@ -7929,7 +8070,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B23" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B14)/(AVERAGE(0,'Balance Sheet'!B19)),0)</f>
@@ -7989,7 +8130,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B24" s="15" t="n">
         <f aca="false">0</f>
@@ -8049,7 +8190,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B25" s="19" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B17)/(0),0)-1)</f>
@@ -8109,7 +8250,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B26" s="52" t="n">
         <f aca="false">0</f>
@@ -8169,7 +8310,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B27" s="52" t="n">
         <f aca="false">0</f>
@@ -8229,7 +8370,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B28" s="19" t="n">
         <f aca="false">IFERROR((Schedules!B22)/('Income Statement'!B18),0)</f>
@@ -8289,7 +8430,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B29" s="52" t="n">
         <f aca="false">0</f>
@@ -8373,44 +8514,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -8422,18 +8563,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -8508,7 +8649,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B7" s="55" t="n">
         <v>2217.15</v>
@@ -8563,7 +8704,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B8" s="56" t="n">
         <f aca="false">(B6-B7)</f>
@@ -8628,7 +8769,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B9" s="52" t="n">
         <f aca="false">(B8-B10)</f>
@@ -8748,7 +8889,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B11" s="55" t="n">
         <v>1160.19</v>
@@ -8803,7 +8944,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B12" s="61" t="n">
         <f aca="false">(B10-B11)</f>
@@ -8868,7 +9009,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B13" s="55" t="n">
         <v>1036.57</v>
@@ -8923,7 +9064,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B14" s="55" t="n">
         <v>1115.74</v>
@@ -8978,7 +9119,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B15" s="55" t="n">
         <v>0</v>
@@ -9033,7 +9174,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B16" s="59" t="n">
         <v>4178.87</v>
@@ -9088,7 +9229,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B17" s="55" t="n">
         <v>267.35</v>
@@ -9198,7 +9339,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B19" s="34" t="n">
         <f aca="false">IFERROR((B18)/(Schedules!B23),0)</f>
@@ -9287,44 +9428,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -9336,18 +9477,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -9367,7 +9508,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B6" s="55" t="n">
         <v>1976.8</v>
@@ -9422,7 +9563,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B7" s="55" t="n">
         <v>2692.99</v>
@@ -9477,7 +9618,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B8" s="55" t="n">
         <v>657.09</v>
@@ -9532,7 +9673,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B9" s="55" t="n">
         <v>11313.66</v>
@@ -9587,7 +9728,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B10" s="55" t="n">
         <v>21053.5</v>
@@ -9642,7 +9783,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B11" s="55" t="n">
         <v>4513.97</v>
@@ -9697,7 +9838,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B12" s="55" t="n">
         <v>1161.36</v>
@@ -9752,7 +9893,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B13" s="61" t="n">
         <f aca="false">((((((B6+B7)+B8)+B9)+B10)+B11)+B12)</f>
@@ -9817,7 +9958,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
@@ -9837,7 +9978,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B15" s="55" t="n">
         <v>414.19</v>
@@ -9892,7 +10033,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B16" s="55" t="n">
         <v>17111.79</v>
@@ -9947,7 +10088,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B17" s="55" t="n">
         <v>22214.26</v>
@@ -10002,7 +10143,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B18" s="55" t="n">
         <v>0</v>
@@ -10057,7 +10198,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B19" s="52" t="n">
         <f aca="false">(B17+B18)</f>
@@ -10122,7 +10263,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B20" s="55" t="n">
         <v>0</v>
@@ -10177,7 +10318,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B21" s="55" t="n">
         <v>3629.13</v>
@@ -10232,7 +10373,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B22" s="61" t="n">
         <f aca="false">((((B15+B16)+B19)+B20)+B21)</f>
@@ -10321,44 +10462,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -10370,18 +10511,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -10401,7 +10542,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">'Income Statement'!B18</f>
@@ -10466,7 +10607,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">'Income Statement'!B11</f>
@@ -10531,7 +10672,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">-(Schedules!B12)</f>
@@ -10596,7 +10737,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B9" s="61" t="n">
         <f aca="false">((B6+B7)+B8)</f>
@@ -10661,7 +10802,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -10681,7 +10822,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">(-(Schedules!B7)-('Balance Sheet'!B11-0))</f>
@@ -10746,7 +10887,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">-(('Balance Sheet'!B12-0))</f>
@@ -10811,7 +10952,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B13" s="61" t="n">
         <f aca="false">(B11+B12)</f>
@@ -10876,7 +11017,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
@@ -10896,7 +11037,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">('Balance Sheet'!B17-0)</f>
@@ -10961,7 +11102,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">('Balance Sheet'!B18-0)</f>
@@ -11026,7 +11167,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">-(Schedules!B22)</f>
@@ -11091,7 +11232,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">Drivers!B27</f>
@@ -11156,7 +11297,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B19" s="61" t="n">
         <f aca="false">(((B15+B16)+B17)+B18)</f>
@@ -11221,7 +11362,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
@@ -11241,7 +11382,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B21" s="63" t="n">
         <f aca="false">((B9+B13)+B19)</f>
@@ -11306,7 +11447,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B22" s="52" t="n">
         <f aca="false">0</f>
@@ -11371,7 +11512,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B23" s="61" t="n">
         <f aca="false">(B22+B21)</f>
@@ -11436,7 +11577,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
@@ -11456,7 +11597,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B25" s="55" t="n">
         <v>4062.57</v>
@@ -11511,7 +11652,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B26" s="55" t="n">
         <v>-2629.15</v>
@@ -11566,7 +11707,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B27" s="55" t="n">
         <v>-1324.71</v>
@@ -11621,7 +11762,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B28" s="65" t="n">
         <f aca="false">(B9-B25)</f>
@@ -11710,44 +11851,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -11759,18 +11900,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -11790,7 +11931,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B6" s="52" t="n">
         <f aca="false">0</f>
@@ -11855,7 +11996,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B7" s="55" t="n">
         <v>0</v>
@@ -11910,7 +12051,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Income Statement'!B11</f>
@@ -11975,7 +12116,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B9" s="61" t="n">
         <f aca="false">((B6+B7)-B8)</f>
@@ -12040,7 +12181,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -12060,7 +12201,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B11" s="29" t="n">
         <f aca="false">(((('Balance Sheet'!B7+'Balance Sheet'!B8)+'Balance Sheet'!B9)-'Balance Sheet'!B20)-'Balance Sheet'!B21)</f>
@@ -12125,7 +12266,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B12" s="52" t="n">
         <f aca="false">(B11-0)</f>
@@ -12190,7 +12331,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B13" s="50" t="n">
         <f aca="false">(IFERROR((B11)/('Income Statement'!B6),0)*365)</f>
@@ -12255,7 +12396,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
@@ -12275,7 +12416,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B15" s="52" t="n">
         <f aca="false">0</f>
@@ -12340,7 +12481,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">(('Cash Flow'!B15+'Cash Flow'!B17)+'Cash Flow'!B18)</f>
@@ -12405,7 +12546,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">(((0+'Cash Flow'!B9)+'Cash Flow'!B13)+B16)</f>
@@ -12470,7 +12611,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">MAX((Drivers!B29-B17),0)</f>
@@ -12535,7 +12676,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">MIN(0,MAX((B17-Drivers!B29),0))</f>
@@ -12600,7 +12741,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">AVERAGE(0,'Balance Sheet'!B19)</f>
@@ -12665,7 +12806,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
@@ -12685,7 +12826,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B22" s="55" t="n">
         <v>269.22</v>
@@ -12740,7 +12881,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B23" s="68" t="n">
         <v>207.0952</v>
@@ -12795,7 +12936,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B24" s="29" t="n">
         <f aca="false">('Balance Sheet'!B15+'Balance Sheet'!B16)</f>
@@ -12860,7 +13001,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B25" s="70" t="n">
         <f aca="false">IFERROR((B24)/(B23),0)</f>

--- a/reports/ADANIPORTS/Adani_Ports_and_Special_Economic_Zone_Ltd_ERIP_Model.xlsx
+++ b/reports/ADANIPORTS/Adani_Ports_and_Special_Economic_Zone_Ltd_ERIP_Model.xlsx
@@ -1964,11 +1964,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="70133606"/>
-        <c:axId val="44563335"/>
+        <c:axId val="40744974"/>
+        <c:axId val="447348"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70133606"/>
+        <c:axId val="40744974"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44563335"/>
+        <c:crossAx val="447348"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2009,7 +2009,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44563335"/>
+        <c:axId val="447348"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2042,7 +2042,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70133606"/>
+        <c:crossAx val="40744974"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/reports/ADANIPORTS/Adani_Ports_and_Special_Economic_Zone_Ltd_ERIP_Model.xlsx
+++ b/reports/ADANIPORTS/Adani_Ports_and_Special_Economic_Zone_Ltd_ERIP_Model.xlsx
@@ -20,18 +20,20 @@
     <sheet name="WACC" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="DCF" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Sensitivity" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Checks" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Stress" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Checks" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Titles" vbProcedure="false">'Balance Sheet'!$A:$A,'Balance Sheet'!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Titles" vbProcedure="false">'Cash Flow'!$A:$A,'Cash Flow'!$1:$4</definedName>
-    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Titles" vbProcedure="false">Checks!$A:$A,Checks!$1:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="13" name="_xlnm.Print_Titles" vbProcedure="false">Checks!$A:$A,Checks!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Titles" vbProcedure="false">DCF!$A:$A,DCF!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">Drivers!$A:$A,Drivers!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">'Income Statement'!$A:$A,'Income Statement'!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">Scenarios!$A:$A,Scenarios!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Titles" vbProcedure="false">Schedules!$A:$A,Schedules!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="11" name="_xlnm.Print_Titles" vbProcedure="false">Sensitivity!$A:$A,Sensitivity!$1:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Titles" vbProcedure="false">Stress!$A:$A,Stress!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Summary!$A:$A,Summary!$1:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Summary!$1:$4,Summary!$A:$A</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">Scenarios!$1:$4,Scenarios!$A:$A</definedName>
@@ -42,7 +44,8 @@
     <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Titles" vbProcedure="false">Schedules!$1:$4,Schedules!$A:$A</definedName>
     <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Titles" vbProcedure="false">DCF!$1:$4,DCF!$A:$A</definedName>
     <definedName function="false" hidden="false" localSheetId="11" name="_xlnm.Print_Titles" vbProcedure="false">Sensitivity!$1:$4,Sensitivity!$A:$A</definedName>
-    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Titles" vbProcedure="false">Checks!$1:$4,Checks!$A:$A</definedName>
+    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Titles" vbProcedure="false">Stress!$1:$4,Stress!$A:$A</definedName>
+    <definedName function="false" hidden="false" localSheetId="13" name="_xlnm.Print_Titles" vbProcedure="false">Checks!$1:$4,Checks!$A:$A</definedName>
   </definedNames>
   <calcPr iterateCount="1000" refMode="A1" iterate="true" iterateDelta="1E-007"/>
   <extLst>
@@ -54,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="372">
   <si>
     <t xml:space="preserve">Adani Ports and Special Economic Zone Ltd - Dashboard</t>
   </si>
@@ -155,9 +158,6 @@
     <t xml:space="preserve">    Bear case, perpetuity DCF</t>
   </si>
   <si>
-    <t xml:space="preserve">    Probability-weighted, perpetuity</t>
-  </si>
-  <si>
     <t xml:space="preserve">    DCF at the cross-check exit multiple</t>
   </si>
   <si>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">INR cr unless stated</t>
   </si>
   <si>
-    <t xml:space="preserve">Base case inputs  (probability 50%)</t>
+    <t xml:space="preserve">Base case inputs</t>
   </si>
   <si>
     <t xml:space="preserve">    Capex (% sales)</t>
@@ -446,19 +446,16 @@
     <t xml:space="preserve">    Effective tax rate</t>
   </si>
   <si>
-    <t xml:space="preserve">    Probability</t>
-  </si>
-  <si>
     <t xml:space="preserve">The assumption set above as recommended.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bull case inputs  (probability 25%)</t>
+    <t xml:space="preserve">Bull case inputs</t>
   </si>
   <si>
     <t xml:space="preserve">Management delivers close to Ambition 2031: the 1bn-tonne capacity target lands on time, Colombo and Vizhinjam phase 2 ramp faster than modelled, the SEZ tax shield persists longer, and capex comes in at the bottom of the guided range. Mundra concession renewal is granted on existing terms.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bear case inputs  (probability 25%)</t>
+    <t xml:space="preserve">Bear case inputs</t>
   </si>
   <si>
     <t xml:space="preserve">The volume-miss pattern continues and worsens: domestic cargo grows mid single digit rather than high single digit, the international book stays sub-scale at NQXT's lower realisation, and capex overshoots guidance as it did by 65% in FY24 and 33% in FY26. The SEZ tax shield unwinds to statutory. Terminal growth cut to 3.5% to reflect unresolved Mundra concession renewal beyond February 2031.</t>
@@ -467,16 +464,13 @@
     <t xml:space="preserve">Active path  (feeds the Drivers sheet)</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenario values  (INR per share; recorded with the selector at each case)</t>
+    <t xml:space="preserve">Scenario values  (INR per share; recorded with the selector at each case; a range, not weighted)</t>
   </si>
   <si>
     <t xml:space="preserve">Case</t>
   </si>
   <si>
-    <t xml:space="preserve">Prob.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weighted</t>
+    <t xml:space="preserve">Target</t>
   </si>
   <si>
     <t xml:space="preserve">    Base</t>
@@ -488,9 +482,6 @@
     <t xml:space="preserve">    Bear</t>
   </si>
   <si>
-    <t xml:space="preserve">Probability-weighted value</t>
-  </si>
-  <si>
     <t xml:space="preserve">Live value, active case (DCF sheet)</t>
   </si>
   <si>
@@ -1062,6 +1053,96 @@
   </si>
   <si>
     <t xml:space="preserve">WACC  ↓  /  exit EV/EBITDA  →</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adani Ports and Special Economic Zone Ltd - Stress tests (recorded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recorded from stress_test.py on 2026-10-14: each case rebuilds the three-statement model. Not live formulas; re-run the script after changing assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INR/share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak ND/EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min cover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Base case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Capex 20% over plan, every year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    EBITDA margin 3pp lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cargo growth 5pp lower, FY27-FY29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SEZ tax shield ends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Rates 200 bp higher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Combined: capex +20%, growth -5pp, margin -2pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference levels (not disclosed covenants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    net debt ebitda max: 2.5 (management's stated ceiling, not a covenant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambition 2031 deck p.33: Net debt/EBITDA FY26 guidance 2.2x-2.5x (reported 1.9x). On the Q4 FY26 call management said 3.2-3.3x is tolerable only briefly around an acquisition. Loan covenants are not disclosed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interest cover min: 3.0 (house reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA / interest of 3.0x, a common floor for investment-grade infrastructure borrowers; no company-specific covenant is disclosed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two drivers at once: value per share (rows EBITDA margin (pp), columns Revenue growth (pp a year))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+0pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Reverse stress, Uniform cut to revenue growth (pp a year): no breach within -15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Reverse stress, Uniform rise in capex (multiple of plan): breaches at +1.9</t>
   </si>
   <si>
     <t xml:space="preserve">Adani Ports and Special Economic Zone Ltd - Checks</t>
@@ -1098,7 +1179,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
+  <numFmts count="16">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;\(#,##0.0\);\-"/>
@@ -1109,13 +1190,12 @@
     <numFmt numFmtId="171" formatCode="0"/>
     <numFmt numFmtId="172" formatCode="0.00%"/>
     <numFmt numFmtId="173" formatCode="0.00\x"/>
-    <numFmt numFmtId="174" formatCode="0%"/>
-    <numFmt numFmtId="175" formatCode="#,##0.0"/>
-    <numFmt numFmtId="176" formatCode="#,##0.000;\(#,##0.000\)"/>
-    <numFmt numFmtId="177" formatCode="dd\-mmm\-yyyy"/>
-    <numFmt numFmtId="178" formatCode="0.000"/>
-    <numFmt numFmtId="179" formatCode="0.0000"/>
-    <numFmt numFmtId="180" formatCode="0.0\x"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0"/>
+    <numFmt numFmtId="175" formatCode="#,##0.000;\(#,##0.000\)"/>
+    <numFmt numFmtId="176" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="178" formatCode="0.0000"/>
+    <numFmt numFmtId="179" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1547,21 +1627,17 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -1571,19 +1647,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="174" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1639,15 +1711,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1687,15 +1759,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="177" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1703,7 +1775,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1715,19 +1787,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="179" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1904,9 +1984,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$22:$A$28</c:f>
+              <c:f>Dashboard!$A$22:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>    Base case, perpetuity DCF</c:v>
                 </c:pt>
@@ -1917,15 +1997,12 @@
                   <c:v>    Bear case, perpetuity DCF</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>    Probability-weighted, perpetuity</c:v>
+                  <c:v>    DCF at the cross-check exit multiple</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>    DCF at the cross-check exit multiple</c:v>
+                  <c:v>    DCF at the alternative exit multiple</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>    DCF at the alternative exit multiple</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>    Current market price</c:v>
                 </c:pt>
               </c:strCache>
@@ -1933,29 +2010,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$22:$B$28</c:f>
+              <c:f>Dashboard!$B$22:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\(#,##0\)</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>513</c:v>
+                  <c:v>575</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>691</c:v>
+                  <c:v>775</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>217</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>483.5</c:v>
+                  <c:v>1144.63376284308</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1144.63376284308</c:v>
+                  <c:v>1616.01193166881</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1616.01193166881</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>1695</c:v>
                 </c:pt>
               </c:numCache>
@@ -1964,11 +2038,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="40744974"/>
-        <c:axId val="447348"/>
+        <c:axId val="85098675"/>
+        <c:axId val="10175127"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40744974"/>
+        <c:axId val="85098675"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2001,7 +2075,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447348"/>
+        <c:crossAx val="10175127"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2009,7 +2083,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="447348"/>
+        <c:axId val="10175127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2042,7 +2116,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40744974"/>
+        <c:crossAx val="85098675"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2503,7 +2577,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2765,8 +2839,8 @@
         <v>30</v>
       </c>
       <c r="B22" s="17" t="n">
-        <f aca="false">Scenarios!C44</f>
-        <v>513</v>
+        <f aca="false">Scenarios!C41</f>
+        <v>575</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2774,8 +2848,8 @@
         <v>31</v>
       </c>
       <c r="B23" s="17" t="n">
-        <f aca="false">Scenarios!C45</f>
-        <v>691</v>
+        <f aca="false">Scenarios!C42</f>
+        <v>775</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2783,8 +2857,8 @@
         <v>32</v>
       </c>
       <c r="B24" s="17" t="n">
-        <f aca="false">Scenarios!C46</f>
-        <v>217</v>
+        <f aca="false">Scenarios!C43</f>
+        <v>240</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2792,8 +2866,8 @@
         <v>33</v>
       </c>
       <c r="B25" s="17" t="n">
-        <f aca="false">Scenarios!D47</f>
-        <v>483.5</v>
+        <f aca="false">DCF!B68</f>
+        <v>1144.63376284308</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2801,8 +2875,8 @@
         <v>34</v>
       </c>
       <c r="B26" s="17" t="n">
-        <f aca="false">DCF!B68</f>
-        <v>1144.63376284308</v>
+        <f aca="false">DCF!B70</f>
+        <v>1616.01193166881</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2810,22 +2884,13 @@
         <v>35</v>
       </c>
       <c r="B27" s="17" t="n">
-        <f aca="false">DCF!B70</f>
-        <v>1616.01193166881</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="17" t="n">
         <f aca="false">DCF!B46</f>
         <v>1695</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
-        <v>37</v>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2856,12 +2921,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2870,96 +2935,96 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B6" s="41" t="n">
         <v>0.0678</v>
       </c>
-      <c r="C6" s="71" t="s">
-        <v>247</v>
+      <c r="C6" s="69" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B7" s="41" t="n">
         <v>0.055</v>
       </c>
-      <c r="C7" s="71" t="s">
-        <v>249</v>
+      <c r="C7" s="69" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B8" s="72" t="n">
+        <v>246</v>
+      </c>
+      <c r="B8" s="70" t="n">
         <v>1.3</v>
       </c>
-      <c r="C8" s="71" t="s">
-        <v>249</v>
+      <c r="C8" s="69" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B9" s="73" t="n">
+        <v>247</v>
+      </c>
+      <c r="B9" s="71" t="n">
         <f aca="false">0.67*B8+0.33</f>
         <v>1.201</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="B10" s="74" t="n">
+        <v>248</v>
+      </c>
+      <c r="B10" s="72" t="n">
         <f aca="false">B6+B9*B7</f>
         <v>0.133855</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B13" s="41" t="n">
         <v>0.08</v>
       </c>
-      <c r="C13" s="71" t="s">
-        <v>249</v>
+      <c r="C13" s="69" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B14" s="19" t="n">
-        <f aca="false">Scenarios!B39</f>
+        <f aca="false">Scenarios!B36</f>
         <v>0.185</v>
       </c>
-      <c r="C14" s="71" t="s">
-        <v>256</v>
+      <c r="C14" s="69" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B15" s="15" t="n">
         <f aca="false">B13*(1-B14)</f>
@@ -2968,38 +3033,38 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B16" s="41" t="n">
         <v>0.12</v>
       </c>
-      <c r="C16" s="71" t="s">
-        <v>249</v>
+      <c r="C16" s="69" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B18" s="75" t="n">
+        <v>255</v>
+      </c>
+      <c r="B18" s="73" t="n">
         <f aca="false">B10*(1-B16)+B15*B16</f>
         <v>0.1256164</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B19" s="19" t="n">
-        <f aca="false">Scenarios!$B$40</f>
+        <f aca="false">Scenarios!$B$37</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="B20" s="76" t="str">
+        <v>257</v>
+      </c>
+      <c r="B20" s="74" t="str">
         <f aca="false">IF(B19&lt;WACC!$B$18,"OK","FAIL")</f>
         <v>OK</v>
       </c>
@@ -3030,17 +3095,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>6</v>
@@ -3049,18 +3114,18 @@
         <v>7</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3115,7 +3180,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Income Statement'!L12</f>
@@ -3140,7 +3205,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">Drivers!L22</f>
@@ -3165,32 +3230,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="B10" s="52" t="n">
+        <v>261</v>
+      </c>
+      <c r="B10" s="50" t="n">
         <f aca="false">B8*(1-B9)</f>
         <v>16206.9790978603</v>
       </c>
-      <c r="C10" s="52" t="n">
+      <c r="C10" s="50" t="n">
         <f aca="false">C8*(1-C9)</f>
         <v>18581.1712334021</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="50" t="n">
         <f aca="false">D8*(1-D9)</f>
         <v>21594.6517841959</v>
       </c>
-      <c r="E10" s="52" t="n">
+      <c r="E10" s="50" t="n">
         <f aca="false">E8*(1-E9)</f>
         <v>25099.9456785432</v>
       </c>
-      <c r="F10" s="52" t="n">
+      <c r="F10" s="50" t="n">
         <f aca="false">F8*(1-F9)</f>
         <v>28206.1435906259</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">'Income Statement'!L11</f>
@@ -3215,7 +3280,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">-Schedules!L7</f>
@@ -3240,7 +3305,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">-Schedules!L12</f>
@@ -3265,169 +3330,169 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="63" t="n">
+        <v>111</v>
+      </c>
+      <c r="B14" s="61" t="n">
         <f aca="false">B10+B11+B12+B13</f>
         <v>7166.15454188759</v>
       </c>
-      <c r="C14" s="63" t="n">
+      <c r="C14" s="61" t="n">
         <f aca="false">C10+C11+C12+C13</f>
         <v>10227.9759710917</v>
       </c>
-      <c r="D14" s="63" t="n">
+      <c r="D14" s="61" t="n">
         <f aca="false">D10+D11+D12+D13</f>
         <v>11890.0288983426</v>
       </c>
-      <c r="E14" s="63" t="n">
+      <c r="E14" s="61" t="n">
         <f aca="false">E10+E11+E12+E13</f>
         <v>13917.619837016</v>
       </c>
-      <c r="F14" s="63" t="n">
+      <c r="F14" s="61" t="n">
         <f aca="false">F10+F11+F12+F13</f>
         <v>16875.713826288</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="B17" s="77" t="n">
+        <v>266</v>
+      </c>
+      <c r="B17" s="75" t="n">
         <v>46112</v>
       </c>
-      <c r="C17" s="71" t="s">
-        <v>271</v>
+      <c r="C17" s="69" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="B18" s="77" t="n">
+        <v>268</v>
+      </c>
+      <c r="B18" s="75" t="n">
         <v>46477</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="B19" s="77" t="n">
+        <v>269</v>
+      </c>
+      <c r="B19" s="75" t="n">
         <v>46241</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="B20" s="78" t="n">
+        <v>270</v>
+      </c>
+      <c r="B20" s="76" t="n">
         <f aca="false">MIN(1,MAX(0,(B18-B17)/365.25))</f>
         <v>0.999315537303217</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="B21" s="78" t="n">
+        <v>271</v>
+      </c>
+      <c r="B21" s="76" t="n">
         <f aca="false">$B$20</f>
         <v>0.999315537303217</v>
       </c>
-      <c r="C21" s="79" t="n">
+      <c r="C21" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="79" t="n">
+      <c r="D21" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="79" t="n">
+      <c r="E21" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="79" t="n">
+      <c r="F21" s="77" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B22" s="73" t="n">
+        <v>272</v>
+      </c>
+      <c r="B22" s="71" t="n">
         <f aca="false">$B$20*0.5</f>
         <v>0.499657768651609</v>
       </c>
-      <c r="C22" s="73" t="n">
+      <c r="C22" s="71" t="n">
         <f aca="false">$B$20+0.5</f>
         <v>1.49931553730322</v>
       </c>
-      <c r="D22" s="73" t="n">
+      <c r="D22" s="71" t="n">
         <f aca="false">C22+1</f>
         <v>2.49931553730322</v>
       </c>
-      <c r="E22" s="73" t="n">
+      <c r="E22" s="71" t="n">
         <f aca="false">D22+1</f>
         <v>3.49931553730322</v>
       </c>
-      <c r="F22" s="73" t="n">
+      <c r="F22" s="71" t="n">
         <f aca="false">E22+1</f>
         <v>4.49931553730322</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="B23" s="78" t="n">
+        <v>273</v>
+      </c>
+      <c r="B23" s="76" t="n">
         <f aca="false">1/(1+WACC!$B$18)^B22</f>
         <v>0.942589030689347</v>
       </c>
-      <c r="C23" s="78" t="n">
+      <c r="C23" s="76" t="n">
         <f aca="false">1/(1+WACC!$B$18)^C22</f>
         <v>0.837432008832314</v>
       </c>
-      <c r="D23" s="78" t="n">
+      <c r="D23" s="76" t="n">
         <f aca="false">1/(1+WACC!$B$18)^D22</f>
         <v>0.743976374928718</v>
       </c>
-      <c r="E23" s="78" t="n">
+      <c r="E23" s="76" t="n">
         <f aca="false">1/(1+WACC!$B$18)^E22</f>
         <v>0.660950191316259</v>
       </c>
-      <c r="F23" s="78" t="n">
+      <c r="F23" s="76" t="n">
         <f aca="false">1/(1+WACC!$B$18)^F22</f>
         <v>0.587189553489322</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="B24" s="52" t="n">
+        <v>274</v>
+      </c>
+      <c r="B24" s="50" t="n">
         <f aca="false">B14*B21*B23</f>
         <v>6750.11529676626</v>
       </c>
-      <c r="C24" s="52" t="n">
+      <c r="C24" s="50" t="n">
         <f aca="false">C14*C21*C23</f>
         <v>8565.23446375993</v>
       </c>
-      <c r="D24" s="52" t="n">
+      <c r="D24" s="50" t="n">
         <f aca="false">D14*D21*D23</f>
         <v>8845.90059758666</v>
       </c>
-      <c r="E24" s="52" t="n">
+      <c r="E24" s="50" t="n">
         <f aca="false">E14*E21*E23</f>
         <v>9198.85349394267</v>
       </c>
-      <c r="F24" s="52" t="n">
+      <c r="F24" s="50" t="n">
         <f aca="false">F14*F21*F23</f>
         <v>9909.24286647165</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="40" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3441,27 +3506,27 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B28" s="19" t="n">
-        <f aca="false">Scenarios!$B$40</f>
+        <f aca="false">Scenarios!$B$37</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B29" s="41" t="n">
         <v>0.105</v>
       </c>
-      <c r="C29" s="71" t="s">
-        <v>281</v>
+      <c r="C29" s="69" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B30" s="15" t="n">
         <f aca="false">$B$28/$B$29</f>
@@ -3470,36 +3535,36 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="B31" s="52" t="n">
+        <v>279</v>
+      </c>
+      <c r="B31" s="50" t="n">
         <f aca="false">SUM(B24:F24)</f>
         <v>43269.3467185272</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="B32" s="52" t="n">
+        <v>280</v>
+      </c>
+      <c r="B32" s="50" t="n">
         <f aca="false">F10*(1+$B$28)*(1-$B$28/$B$29)/($B$27-$B$28)</f>
         <v>205158.920218951</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="B33" s="52" t="n">
+        <v>281</v>
+      </c>
+      <c r="B33" s="50" t="n">
         <f aca="false">$B$32/(1+$B$27)^F22</f>
         <v>120467.174757717</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B34" s="63" t="n">
+        <v>282</v>
+      </c>
+      <c r="B34" s="61" t="n">
         <f aca="false">$B$31+$B$33</f>
         <v>163736.521476244</v>
       </c>
@@ -3515,60 +3580,60 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="B36" s="80" t="n">
+        <v>283</v>
+      </c>
+      <c r="B36" s="78" t="n">
         <v>42910</v>
       </c>
-      <c r="C36" s="71" t="s">
-        <v>288</v>
+      <c r="C36" s="69" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="B37" s="80" t="n">
+        <v>285</v>
+      </c>
+      <c r="B37" s="78" t="n">
         <v>8296.02</v>
       </c>
-      <c r="C37" s="71" t="s">
-        <v>290</v>
+      <c r="C37" s="69" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="B38" s="80" t="n">
+        <v>287</v>
+      </c>
+      <c r="B38" s="78" t="n">
         <v>2856.18</v>
       </c>
-      <c r="C38" s="71" t="s">
-        <v>292</v>
+      <c r="C38" s="69" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="B39" s="80" t="n">
+        <v>289</v>
+      </c>
+      <c r="B39" s="78" t="n">
         <v>3340.86</v>
       </c>
-      <c r="C39" s="71" t="s">
-        <v>294</v>
+      <c r="C39" s="69" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="B40" s="52" t="n">
+        <v>291</v>
+      </c>
+      <c r="B40" s="50" t="n">
         <f aca="false">$B$34-$B$36-$B$37-$B$38+$B$39</f>
         <v>113015.181476244</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B41" s="19" t="n">
         <f aca="false">WACC!$B$10</f>
@@ -3577,25 +3642,25 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="B42" s="81" t="n">
+        <v>293</v>
+      </c>
+      <c r="B42" s="79" t="n">
         <f aca="false">(1+$B$41)^((B19-B17)/365.25)</f>
         <v>1.0453669726383</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="B43" s="63" t="n">
+        <v>294</v>
+      </c>
+      <c r="B43" s="61" t="n">
         <f aca="false">$B$40*$B$42</f>
         <v>118142.338121989</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B44" s="13" t="n">
         <f aca="false">Schedules!K23</f>
@@ -3604,9 +3669,9 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="B45" s="47" t="n">
+        <v>296</v>
+      </c>
+      <c r="B45" s="46" t="n">
         <f aca="false">$B$43/$B$44</f>
         <v>512.779689751377</v>
       </c>
@@ -3615,16 +3680,16 @@
       <c r="A46" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="82" t="n">
+      <c r="B46" s="80" t="n">
         <v>1695</v>
       </c>
-      <c r="C46" s="71" t="s">
-        <v>301</v>
+      <c r="C46" s="69" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B47" s="15" t="n">
         <f aca="false">$B$45/$B$46-1</f>
@@ -3633,23 +3698,23 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="40" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="B50" s="83" t="s">
-        <v>305</v>
-      </c>
-      <c r="C50" s="71" t="s">
-        <v>306</v>
+        <v>300</v>
+      </c>
+      <c r="B50" s="81" t="s">
+        <v>301</v>
+      </c>
+      <c r="C50" s="69" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B51" s="38" t="n">
         <v>12</v>
@@ -3657,37 +3722,37 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B52" s="46" t="n">
+        <v>304</v>
+      </c>
+      <c r="B52" s="45" t="n">
         <f aca="false">IF($B$50="Exit multiple",$B$68,$B$45)</f>
         <v>512.779689751377</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B53" s="13" t="n">
         <f aca="false">IFERROR(Schedules!L22/Schedules!L23,0)</f>
         <v>8.54922515313609</v>
       </c>
-      <c r="C53" s="71" t="s">
-        <v>310</v>
+      <c r="C53" s="69" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="B54" s="46" t="n">
+        <v>307</v>
+      </c>
+      <c r="B54" s="45" t="n">
         <f aca="false">$B$52*(1+$B$41)^($B$51/12)-$B$53*$B$51/12</f>
         <v>572.868589969911</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B55" s="38" t="n">
         <v>5</v>
@@ -3695,9 +3760,9 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="B56" s="47" t="n">
+        <v>309</v>
+      </c>
+      <c r="B56" s="46" t="n">
         <f aca="false">ROUND($B$54/$B$55,0)*$B$55</f>
         <v>575</v>
       </c>
@@ -3713,29 +3778,29 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B58" s="41" t="n">
         <v>0.15</v>
       </c>
-      <c r="C58" s="71" t="s">
-        <v>315</v>
+      <c r="C58" s="69" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B59" s="41" t="n">
         <v>-0.1</v>
       </c>
-      <c r="C59" s="71" t="s">
-        <v>315</v>
+      <c r="C59" s="69" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B60" s="39" t="str">
         <f aca="false">IF($B$57&gt;$B$58,"BUY",IF($B$57&lt;$B$59,"SELL","HOLD"))</f>
@@ -3744,78 +3809,78 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="40" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="B63" s="52" t="n">
+        <v>315</v>
+      </c>
+      <c r="B63" s="50" t="n">
         <f aca="false">F7</f>
         <v>44232.0557729482</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="B64" s="84" t="n">
+        <v>316</v>
+      </c>
+      <c r="B64" s="82" t="n">
         <f aca="false">$B$32/$B$63</f>
         <v>4.63824067486421</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="B65" s="85" t="n">
+        <v>317</v>
+      </c>
+      <c r="B65" s="83" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="B66" s="52" t="n">
+        <v>318</v>
+      </c>
+      <c r="B66" s="50" t="n">
         <f aca="false">$B$65*$B$63</f>
         <v>442320.557729482</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B67" s="52" t="n">
+        <v>319</v>
+      </c>
+      <c r="B67" s="50" t="n">
         <f aca="false">$B$66/(1+$B$27)^F22</f>
         <v>259726.010792323</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B68" s="47" t="n">
+        <v>320</v>
+      </c>
+      <c r="B68" s="46" t="n">
         <f aca="false">($B$31+$B$67-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
         <v>1144.63376284308</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="B69" s="85" t="n">
+        <v>321</v>
+      </c>
+      <c r="B69" s="83" t="n">
         <v>14</v>
       </c>
-      <c r="C69" s="71" t="s">
-        <v>326</v>
+      <c r="C69" s="69" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="B70" s="46" t="n">
+        <v>323</v>
+      </c>
+      <c r="B70" s="45" t="n">
         <f aca="false">($B$31+$B$69*$B$63/(1+$B$27)^F22-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
         <v>1616.01193166881</v>
       </c>
@@ -3846,17 +3911,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B4" s="41" t="n">
         <v>0.005</v>
@@ -3864,328 +3929,328 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="B5" s="85" t="n">
+        <v>327</v>
+      </c>
+      <c r="B5" s="83" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="B8" s="74" t="n">
+        <v>329</v>
+      </c>
+      <c r="B8" s="72" t="n">
         <f aca="false">DCF!$B$28+(-2)*$B$4</f>
         <v>0.04</v>
       </c>
-      <c r="C8" s="74" t="n">
+      <c r="C8" s="72" t="n">
         <f aca="false">DCF!$B$28+(-1)*$B$4</f>
         <v>0.045</v>
       </c>
-      <c r="D8" s="74" t="n">
+      <c r="D8" s="72" t="n">
         <f aca="false">DCF!$B$28+(0)*$B$4</f>
         <v>0.05</v>
       </c>
-      <c r="E8" s="74" t="n">
+      <c r="E8" s="72" t="n">
         <f aca="false">DCF!$B$28+(1)*$B$4</f>
         <v>0.055</v>
       </c>
-      <c r="F8" s="74" t="n">
+      <c r="F8" s="72" t="n">
         <f aca="false">DCF!$B$28+(2)*$B$4</f>
         <v>0.06</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="75" t="n">
+      <c r="A9" s="73" t="n">
         <f aca="false">DCF!$B$27+(-2)*$B$4</f>
         <v>0.1156164</v>
       </c>
-      <c r="B9" s="46" t="n">
+      <c r="B9" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A9-B$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>636.951049890538</v>
       </c>
-      <c r="C9" s="46" t="n">
+      <c r="C9" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A9-C$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>632.413747405703</v>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="45" t="n">
         <f aca="false">IF(D$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A9-D$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>626.617252338779</v>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="E9" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A9-E$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>619.249967684149</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A9-F$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>609.888244233744</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="75" t="n">
+      <c r="A10" s="73" t="n">
         <f aca="false">DCF!$B$27+(-1)*$B$4</f>
         <v>0.1206164</v>
       </c>
-      <c r="B10" s="46" t="n">
+      <c r="B10" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A10-B$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>580.809643434919</v>
       </c>
-      <c r="C10" s="46" t="n">
+      <c r="C10" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A10-C$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>573.979710054484</v>
       </c>
-      <c r="D10" s="46" t="n">
+      <c r="D10" s="45" t="n">
         <f aca="false">IF(D$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A10-D$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>565.665588926925</v>
       </c>
-      <c r="E10" s="46" t="n">
+      <c r="E10" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A10-E$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>555.527992675812</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A10-F$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>543.115688188434</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="75" t="n">
+      <c r="A11" s="73" t="n">
         <f aca="false">DCF!$B$27+(0)*$B$4</f>
         <v>0.1256164</v>
       </c>
-      <c r="B11" s="46" t="n">
+      <c r="B11" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A11-B$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>531.276875408261</v>
       </c>
-      <c r="C11" s="46" t="n">
+      <c r="C11" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A11-C$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>522.823843890574</v>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="46" t="n">
         <f aca="false">IF(D$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A11-D$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>512.779689751377</v>
       </c>
-      <c r="E11" s="46" t="n">
+      <c r="E11" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A11-E$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>500.806434287101</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A11-F$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>486.463082260638</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="75" t="n">
+      <c r="A12" s="73" t="n">
         <f aca="false">DCF!$B$27+(1)*$B$4</f>
         <v>0.1306164</v>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A12-B$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>487.257658007067</v>
       </c>
-      <c r="C12" s="46" t="n">
+      <c r="C12" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A12-C$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>477.670460418578</v>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="45" t="n">
         <f aca="false">IF(D$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A12-D$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>466.458902463789</v>
       </c>
-      <c r="E12" s="46" t="n">
+      <c r="E12" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A12-E$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>453.300760319635</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A12-F$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>437.782549826056</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="75" t="n">
+      <c r="A13" s="73" t="n">
         <f aca="false">DCF!$B$27+(2)*$B$4</f>
         <v>0.1356164</v>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A13-B$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>447.885992415038</v>
       </c>
-      <c r="C13" s="46" t="n">
+      <c r="C13" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A13-C$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>437.525441123469</v>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="45" t="n">
         <f aca="false">IF(D$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A13-D$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>425.553118514876</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="E13" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A13-E$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>411.66912816923</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A13-F$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
         <v>395.494253196338</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>335</v>
-      </c>
-      <c r="B16" s="86" t="n">
+        <v>331</v>
+      </c>
+      <c r="B16" s="84" t="n">
         <f aca="false">DCF!$B$65+(-2)*$B$5</f>
         <v>6</v>
       </c>
-      <c r="C16" s="86" t="n">
+      <c r="C16" s="84" t="n">
         <f aca="false">DCF!$B$65+(-1)*$B$5</f>
         <v>8</v>
       </c>
-      <c r="D16" s="86" t="n">
+      <c r="D16" s="84" t="n">
         <f aca="false">DCF!$B$65+(0)*$B$5</f>
         <v>10</v>
       </c>
-      <c r="E16" s="86" t="n">
+      <c r="E16" s="84" t="n">
         <f aca="false">DCF!$B$65+(1)*$B$5</f>
         <v>12</v>
       </c>
-      <c r="F16" s="86" t="n">
+      <c r="F16" s="84" t="n">
         <f aca="false">DCF!$B$65+(2)*$B$5</f>
         <v>14</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="75" t="n">
+      <c r="A17" s="73" t="n">
         <f aca="false">DCF!$B$27+(-2)*$B$4</f>
         <v>0.1156164</v>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>706.953796531303</v>
       </c>
-      <c r="C17" s="46" t="n">
+      <c r="C17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>952.298488326392</v>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1197.64318012148</v>
       </c>
-      <c r="E17" s="46" t="n">
+      <c r="E17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1442.98787191657</v>
       </c>
-      <c r="F17" s="46" t="n">
+      <c r="F17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1688.33256371166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="75" t="n">
+      <c r="A18" s="73" t="n">
         <f aca="false">DCF!$B$27+(-1)*$B$4</f>
         <v>0.1206164</v>
       </c>
-      <c r="B18" s="46" t="n">
+      <c r="B18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>689.90384782781</v>
       </c>
-      <c r="C18" s="46" t="n">
+      <c r="C18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>930.361508228743</v>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1170.81916862968</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1411.27682903061</v>
       </c>
-      <c r="F18" s="46" t="n">
+      <c r="F18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1651.73448943154</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="75" t="n">
+      <c r="A19" s="73" t="n">
         <f aca="false">DCF!$B$27+(0)*$B$4</f>
         <v>0.1256164</v>
       </c>
-      <c r="B19" s="46" t="n">
+      <c r="B19" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>673.255594017346</v>
       </c>
-      <c r="C19" s="46" t="n">
+      <c r="C19" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>908.944678430213</v>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="D19" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1144.63376284308</v>
       </c>
-      <c r="E19" s="46" t="n">
+      <c r="E19" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1380.32284725595</v>
       </c>
-      <c r="F19" s="46" t="n">
+      <c r="F19" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1616.01193166881</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="75" t="n">
+      <c r="A20" s="73" t="n">
         <f aca="false">DCF!$B$27+(1)*$B$4</f>
         <v>0.1306164</v>
       </c>
-      <c r="B20" s="46" t="n">
+      <c r="B20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>656.997743702566</v>
       </c>
-      <c r="C20" s="46" t="n">
+      <c r="C20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>888.033329132418</v>
       </c>
-      <c r="D20" s="46" t="n">
+      <c r="D20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1119.06891456227</v>
       </c>
-      <c r="E20" s="46" t="n">
+      <c r="E20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1350.10449999212</v>
       </c>
-      <c r="F20" s="46" t="n">
+      <c r="F20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1581.14008542197</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="75" t="n">
+      <c r="A21" s="73" t="n">
         <f aca="false">DCF!$B$27+(2)*$B$4</f>
         <v>0.1356164</v>
       </c>
-      <c r="B21" s="46" t="n">
+      <c r="B21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>641.119372178411</v>
       </c>
-      <c r="C21" s="46" t="n">
+      <c r="C21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>867.613267921581</v>
       </c>
-      <c r="D21" s="46" t="n">
+      <c r="D21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1094.10716366475</v>
       </c>
-      <c r="E21" s="46" t="n">
+      <c r="E21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1320.60105940792</v>
       </c>
-      <c r="F21" s="46" t="n">
+      <c r="F21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
         <v>1547.09495515109</v>
       </c>
@@ -4207,6 +4272,378 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="45" t="n">
+        <v>513</v>
+      </c>
+      <c r="C5" s="85" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="82" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="F5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="86" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="B6" s="45" t="n">
+        <v>443</v>
+      </c>
+      <c r="C6" s="85" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D6" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="82" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="F6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="86" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7" s="45" t="n">
+        <v>451</v>
+      </c>
+      <c r="C7" s="85" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D7" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="82" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="F7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="86" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="B8" s="45" t="n">
+        <v>415</v>
+      </c>
+      <c r="C8" s="85" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="82" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="F8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="86" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" s="45" t="n">
+        <v>444</v>
+      </c>
+      <c r="C9" s="85" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="82" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="F9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="86" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="45" t="n">
+        <v>362</v>
+      </c>
+      <c r="C10" s="85" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="82" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="F10" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="86" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="45" t="n">
+        <v>316</v>
+      </c>
+      <c r="C11" s="85" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D11" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="82" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="F11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="86" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="40" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="40" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="39" t="s">
+        <v>355</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="39" t="s">
+        <v>355</v>
+      </c>
+      <c r="B19" s="45" t="n">
+        <v>233</v>
+      </c>
+      <c r="C19" s="45" t="n">
+        <v>306</v>
+      </c>
+      <c r="D19" s="45" t="n">
+        <v>388</v>
+      </c>
+      <c r="E19" s="45" t="n">
+        <v>479</v>
+      </c>
+      <c r="F19" s="45" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="B20" s="45" t="n">
+        <v>282</v>
+      </c>
+      <c r="C20" s="45" t="n">
+        <v>362</v>
+      </c>
+      <c r="D20" s="45" t="n">
+        <v>451</v>
+      </c>
+      <c r="E20" s="45" t="n">
+        <v>549</v>
+      </c>
+      <c r="F20" s="45" t="n">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="B21" s="45" t="n">
+        <v>332</v>
+      </c>
+      <c r="C21" s="45" t="n">
+        <v>418</v>
+      </c>
+      <c r="D21" s="45" t="n">
+        <v>513</v>
+      </c>
+      <c r="E21" s="45" t="n">
+        <v>618</v>
+      </c>
+      <c r="F21" s="45" t="n">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="B22" s="45" t="n">
+        <v>382</v>
+      </c>
+      <c r="C22" s="45" t="n">
+        <v>473</v>
+      </c>
+      <c r="D22" s="45" t="n">
+        <v>575</v>
+      </c>
+      <c r="E22" s="45" t="n">
+        <v>687</v>
+      </c>
+      <c r="F22" s="45" t="n">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="39" t="s">
+        <v>359</v>
+      </c>
+      <c r="B23" s="45" t="n">
+        <v>432</v>
+      </c>
+      <c r="C23" s="45" t="n">
+        <v>529</v>
+      </c>
+      <c r="D23" s="45" t="n">
+        <v>637</v>
+      </c>
+      <c r="E23" s="45" t="n">
+        <v>757</v>
+      </c>
+      <c r="F23" s="45" t="n">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>361</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" formatColumns="false" formatRows="false"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4216,44 +4653,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -4265,18 +4702,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -4296,7 +4733,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="B6" s="87" t="n">
         <f aca="false">('Balance Sheet'!B13-'Balance Sheet'!B22)</f>
@@ -4361,7 +4798,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="B7" s="87" t="n">
         <f aca="false">('Balance Sheet'!B6-'Cash Flow'!B23)</f>
@@ -4426,7 +4863,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="B8" s="87" t="n">
         <f aca="false">('Balance Sheet'!B16-(((0+'Income Statement'!B18)-Schedules!B22)+Drivers!B27))</f>
@@ -4491,7 +4928,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="B9" s="87" t="n">
         <f aca="false">('Balance Sheet'!B10-Schedules!B9)</f>
@@ -4556,7 +4993,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -4576,7 +5013,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="B11" s="87" t="n">
         <f aca="false">('Balance Sheet'!B6-Drivers!B29)</f>
@@ -4641,7 +5078,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="B12" s="87" t="n">
         <f aca="false">'Balance Sheet'!B18</f>
@@ -4706,7 +5143,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="B13" s="87" t="n">
         <f aca="false">'Balance Sheet'!B10</f>
@@ -4771,7 +5208,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B14" s="87" t="n">
         <f aca="false">Schedules!B24</f>
@@ -4866,132 +5303,132 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>43</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>47</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="C12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0" t="s">
         <v>55</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="0" t="s">
         <v>57</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>61</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>62</v>
       </c>
       <c r="C16" s="0" t="n">
         <v>22582.9</v>
@@ -5002,38 +5439,38 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0" t="s">
         <v>63</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>4415.24</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>10550.461</v>
@@ -5044,10 +5481,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>0</v>
@@ -5058,10 +5495,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>138607.4628</v>
@@ -5072,10 +5509,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>107697.64</v>
@@ -5086,10 +5523,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>0</v>
@@ -5100,148 +5537,148 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="0" t="s">
         <v>72</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -5270,44 +5707,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -5319,18 +5756,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -5415,7 +5852,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">(IFERROR(('Income Statement'!B6)/(0),0)-1)</f>
@@ -5545,7 +5982,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B10)/('Income Statement'!B6),0)</f>
@@ -5610,7 +6047,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">'Income Statement'!B12</f>
@@ -5740,7 +6177,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B12" s="34" t="n">
         <f aca="false">'Income Statement'!B19</f>
@@ -5805,7 +6242,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
@@ -5825,7 +6262,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B14" s="29" t="n">
         <f aca="false">(((('Income Statement'!B12*(1-Drivers!B22))+'Income Statement'!B11)-Schedules!B7)-Schedules!B12)</f>
@@ -5890,7 +6327,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">(((('Income Statement'!B18+'Income Statement'!B11)-Schedules!B7)-Schedules!B12)+('Balance Sheet'!B19-0))</f>
@@ -5955,7 +6392,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">IFERROR((B14)/('Income Statement'!B10),0)</f>
@@ -6020,7 +6457,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -6040,7 +6477,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">(('Balance Sheet'!B19-'Balance Sheet'!B6)-'Balance Sheet'!B12)</f>
@@ -6105,7 +6542,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B19" s="36" t="n">
         <f aca="false">IFERROR((B18)/('Income Statement'!B10),0)</f>
@@ -6170,7 +6607,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" s="36" t="n">
         <f aca="false">IFERROR(('Income Statement'!B12)/('Income Statement'!B14),0)</f>
@@ -6235,7 +6672,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">((('Balance Sheet'!B15+'Balance Sheet'!B16)+'Balance Sheet'!B19)-'Balance Sheet'!B6)</f>
@@ -6300,7 +6737,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">IFERROR((('Income Statement'!B12*(1-Drivers!B22)))/(AVERAGE(0,B21)),0)</f>
@@ -6365,7 +6802,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B23" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B18)/(AVERAGE(0,Schedules!B24)),0)</f>
@@ -6445,7 +6882,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -6454,17 +6891,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B4" s="38" t="n">
         <v>1</v>
@@ -6472,7 +6909,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B5" s="39" t="str">
         <f aca="false">CHOOSE($B$4,"Base","Bull","Bear")</f>
@@ -6481,7 +6918,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>6</v>
@@ -6490,23 +6927,23 @@
         <v>7</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B9" s="41" t="n">
         <v>0.2139</v>
@@ -6526,7 +6963,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" s="41" t="n">
         <v>0.585</v>
@@ -6546,7 +6983,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="41" t="n">
         <v>0.31</v>
@@ -6566,7 +7003,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" s="41" t="n">
         <v>0.185</v>
@@ -6593,21 +7030,33 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="42" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="42" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="40" t="s">
-        <v>132</v>
+      <c r="A17" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="41" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C17" s="41" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D17" s="41" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E17" s="41" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F17" s="41" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6615,39 +7064,39 @@
         <v>107</v>
       </c>
       <c r="B18" s="41" t="n">
-        <v>0.24</v>
+        <v>0.595</v>
       </c>
       <c r="C18" s="41" t="n">
-        <v>0.16</v>
+        <v>0.595</v>
       </c>
       <c r="D18" s="41" t="n">
-        <v>0.17</v>
+        <v>0.59</v>
       </c>
       <c r="E18" s="41" t="n">
-        <v>0.17</v>
+        <v>0.59</v>
       </c>
       <c r="F18" s="41" t="n">
-        <v>0.15</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>0.595</v>
+        <v>0.3</v>
       </c>
       <c r="C19" s="41" t="n">
-        <v>0.595</v>
+        <v>0.28</v>
       </c>
       <c r="D19" s="41" t="n">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="E19" s="41" t="n">
-        <v>0.59</v>
+        <v>0.25</v>
       </c>
       <c r="F19" s="41" t="n">
-        <v>0.585</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6655,386 +7104,319 @@
         <v>128</v>
       </c>
       <c r="B20" s="41" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="C20" s="41" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="D20" s="41" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="E20" s="41" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="F20" s="41" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="B21" s="41" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="42" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="40" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="41" t="n">
         <v>0.16</v>
       </c>
-      <c r="C21" s="41" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D21" s="41" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E21" s="41" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F21" s="41" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="41" t="n">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B23" s="42" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="43" t="s">
-        <v>133</v>
+      <c r="C25" s="41" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D25" s="41" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E25" s="41" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F25" s="41" t="n">
+        <v>0.07</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="40" t="s">
-        <v>134</v>
+      <c r="A26" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="41" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C26" s="41" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="D26" s="41" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E26" s="41" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F26" s="41" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="C27" s="41" t="n">
-        <v>0.08</v>
+        <v>0.34</v>
       </c>
       <c r="D27" s="41" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="E27" s="41" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="F27" s="41" t="n">
-        <v>0.07</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B28" s="41" t="n">
-        <v>0.57</v>
+        <v>0.23</v>
       </c>
       <c r="C28" s="41" t="n">
-        <v>0.555</v>
+        <v>0.23</v>
       </c>
       <c r="D28" s="41" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="E28" s="41" t="n">
-        <v>0.53</v>
+        <v>0.23</v>
       </c>
       <c r="F28" s="41" t="n">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="C29" s="41" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="D29" s="41" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E29" s="41" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F29" s="41" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="42" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="40" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,B9,B17,B25)</f>
+        <v>0.2139</v>
+      </c>
+      <c r="C33" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,C9,C17,C25)</f>
+        <v>0.1302</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,D9,D17,D25)</f>
+        <v>0.1447</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,E9,E17,E25)</f>
+        <v>0.1481</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,F9,F17,F25)</f>
+        <v>0.1209</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,B10,B18,B26)</f>
+        <v>0.585</v>
+      </c>
+      <c r="C34" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,C10,C18,C26)</f>
+        <v>0.58</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,D10,D18,D26)</f>
+        <v>0.575</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,E10,E18,E26)</f>
+        <v>0.57</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,F10,F18,F26)</f>
+        <v>0.565</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,B11,B19,B27)</f>
+        <v>0.31</v>
+      </c>
+      <c r="C35" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,C11,C19,C27)</f>
         <v>0.3</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="41" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="C30" s="41" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="D30" s="41" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E30" s="41" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F30" s="41" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="41" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B32" s="42" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="43" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="40" t="s">
-        <v>136</v>
+      <c r="D35" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,D11,D19,D27)</f>
+        <v>0.29</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,E11,E19,E27)</f>
+        <v>0.28</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <f aca="false">CHOOSE(Scenarios!$B$4,F11,F19,F27)</f>
+        <v>0.26</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B36" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,B9,B18,B27)</f>
-        <v>0.2139</v>
+        <f aca="false">CHOOSE(Scenarios!$B$4,B12,B20,B28)</f>
+        <v>0.185</v>
       </c>
       <c r="C36" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,C9,C18,C27)</f>
-        <v>0.1302</v>
+        <f aca="false">CHOOSE(Scenarios!$B$4,C12,C20,C28)</f>
+        <v>0.185</v>
       </c>
       <c r="D36" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,D9,D18,D27)</f>
-        <v>0.1447</v>
+        <f aca="false">CHOOSE(Scenarios!$B$4,D12,D20,D28)</f>
+        <v>0.185</v>
       </c>
       <c r="E36" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,E9,E18,E27)</f>
-        <v>0.1481</v>
+        <f aca="false">CHOOSE(Scenarios!$B$4,E12,E20,E28)</f>
+        <v>0.185</v>
       </c>
       <c r="F36" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,F9,F18,F27)</f>
-        <v>0.1209</v>
+        <f aca="false">CHOOSE(Scenarios!$B$4,F12,F20,F28)</f>
+        <v>0.185</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="B37" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,B10,B19,B28)</f>
-        <v>0.585</v>
-      </c>
-      <c r="C37" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,C10,C19,C28)</f>
-        <v>0.58</v>
-      </c>
-      <c r="D37" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,D10,D19,D28)</f>
-        <v>0.575</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,E10,E19,E28)</f>
-        <v>0.57</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,F10,F19,F28)</f>
-        <v>0.565</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B38" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,B11,B20,B29)</f>
-        <v>0.31</v>
-      </c>
-      <c r="C38" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,C11,C20,C29)</f>
-        <v>0.3</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,D11,D20,D29)</f>
-        <v>0.29</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,E11,E20,E29)</f>
-        <v>0.28</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,F11,F20,F29)</f>
-        <v>0.26</v>
+        <f aca="false">CHOOSE(Scenarios!$B$4,B13,B21,B29)</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B39" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,B12,B21,B30)</f>
-        <v>0.185</v>
-      </c>
-      <c r="C39" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,C12,C21,C30)</f>
-        <v>0.185</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,D12,D21,D30)</f>
-        <v>0.185</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,E12,E21,E30)</f>
-        <v>0.185</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,F12,F21,F30)</f>
-        <v>0.185</v>
+      <c r="A39" s="40" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" s="15" t="n">
-        <f aca="false">CHOOSE(Scenarios!$B$4,B13,B22,B31)</f>
-        <v>0.05</v>
+      <c r="A40" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" s="43" t="n">
+        <v>513</v>
+      </c>
+      <c r="C41" s="43" t="n">
+        <v>575</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="40" t="s">
-        <v>137</v>
+      <c r="A42" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" s="43" t="n">
+        <v>691</v>
+      </c>
+      <c r="C42" s="43" t="n">
+        <v>775</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="A43" s="8" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B44" s="44" t="n">
-        <f aca="false">B14</f>
-        <v>0.5</v>
-      </c>
-      <c r="C44" s="45" t="n">
-        <v>513</v>
-      </c>
-      <c r="D44" s="46" t="n">
-        <f aca="false">B44*C44</f>
-        <v>256.5</v>
+      <c r="B43" s="43" t="n">
+        <v>217</v>
+      </c>
+      <c r="C43" s="43" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B45" s="44" t="n">
-        <f aca="false">B23</f>
-        <v>0.25</v>
-      </c>
-      <c r="C45" s="45" t="n">
-        <v>691</v>
-      </c>
-      <c r="D45" s="46" t="n">
-        <f aca="false">B45*C45</f>
-        <v>172.75</v>
+        <f aca="false">DCF!B45</f>
+        <v>512.779689751377</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B46" s="44" t="n">
-        <f aca="false">B32</f>
-        <v>0.25</v>
-      </c>
-      <c r="C46" s="45" t="n">
-        <v>217</v>
-      </c>
-      <c r="D46" s="46" t="n">
-        <f aca="false">B46*C46</f>
-        <v>54.25</v>
+        <v>142</v>
+      </c>
+      <c r="B46" s="45" t="n">
+        <f aca="false">INDEX(B41:B43,Scenarios!$B$4)</f>
+        <v>513</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B47" s="44" t="n">
-        <f aca="false">SUM(B44:B46)</f>
-        <v>1</v>
-      </c>
-      <c r="D47" s="47" t="n">
-        <f aca="false">SUM(D44:D46)</f>
-        <v>483.5</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B49" s="48" t="n">
-        <f aca="false">DCF!B45</f>
-        <v>512.779689751377</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B50" s="46" t="n">
-        <f aca="false">INDEX(C44:C46,Scenarios!$B$4)</f>
-        <v>513</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B51" s="47" t="n">
-        <f aca="false">ROUND(B49,0)-B50</f>
+        <v>143</v>
+      </c>
+      <c r="B47" s="46" t="n">
+        <f aca="false">ROUND(B45,0)-B46</f>
         <v>0</v>
       </c>
     </row>
@@ -7070,44 +7452,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -7119,18 +7501,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -7150,7 +7532,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" s="19" t="n">
         <f aca="false">(IFERROR(('Income Statement'!B6)/(0),0)-1)</f>
@@ -7193,29 +7575,29 @@
         <v>0.271053340521661</v>
       </c>
       <c r="L6" s="19" t="n">
-        <f aca="false">Scenarios!B36</f>
+        <f aca="false">Scenarios!B33</f>
         <v>0.2139</v>
       </c>
       <c r="M6" s="19" t="n">
-        <f aca="false">Scenarios!C36</f>
+        <f aca="false">Scenarios!C33</f>
         <v>0.1302</v>
       </c>
       <c r="N6" s="19" t="n">
-        <f aca="false">Scenarios!D36</f>
+        <f aca="false">Scenarios!D33</f>
         <v>0.1447</v>
       </c>
       <c r="O6" s="19" t="n">
-        <f aca="false">Scenarios!E36</f>
+        <f aca="false">Scenarios!E33</f>
         <v>0.1481</v>
       </c>
       <c r="P6" s="19" t="n">
-        <f aca="false">Scenarios!F36</f>
+        <f aca="false">Scenarios!F33</f>
         <v>0.1209</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B8)/('Income Statement'!B6),0)</f>
@@ -7257,25 +7639,25 @@
         <f aca="false">IFERROR(('Income Statement'!K8)/('Income Statement'!K6),0)</f>
         <v>0.702267955432408</v>
       </c>
-      <c r="L7" s="49" t="n">
+      <c r="L7" s="47" t="n">
         <v>0.702</v>
       </c>
-      <c r="M7" s="49" t="n">
+      <c r="M7" s="47" t="n">
         <v>0.702</v>
       </c>
-      <c r="N7" s="49" t="n">
+      <c r="N7" s="47" t="n">
         <v>0.702</v>
       </c>
-      <c r="O7" s="49" t="n">
+      <c r="O7" s="47" t="n">
         <v>0.702</v>
       </c>
-      <c r="P7" s="49" t="n">
+      <c r="P7" s="47" t="n">
         <v>0.702</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B10)/('Income Statement'!B6),0)</f>
@@ -7318,29 +7700,29 @@
         <v>0.590363635471813</v>
       </c>
       <c r="L8" s="19" t="n">
-        <f aca="false">Scenarios!B37</f>
+        <f aca="false">Scenarios!B34</f>
         <v>0.585</v>
       </c>
       <c r="M8" s="19" t="n">
-        <f aca="false">Scenarios!C37</f>
+        <f aca="false">Scenarios!C34</f>
         <v>0.58</v>
       </c>
       <c r="N8" s="19" t="n">
-        <f aca="false">Scenarios!D37</f>
+        <f aca="false">Scenarios!D34</f>
         <v>0.575</v>
       </c>
       <c r="O8" s="19" t="n">
-        <f aca="false">Scenarios!E37</f>
+        <f aca="false">Scenarios!E34</f>
         <v>0.57</v>
       </c>
       <c r="P8" s="19" t="n">
-        <f aca="false">Scenarios!F37</f>
+        <f aca="false">Scenarios!F34</f>
         <v>0.565</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B13)/('Income Statement'!B6),0)</f>
@@ -7382,25 +7764,25 @@
         <f aca="false">IFERROR(('Income Statement'!K13)/('Income Statement'!K6),0)</f>
         <v>0.0555489151241863</v>
       </c>
-      <c r="L9" s="49" t="n">
+      <c r="L9" s="47" t="n">
         <v>0.046571</v>
       </c>
-      <c r="M9" s="49" t="n">
+      <c r="M9" s="47" t="n">
         <v>0.046571</v>
       </c>
-      <c r="N9" s="49" t="n">
+      <c r="N9" s="47" t="n">
         <v>0.046571</v>
       </c>
-      <c r="O9" s="49" t="n">
+      <c r="O9" s="47" t="n">
         <v>0.046571</v>
       </c>
-      <c r="P9" s="49" t="n">
+      <c r="P9" s="47" t="n">
         <v>0.046571</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -7420,7 +7802,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">IFERROR((Schedules!B7)/('Income Statement'!B6),0)</f>
@@ -7463,29 +7845,29 @@
         <v>1.22763946605424</v>
       </c>
       <c r="L11" s="19" t="n">
-        <f aca="false">Scenarios!B38</f>
+        <f aca="false">Scenarios!B35</f>
         <v>0.31</v>
       </c>
       <c r="M11" s="19" t="n">
-        <f aca="false">Scenarios!C38</f>
+        <f aca="false">Scenarios!C35</f>
         <v>0.3</v>
       </c>
       <c r="N11" s="19" t="n">
-        <f aca="false">Scenarios!D38</f>
+        <f aca="false">Scenarios!D35</f>
         <v>0.29</v>
       </c>
       <c r="O11" s="19" t="n">
-        <f aca="false">Scenarios!E38</f>
+        <f aca="false">Scenarios!E35</f>
         <v>0.28</v>
       </c>
       <c r="P11" s="19" t="n">
-        <f aca="false">Scenarios!F38</f>
+        <f aca="false">Scenarios!F35</f>
         <v>0.26</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B12" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B11)/(0),0)</f>
@@ -7527,25 +7909,25 @@
         <f aca="false">IFERROR(('Income Statement'!K11)/('Balance Sheet'!J10),0)</f>
         <v>0.0615666878532839</v>
       </c>
-      <c r="L12" s="49" t="n">
+      <c r="L12" s="47" t="n">
         <v>0.057892</v>
       </c>
-      <c r="M12" s="49" t="n">
+      <c r="M12" s="47" t="n">
         <v>0.057892</v>
       </c>
-      <c r="N12" s="49" t="n">
+      <c r="N12" s="47" t="n">
         <v>0.057892</v>
       </c>
-      <c r="O12" s="49" t="n">
+      <c r="O12" s="47" t="n">
         <v>0.057892</v>
       </c>
-      <c r="P12" s="49" t="n">
+      <c r="P12" s="47" t="n">
         <v>0.057892</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B13" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B11)/('Income Statement'!B6),0)</f>
@@ -7587,25 +7969,25 @@
         <f aca="false">IFERROR(('Income Statement'!K11)/('Income Statement'!K6),0)</f>
         <v>0.142436306287444</v>
       </c>
-      <c r="L13" s="49" t="n">
+      <c r="L13" s="47" t="n">
         <v>0.145</v>
       </c>
-      <c r="M13" s="49" t="n">
+      <c r="M13" s="47" t="n">
         <v>0.145</v>
       </c>
-      <c r="N13" s="49" t="n">
+      <c r="N13" s="47" t="n">
         <v>0.148</v>
       </c>
-      <c r="O13" s="49" t="n">
+      <c r="O13" s="47" t="n">
         <v>0.15</v>
       </c>
-      <c r="P13" s="49" t="n">
+      <c r="P13" s="47" t="n">
         <v>0.152</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!B11)/('Income Statement'!B6),0)</f>
@@ -7647,25 +8029,25 @@
         <f aca="false">IFERROR(('Balance Sheet'!K11)/('Income Statement'!K6),0)</f>
         <v>0.327579650540056</v>
       </c>
-      <c r="L14" s="49" t="n">
+      <c r="L14" s="47" t="n">
         <v>0.373709</v>
       </c>
-      <c r="M14" s="49" t="n">
+      <c r="M14" s="47" t="n">
         <v>0.373709</v>
       </c>
-      <c r="N14" s="49" t="n">
+      <c r="N14" s="47" t="n">
         <v>0.373709</v>
       </c>
-      <c r="O14" s="49" t="n">
+      <c r="O14" s="47" t="n">
         <v>0.373709</v>
       </c>
-      <c r="P14" s="49" t="n">
+      <c r="P14" s="47" t="n">
         <v>0.373709</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B15" s="28"/>
       <c r="C15" s="28"/>
@@ -7685,187 +8067,187 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="50" t="n">
+        <v>153</v>
+      </c>
+      <c r="B16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B7)/('Income Statement'!B6),0)*365)</f>
         <v>116.471215200223</v>
       </c>
-      <c r="C16" s="50" t="n">
+      <c r="C16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!C7)/('Income Statement'!C6),0)*365)</f>
         <v>138.931617704205</v>
       </c>
-      <c r="D16" s="50" t="n">
+      <c r="D16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!D7)/('Income Statement'!D6),0)*365)</f>
         <v>93.197701877453</v>
       </c>
-      <c r="E16" s="50" t="n">
+      <c r="E16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!E7)/('Income Statement'!E6),0)*365)</f>
         <v>98.4396706159401</v>
       </c>
-      <c r="F16" s="50" t="n">
+      <c r="F16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!F7)/('Income Statement'!F6),0)*365)</f>
         <v>85.0930826480525</v>
       </c>
-      <c r="G16" s="50" t="n">
+      <c r="G16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!G7)/('Income Statement'!G6),0)*365)</f>
         <v>53.754739674942</v>
       </c>
-      <c r="H16" s="50" t="n">
+      <c r="H16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!H7)/('Income Statement'!H6),0)*365)</f>
         <v>69.2661032010977</v>
       </c>
-      <c r="I16" s="50" t="n">
+      <c r="I16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!I7)/('Income Statement'!I6),0)*365)</f>
         <v>50.1087622273737</v>
       </c>
-      <c r="J16" s="50" t="n">
+      <c r="J16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!J7)/('Income Statement'!J6),0)*365)</f>
         <v>53.0859354107076</v>
       </c>
-      <c r="K16" s="50" t="n">
+      <c r="K16" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!K7)/('Income Statement'!K6),0)*365)</f>
         <v>60.1414945410921</v>
       </c>
-      <c r="L16" s="51" t="n">
+      <c r="L16" s="49" t="n">
         <v>58</v>
       </c>
-      <c r="M16" s="51" t="n">
+      <c r="M16" s="49" t="n">
         <v>58</v>
       </c>
-      <c r="N16" s="51" t="n">
+      <c r="N16" s="49" t="n">
         <v>58</v>
       </c>
-      <c r="O16" s="51" t="n">
+      <c r="O16" s="49" t="n">
         <v>58</v>
       </c>
-      <c r="P16" s="51" t="n">
+      <c r="P16" s="49" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="50" t="n">
+        <v>154</v>
+      </c>
+      <c r="B17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B8)/('Income Statement'!B7),0)*365)</f>
         <v>108.173939516947</v>
       </c>
-      <c r="C17" s="50" t="n">
+      <c r="C17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!C8)/('Income Statement'!C7),0)*365)</f>
         <v>57.7997948611813</v>
       </c>
-      <c r="D17" s="50" t="n">
+      <c r="D17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!D8)/('Income Statement'!D7),0)*365)</f>
         <v>104.331165955034</v>
       </c>
-      <c r="E17" s="50" t="n">
+      <c r="E17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!E8)/('Income Statement'!E7),0)*365)</f>
         <v>33.2265592188985</v>
       </c>
-      <c r="F17" s="50" t="n">
+      <c r="F17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!F8)/('Income Statement'!F7),0)*365)</f>
         <v>108.732617510137</v>
       </c>
-      <c r="G17" s="50" t="n">
+      <c r="G17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!G8)/('Income Statement'!G7),0)*365)</f>
         <v>29.1939197781071</v>
       </c>
-      <c r="H17" s="50" t="n">
+      <c r="H17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!H8)/('Income Statement'!H7),0)*365)</f>
         <v>28.6022244568892</v>
       </c>
-      <c r="I17" s="50" t="n">
+      <c r="I17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!I8)/('Income Statement'!I7),0)*365)</f>
         <v>21.945846961493</v>
       </c>
-      <c r="J17" s="50" t="n">
+      <c r="J17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!J8)/('Income Statement'!J7),0)*365)</f>
         <v>23.0269990557403</v>
       </c>
-      <c r="K17" s="50" t="n">
+      <c r="K17" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!K8)/('Income Statement'!K7),0)*365)</f>
         <v>21.6793203432274</v>
       </c>
-      <c r="L17" s="51" t="n">
+      <c r="L17" s="49" t="n">
         <v>21.7</v>
       </c>
-      <c r="M17" s="51" t="n">
+      <c r="M17" s="49" t="n">
         <v>21.7</v>
       </c>
-      <c r="N17" s="51" t="n">
+      <c r="N17" s="49" t="n">
         <v>21.7</v>
       </c>
-      <c r="O17" s="51" t="n">
+      <c r="O17" s="49" t="n">
         <v>21.7</v>
       </c>
-      <c r="P17" s="51" t="n">
+      <c r="P17" s="49" t="n">
         <v>21.7</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B18" s="50" t="n">
+        <v>155</v>
+      </c>
+      <c r="B18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B20)/('Income Statement'!B7),0)*365)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="50" t="n">
+      <c r="C18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!C20)/('Income Statement'!C7),0)*365)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="50" t="n">
+      <c r="D18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!D20)/('Income Statement'!D7),0)*365)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="50" t="n">
+      <c r="E18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!E20)/('Income Statement'!E7),0)*365)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="50" t="n">
+      <c r="F18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!F20)/('Income Statement'!F7),0)*365)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="50" t="n">
+      <c r="G18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!G20)/('Income Statement'!G7),0)*365)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="50" t="n">
+      <c r="H18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!H20)/('Income Statement'!H7),0)*365)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="50" t="n">
+      <c r="I18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!I20)/('Income Statement'!I7),0)*365)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="50" t="n">
+      <c r="J18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!J20)/('Income Statement'!J7),0)*365)</f>
         <v>120.055482811693</v>
       </c>
-      <c r="K18" s="50" t="n">
+      <c r="K18" s="48" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!K20)/('Income Statement'!K7),0)*365)</f>
         <v>86.598282475843</v>
       </c>
-      <c r="L18" s="51" t="n">
+      <c r="L18" s="49" t="n">
         <v>86.6</v>
       </c>
-      <c r="M18" s="51" t="n">
+      <c r="M18" s="49" t="n">
         <v>86.6</v>
       </c>
-      <c r="N18" s="51" t="n">
+      <c r="N18" s="49" t="n">
         <v>86.6</v>
       </c>
-      <c r="O18" s="51" t="n">
+      <c r="O18" s="49" t="n">
         <v>86.6</v>
       </c>
-      <c r="P18" s="51" t="n">
+      <c r="P18" s="49" t="n">
         <v>86.6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B19" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!B9)/('Income Statement'!B6),0)</f>
@@ -7907,25 +8289,25 @@
         <f aca="false">IFERROR(('Balance Sheet'!K9)/('Income Statement'!K6),0)</f>
         <v>0.458420731019417</v>
       </c>
-      <c r="L19" s="49" t="n">
+      <c r="L19" s="47" t="n">
         <v>0.512548</v>
       </c>
-      <c r="M19" s="49" t="n">
+      <c r="M19" s="47" t="n">
         <v>0.512548</v>
       </c>
-      <c r="N19" s="49" t="n">
+      <c r="N19" s="47" t="n">
         <v>0.512548</v>
       </c>
-      <c r="O19" s="49" t="n">
+      <c r="O19" s="47" t="n">
         <v>0.512548</v>
       </c>
-      <c r="P19" s="49" t="n">
+      <c r="P19" s="47" t="n">
         <v>0.512548</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B20" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!B21)/('Income Statement'!B6),0)</f>
@@ -7967,25 +8349,25 @@
         <f aca="false">IFERROR(('Balance Sheet'!K21)/('Income Statement'!K6),0)</f>
         <v>0.537952388709454</v>
       </c>
-      <c r="L20" s="49" t="n">
+      <c r="L20" s="47" t="n">
         <v>0.54751</v>
       </c>
-      <c r="M20" s="49" t="n">
+      <c r="M20" s="47" t="n">
         <v>0.54751</v>
       </c>
-      <c r="N20" s="49" t="n">
+      <c r="N20" s="47" t="n">
         <v>0.54751</v>
       </c>
-      <c r="O20" s="49" t="n">
+      <c r="O20" s="47" t="n">
         <v>0.54751</v>
       </c>
-      <c r="P20" s="49" t="n">
+      <c r="P20" s="47" t="n">
         <v>0.54751</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
@@ -8005,7 +8387,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B17)/('Income Statement'!B16),0)</f>
@@ -8048,29 +8430,29 @@
         <v>0.1375453242604</v>
       </c>
       <c r="L22" s="19" t="n">
-        <f aca="false">Scenarios!B39</f>
+        <f aca="false">Scenarios!B36</f>
         <v>0.185</v>
       </c>
       <c r="M22" s="19" t="n">
-        <f aca="false">Scenarios!C39</f>
+        <f aca="false">Scenarios!C36</f>
         <v>0.185</v>
       </c>
       <c r="N22" s="19" t="n">
-        <f aca="false">Scenarios!D39</f>
+        <f aca="false">Scenarios!D36</f>
         <v>0.185</v>
       </c>
       <c r="O22" s="19" t="n">
-        <f aca="false">Scenarios!E39</f>
+        <f aca="false">Scenarios!E36</f>
         <v>0.185</v>
       </c>
       <c r="P22" s="19" t="n">
-        <f aca="false">Scenarios!F39</f>
+        <f aca="false">Scenarios!F36</f>
         <v>0.185</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B23" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B14)/(AVERAGE(0,'Balance Sheet'!B19)),0)</f>
@@ -8112,25 +8494,25 @@
         <f aca="false">IFERROR(('Income Statement'!K14)/(AVERAGE('Balance Sheet'!J19,'Balance Sheet'!K19)),0)</f>
         <v>0.0808079089301023</v>
       </c>
-      <c r="L23" s="49" t="n">
+      <c r="L23" s="47" t="n">
         <v>0.08</v>
       </c>
-      <c r="M23" s="49" t="n">
+      <c r="M23" s="47" t="n">
         <v>0.08</v>
       </c>
-      <c r="N23" s="49" t="n">
+      <c r="N23" s="47" t="n">
         <v>0.08</v>
       </c>
-      <c r="O23" s="49" t="n">
+      <c r="O23" s="47" t="n">
         <v>0.08</v>
       </c>
-      <c r="P23" s="49" t="n">
+      <c r="P23" s="47" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B24" s="15" t="n">
         <f aca="false">0</f>
@@ -8172,25 +8554,25 @@
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="L24" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="49" t="n">
+      <c r="L24" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B25" s="19" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B17)/(0),0)-1)</f>
@@ -8232,145 +8614,145 @@
         <f aca="false">(IFERROR(('Balance Sheet'!K17)/('Balance Sheet'!J17),0)-1)</f>
         <v>0.231395216611621</v>
       </c>
-      <c r="L25" s="49" t="n">
+      <c r="L25" s="47" t="n">
         <v>0.066894</v>
       </c>
-      <c r="M25" s="49" t="n">
+      <c r="M25" s="47" t="n">
         <v>0.066894</v>
       </c>
-      <c r="N25" s="49" t="n">
+      <c r="N25" s="47" t="n">
         <v>0.066894</v>
       </c>
-      <c r="O25" s="49" t="n">
+      <c r="O25" s="47" t="n">
         <v>0.066894</v>
       </c>
-      <c r="P25" s="49" t="n">
+      <c r="P25" s="47" t="n">
         <v>0.066894</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26" s="52" t="n">
+        <v>162</v>
+      </c>
+      <c r="B26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C26" s="52" t="n">
+      <c r="C26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="D26" s="52" t="n">
+      <c r="D26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="E26" s="52" t="n">
+      <c r="E26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="F26" s="52" t="n">
+      <c r="F26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G26" s="52" t="n">
+      <c r="G26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="H26" s="52" t="n">
+      <c r="H26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="I26" s="52" t="n">
+      <c r="I26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="J26" s="52" t="n">
+      <c r="J26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="K26" s="52" t="n">
+      <c r="K26" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="L26" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="53" t="n">
+      <c r="L26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="B27" s="52" t="n">
+        <v>163</v>
+      </c>
+      <c r="B27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C27" s="52" t="n">
+      <c r="C27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="D27" s="52" t="n">
+      <c r="D27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="E27" s="52" t="n">
+      <c r="E27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="F27" s="52" t="n">
+      <c r="F27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G27" s="52" t="n">
+      <c r="G27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="H27" s="52" t="n">
+      <c r="H27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="I27" s="52" t="n">
+      <c r="I27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="J27" s="52" t="n">
+      <c r="J27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="K27" s="52" t="n">
+      <c r="K27" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="L27" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="53" t="n">
+      <c r="L27" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B28" s="19" t="n">
         <f aca="false">IFERROR((Schedules!B22)/('Income Statement'!B18),0)</f>
@@ -8412,79 +8794,79 @@
         <f aca="false">IFERROR((Schedules!K22)/('Income Statement'!K18),0)</f>
         <v>0.134931412182059</v>
       </c>
-      <c r="L28" s="49" t="n">
+      <c r="L28" s="47" t="n">
         <v>0.143684</v>
       </c>
-      <c r="M28" s="49" t="n">
+      <c r="M28" s="47" t="n">
         <v>0.143684</v>
       </c>
-      <c r="N28" s="49" t="n">
+      <c r="N28" s="47" t="n">
         <v>0.143684</v>
       </c>
-      <c r="O28" s="49" t="n">
+      <c r="O28" s="47" t="n">
         <v>0.143684</v>
       </c>
-      <c r="P28" s="49" t="n">
+      <c r="P28" s="47" t="n">
         <v>0.143684</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="B29" s="52" t="n">
+        <v>165</v>
+      </c>
+      <c r="B29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C29" s="52" t="n">
+      <c r="C29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="D29" s="52" t="n">
+      <c r="D29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="E29" s="52" t="n">
+      <c r="E29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="F29" s="52" t="n">
+      <c r="F29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G29" s="52" t="n">
+      <c r="G29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="H29" s="52" t="n">
+      <c r="H29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="I29" s="52" t="n">
+      <c r="I29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="J29" s="52" t="n">
+      <c r="J29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="K29" s="52" t="n">
+      <c r="K29" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="L29" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="53" t="n">
+      <c r="L29" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8514,44 +8896,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -8563,18 +8945,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -8596,34 +8978,34 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="54" t="n">
+      <c r="B6" s="52" t="n">
         <v>8439.35</v>
       </c>
-      <c r="C6" s="54" t="n">
+      <c r="C6" s="52" t="n">
         <v>11322.96</v>
       </c>
-      <c r="D6" s="54" t="n">
+      <c r="D6" s="52" t="n">
         <v>10925.44</v>
       </c>
-      <c r="E6" s="54" t="n">
+      <c r="E6" s="52" t="n">
         <v>11873.07</v>
       </c>
-      <c r="F6" s="54" t="n">
+      <c r="F6" s="52" t="n">
         <v>12549.6</v>
       </c>
-      <c r="G6" s="54" t="n">
+      <c r="G6" s="52" t="n">
         <v>17118.79</v>
       </c>
-      <c r="H6" s="54" t="n">
+      <c r="H6" s="52" t="n">
         <v>20851.91</v>
       </c>
-      <c r="I6" s="54" t="n">
+      <c r="I6" s="52" t="n">
         <v>26710.56</v>
       </c>
-      <c r="J6" s="54" t="n">
+      <c r="J6" s="52" t="n">
         <v>30475.33</v>
       </c>
-      <c r="K6" s="54" t="n">
+      <c r="K6" s="52" t="n">
         <v>38735.77</v>
       </c>
       <c r="L6" s="30" t="n">
@@ -8649,36 +9031,36 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="55" t="n">
+        <v>168</v>
+      </c>
+      <c r="B7" s="53" t="n">
         <v>2217.15</v>
       </c>
-      <c r="C7" s="55" t="n">
+      <c r="C7" s="53" t="n">
         <v>3285.58</v>
       </c>
-      <c r="D7" s="55" t="n">
+      <c r="D7" s="53" t="n">
         <v>2822.15</v>
       </c>
-      <c r="E7" s="55" t="n">
+      <c r="E7" s="53" t="n">
         <v>3166.81</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="53" t="n">
         <v>3329.5</v>
       </c>
-      <c r="G7" s="55" t="n">
+      <c r="G7" s="53" t="n">
         <v>4946.53</v>
       </c>
-      <c r="H7" s="55" t="n">
+      <c r="H7" s="53" t="n">
         <v>5767.7</v>
       </c>
-      <c r="I7" s="55" t="n">
+      <c r="I7" s="53" t="n">
         <v>7276.6</v>
       </c>
-      <c r="J7" s="55" t="n">
+      <c r="J7" s="53" t="n">
         <v>8271.03</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="53" t="n">
         <v>11532.88</v>
       </c>
       <c r="L7" s="33" t="n">
@@ -8704,130 +9086,130 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="56" t="n">
+        <v>169</v>
+      </c>
+      <c r="B8" s="54" t="n">
         <f aca="false">(B6-B7)</f>
         <v>6222.2</v>
       </c>
-      <c r="C8" s="56" t="n">
+      <c r="C8" s="54" t="n">
         <f aca="false">(C6-C7)</f>
         <v>8037.38</v>
       </c>
-      <c r="D8" s="56" t="n">
+      <c r="D8" s="54" t="n">
         <f aca="false">(D6-D7)</f>
         <v>8103.29</v>
       </c>
-      <c r="E8" s="56" t="n">
+      <c r="E8" s="54" t="n">
         <f aca="false">(E6-E7)</f>
         <v>8706.26</v>
       </c>
-      <c r="F8" s="56" t="n">
+      <c r="F8" s="54" t="n">
         <f aca="false">(F6-F7)</f>
         <v>9220.1</v>
       </c>
-      <c r="G8" s="56" t="n">
+      <c r="G8" s="54" t="n">
         <f aca="false">(G6-G7)</f>
         <v>12172.26</v>
       </c>
-      <c r="H8" s="56" t="n">
+      <c r="H8" s="54" t="n">
         <f aca="false">(H6-H7)</f>
         <v>15084.21</v>
       </c>
-      <c r="I8" s="56" t="n">
+      <c r="I8" s="54" t="n">
         <f aca="false">(I6-I7)</f>
         <v>19433.96</v>
       </c>
-      <c r="J8" s="56" t="n">
+      <c r="J8" s="54" t="n">
         <f aca="false">(J6-J7)</f>
         <v>22204.3</v>
       </c>
-      <c r="K8" s="56" t="n">
+      <c r="K8" s="54" t="n">
         <f aca="false">(K6-K7)</f>
         <v>27202.89</v>
       </c>
-      <c r="L8" s="57" t="n">
+      <c r="L8" s="55" t="n">
         <f aca="false">(L6-L7)</f>
         <v>33008.988544506</v>
       </c>
-      <c r="M8" s="57" t="n">
+      <c r="M8" s="55" t="n">
         <f aca="false">(M6-M7)</f>
         <v>37306.7588530007</v>
       </c>
-      <c r="N8" s="57" t="n">
+      <c r="N8" s="55" t="n">
         <f aca="false">(N6-N7)</f>
         <v>42705.0468590299</v>
       </c>
-      <c r="O8" s="57" t="n">
+      <c r="O8" s="55" t="n">
         <f aca="false">(O6-O7)</f>
         <v>49029.6642988522</v>
       </c>
-      <c r="P8" s="57" t="n">
+      <c r="P8" s="55" t="n">
         <f aca="false">(P6-P7)</f>
         <v>54957.3507125834</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="B9" s="52" t="n">
+        <v>170</v>
+      </c>
+      <c r="B9" s="50" t="n">
         <f aca="false">(B8-B10)</f>
         <v>803.970000000001</v>
       </c>
-      <c r="C9" s="52" t="n">
+      <c r="C9" s="50" t="n">
         <f aca="false">(C8-C10)</f>
         <v>880.709999999999</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="50" t="n">
         <f aca="false">(D8-D10)</f>
         <v>1507.65</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="50" t="n">
         <f aca="false">(E8-E10)</f>
         <v>2759.15</v>
       </c>
-      <c r="F9" s="52" t="n">
+      <c r="F9" s="50" t="n">
         <f aca="false">(F8-F10)</f>
         <v>532.140000000001</v>
       </c>
-      <c r="G9" s="52" t="n">
+      <c r="G9" s="50" t="n">
         <f aca="false">(G8-G10)</f>
         <v>2644.3</v>
       </c>
-      <c r="H9" s="52" t="n">
+      <c r="H9" s="50" t="n">
         <f aca="false">(H8-H10)</f>
         <v>4137.08</v>
       </c>
-      <c r="I9" s="52" t="n">
+      <c r="I9" s="50" t="n">
         <f aca="false">(I8-I10)</f>
         <v>3844.55</v>
       </c>
-      <c r="J9" s="52" t="n">
+      <c r="J9" s="50" t="n">
         <f aca="false">(J8-J10)</f>
         <v>3782.93</v>
       </c>
-      <c r="K9" s="52" t="n">
+      <c r="K9" s="50" t="n">
         <f aca="false">(K8-K10)</f>
         <v>4334.7</v>
       </c>
-      <c r="L9" s="58" t="n">
+      <c r="L9" s="56" t="n">
         <f aca="false">(L8-L10)</f>
         <v>5501.498090751</v>
       </c>
-      <c r="M9" s="58" t="n">
+      <c r="M9" s="56" t="n">
         <f aca="false">(M8-M10)</f>
         <v>6483.51079781494</v>
       </c>
-      <c r="N9" s="58" t="n">
+      <c r="N9" s="56" t="n">
         <f aca="false">(N8-N10)</f>
         <v>7725.84181067919</v>
       </c>
-      <c r="O9" s="58" t="n">
+      <c r="O9" s="56" t="n">
         <f aca="false">(O8-O10)</f>
         <v>9219.25311602349</v>
       </c>
-      <c r="P9" s="58" t="n">
+      <c r="P9" s="56" t="n">
         <f aca="false">(P8-P10)</f>
         <v>10725.2949396352</v>
       </c>
@@ -8836,89 +9218,89 @@
       <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="59" t="n">
+      <c r="B10" s="57" t="n">
         <v>5418.23</v>
       </c>
-      <c r="C10" s="59" t="n">
+      <c r="C10" s="57" t="n">
         <v>7156.67</v>
       </c>
-      <c r="D10" s="59" t="n">
+      <c r="D10" s="57" t="n">
         <v>6595.64</v>
       </c>
-      <c r="E10" s="59" t="n">
+      <c r="E10" s="57" t="n">
         <v>5947.11</v>
       </c>
-      <c r="F10" s="59" t="n">
+      <c r="F10" s="57" t="n">
         <v>8687.96</v>
       </c>
-      <c r="G10" s="59" t="n">
+      <c r="G10" s="57" t="n">
         <v>9527.96</v>
       </c>
-      <c r="H10" s="59" t="n">
+      <c r="H10" s="57" t="n">
         <v>10947.13</v>
       </c>
-      <c r="I10" s="59" t="n">
+      <c r="I10" s="57" t="n">
         <v>15589.41</v>
       </c>
-      <c r="J10" s="59" t="n">
+      <c r="J10" s="57" t="n">
         <v>18421.37</v>
       </c>
-      <c r="K10" s="59" t="n">
+      <c r="K10" s="57" t="n">
         <v>22868.19</v>
       </c>
-      <c r="L10" s="60" t="n">
+      <c r="L10" s="58" t="n">
         <f aca="false">(L6*Drivers!L8)</f>
         <v>27507.490453755</v>
       </c>
-      <c r="M10" s="60" t="n">
+      <c r="M10" s="58" t="n">
         <f aca="false">(M6*Drivers!M8)</f>
         <v>30823.2480551857</v>
       </c>
-      <c r="N10" s="60" t="n">
+      <c r="N10" s="58" t="n">
         <f aca="false">(N6*Drivers!N8)</f>
         <v>34979.2050483507</v>
       </c>
-      <c r="O10" s="60" t="n">
+      <c r="O10" s="58" t="n">
         <f aca="false">(O6*Drivers!O8)</f>
         <v>39810.4111828287</v>
       </c>
-      <c r="P10" s="60" t="n">
+      <c r="P10" s="58" t="n">
         <f aca="false">(P6*Drivers!P8)</f>
         <v>44232.0557729482</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="55" t="n">
+        <v>171</v>
+      </c>
+      <c r="B11" s="53" t="n">
         <v>1160.19</v>
       </c>
-      <c r="C11" s="55" t="n">
+      <c r="C11" s="53" t="n">
         <v>1188.37</v>
       </c>
-      <c r="D11" s="55" t="n">
+      <c r="D11" s="53" t="n">
         <v>1373.48</v>
       </c>
-      <c r="E11" s="55" t="n">
+      <c r="E11" s="53" t="n">
         <v>1680.28</v>
       </c>
-      <c r="F11" s="55" t="n">
+      <c r="F11" s="53" t="n">
         <v>2107.34</v>
       </c>
-      <c r="G11" s="55" t="n">
+      <c r="G11" s="53" t="n">
         <v>3099.3</v>
       </c>
-      <c r="H11" s="55" t="n">
+      <c r="H11" s="53" t="n">
         <v>3424.71</v>
       </c>
-      <c r="I11" s="55" t="n">
+      <c r="I11" s="53" t="n">
         <v>3888.46</v>
       </c>
-      <c r="J11" s="55" t="n">
+      <c r="J11" s="53" t="n">
         <v>4378.93</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="53" t="n">
         <v>5517.38</v>
       </c>
       <c r="L11" s="33" t="n">
@@ -8944,101 +9326,101 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="61" t="n">
+        <v>108</v>
+      </c>
+      <c r="B12" s="59" t="n">
         <f aca="false">(B10-B11)</f>
         <v>4258.04</v>
       </c>
-      <c r="C12" s="61" t="n">
+      <c r="C12" s="59" t="n">
         <f aca="false">(C10-C11)</f>
         <v>5968.3</v>
       </c>
-      <c r="D12" s="61" t="n">
+      <c r="D12" s="59" t="n">
         <f aca="false">(D10-D11)</f>
         <v>5222.16</v>
       </c>
-      <c r="E12" s="61" t="n">
+      <c r="E12" s="59" t="n">
         <f aca="false">(E10-E11)</f>
         <v>4266.83</v>
       </c>
-      <c r="F12" s="61" t="n">
+      <c r="F12" s="59" t="n">
         <f aca="false">(F10-F11)</f>
         <v>6580.62</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="59" t="n">
         <f aca="false">(G10-G11)</f>
         <v>6428.66</v>
       </c>
-      <c r="H12" s="61" t="n">
+      <c r="H12" s="59" t="n">
         <f aca="false">(H10-H11)</f>
         <v>7522.42</v>
       </c>
-      <c r="I12" s="61" t="n">
+      <c r="I12" s="59" t="n">
         <f aca="false">(I10-I11)</f>
         <v>11700.95</v>
       </c>
-      <c r="J12" s="61" t="n">
+      <c r="J12" s="59" t="n">
         <f aca="false">(J10-J11)</f>
         <v>14042.44</v>
       </c>
-      <c r="K12" s="61" t="n">
+      <c r="K12" s="59" t="n">
         <f aca="false">(K10-K11)</f>
         <v>17350.81</v>
       </c>
-      <c r="L12" s="62" t="n">
+      <c r="L12" s="60" t="n">
         <f aca="false">(L10-L11)</f>
         <v>19885.863923755</v>
       </c>
-      <c r="M12" s="62" t="n">
+      <c r="M12" s="60" t="n">
         <f aca="false">(M10-M11)</f>
         <v>22798.9831084688</v>
       </c>
-      <c r="N12" s="62" t="n">
+      <c r="N12" s="60" t="n">
         <f aca="false">(N10-N11)</f>
         <v>26496.5052566821</v>
       </c>
-      <c r="O12" s="62" t="n">
+      <c r="O12" s="60" t="n">
         <f aca="false">(O10-O11)</f>
         <v>30797.4793601757</v>
       </c>
-      <c r="P12" s="62" t="n">
+      <c r="P12" s="60" t="n">
         <f aca="false">(P10-P11)</f>
         <v>34608.7651418723</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="B13" s="55" t="n">
+        <v>172</v>
+      </c>
+      <c r="B13" s="53" t="n">
         <v>1036.57</v>
       </c>
-      <c r="C13" s="55" t="n">
+      <c r="C13" s="53" t="n">
         <v>844.49</v>
       </c>
-      <c r="D13" s="55" t="n">
+      <c r="D13" s="53" t="n">
         <v>1289.25</v>
       </c>
-      <c r="E13" s="55" t="n">
+      <c r="E13" s="53" t="n">
         <v>1927.73</v>
       </c>
-      <c r="F13" s="55" t="n">
+      <c r="F13" s="53" t="n">
         <v>1966.68</v>
       </c>
-      <c r="G13" s="55" t="n">
+      <c r="G13" s="53" t="n">
         <v>1832.4</v>
       </c>
-      <c r="H13" s="55" t="n">
+      <c r="H13" s="53" t="n">
         <v>327.11</v>
       </c>
-      <c r="I13" s="55" t="n">
+      <c r="I13" s="53" t="n">
         <v>670.56</v>
       </c>
-      <c r="J13" s="55" t="n">
+      <c r="J13" s="53" t="n">
         <v>1799.85</v>
       </c>
-      <c r="K13" s="55" t="n">
+      <c r="K13" s="53" t="n">
         <v>2151.73</v>
       </c>
       <c r="L13" s="33" t="n">
@@ -9064,36 +9446,36 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="B14" s="55" t="n">
+        <v>173</v>
+      </c>
+      <c r="B14" s="53" t="n">
         <v>1115.74</v>
       </c>
-      <c r="C14" s="55" t="n">
+      <c r="C14" s="53" t="n">
         <v>1578.66</v>
       </c>
-      <c r="D14" s="55" t="n">
+      <c r="D14" s="53" t="n">
         <v>1385.19</v>
       </c>
-      <c r="E14" s="55" t="n">
+      <c r="E14" s="53" t="n">
         <v>1950.64</v>
       </c>
-      <c r="F14" s="55" t="n">
+      <c r="F14" s="53" t="n">
         <v>2255.29</v>
       </c>
-      <c r="G14" s="55" t="n">
+      <c r="G14" s="53" t="n">
         <v>2543.92</v>
       </c>
-      <c r="H14" s="55" t="n">
+      <c r="H14" s="53" t="n">
         <v>2362.64</v>
       </c>
-      <c r="I14" s="55" t="n">
+      <c r="I14" s="53" t="n">
         <v>2732.94</v>
       </c>
-      <c r="J14" s="55" t="n">
+      <c r="J14" s="53" t="n">
         <v>2812.67</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="53" t="n">
         <v>4653.98</v>
       </c>
       <c r="L14" s="33" t="n">
@@ -9119,146 +9501,146 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="B15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="58" t="n">
+        <v>174</v>
+      </c>
+      <c r="B15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="M15" s="58" t="n">
+      <c r="M15" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="N15" s="58" t="n">
+      <c r="N15" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="O15" s="58" t="n">
+      <c r="O15" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="P15" s="58" t="n">
+      <c r="P15" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B16" s="59" t="n">
+        <v>175</v>
+      </c>
+      <c r="B16" s="57" t="n">
         <v>4178.87</v>
       </c>
-      <c r="C16" s="59" t="n">
+      <c r="C16" s="57" t="n">
         <v>5234.13</v>
       </c>
-      <c r="D16" s="59" t="n">
+      <c r="D16" s="57" t="n">
         <v>5126.22</v>
       </c>
-      <c r="E16" s="59" t="n">
+      <c r="E16" s="57" t="n">
         <v>4243.92</v>
       </c>
-      <c r="F16" s="59" t="n">
+      <c r="F16" s="57" t="n">
         <v>6292.01</v>
       </c>
-      <c r="G16" s="59" t="n">
+      <c r="G16" s="57" t="n">
         <v>5717.14</v>
       </c>
-      <c r="H16" s="59" t="n">
+      <c r="H16" s="57" t="n">
         <v>5486.89</v>
       </c>
-      <c r="I16" s="59" t="n">
+      <c r="I16" s="57" t="n">
         <v>9638.57</v>
       </c>
-      <c r="J16" s="59" t="n">
+      <c r="J16" s="57" t="n">
         <v>13029.62</v>
       </c>
-      <c r="K16" s="59" t="n">
+      <c r="K16" s="57" t="n">
         <v>14848.56</v>
       </c>
-      <c r="L16" s="62" t="n">
+      <c r="L16" s="60" t="n">
         <f aca="false">(((L12+L13)-L14)+L15)</f>
         <v>16820.3675948347</v>
       </c>
-      <c r="M16" s="62" t="n">
+      <c r="M16" s="60" t="n">
         <f aca="false">(((M12+M13)-M14)+M15)</f>
         <v>19667.052931367</v>
       </c>
-      <c r="N16" s="62" t="n">
+      <c r="N16" s="60" t="n">
         <f aca="false">(((N12+N13)-N14)+N15)</f>
         <v>23347.6334988025</v>
       </c>
-      <c r="O16" s="62" t="n">
+      <c r="O16" s="60" t="n">
         <f aca="false">(((O12+O13)-O14)+O15)</f>
         <v>27668.0294421138</v>
       </c>
-      <c r="P16" s="62" t="n">
+      <c r="P16" s="60" t="n">
         <f aca="false">(((P12+P13)-P14)+P15)</f>
         <v>31445.6364319749</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="B17" s="55" t="n">
+        <v>176</v>
+      </c>
+      <c r="B17" s="53" t="n">
         <v>267.35</v>
       </c>
-      <c r="C17" s="55" t="n">
+      <c r="C17" s="53" t="n">
         <v>1560.51</v>
       </c>
-      <c r="D17" s="55" t="n">
+      <c r="D17" s="53" t="n">
         <v>1136</v>
       </c>
-      <c r="E17" s="55" t="n">
+      <c r="E17" s="53" t="n">
         <v>480.79</v>
       </c>
-      <c r="F17" s="55" t="n">
+      <c r="F17" s="53" t="n">
         <v>1297.71</v>
       </c>
-      <c r="G17" s="55" t="n">
+      <c r="G17" s="53" t="n">
         <v>831.11</v>
       </c>
-      <c r="H17" s="55" t="n">
+      <c r="H17" s="53" t="n">
         <v>178.04</v>
       </c>
-      <c r="I17" s="55" t="n">
+      <c r="I17" s="53" t="n">
         <v>1527.93</v>
       </c>
-      <c r="J17" s="55" t="n">
+      <c r="J17" s="53" t="n">
         <v>1937.31</v>
       </c>
-      <c r="K17" s="55" t="n">
+      <c r="K17" s="53" t="n">
         <v>2042.35</v>
       </c>
       <c r="L17" s="33" t="n">
@@ -9286,60 +9668,60 @@
       <c r="A18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="59" t="n">
+      <c r="B18" s="57" t="n">
         <v>3911.52</v>
       </c>
-      <c r="C18" s="59" t="n">
+      <c r="C18" s="57" t="n">
         <v>3673.62</v>
       </c>
-      <c r="D18" s="59" t="n">
+      <c r="D18" s="57" t="n">
         <v>3990.22</v>
       </c>
-      <c r="E18" s="59" t="n">
+      <c r="E18" s="57" t="n">
         <v>3763.13</v>
       </c>
-      <c r="F18" s="59" t="n">
+      <c r="F18" s="57" t="n">
         <v>4994.3</v>
       </c>
-      <c r="G18" s="59" t="n">
+      <c r="G18" s="57" t="n">
         <v>4886.03</v>
       </c>
-      <c r="H18" s="59" t="n">
+      <c r="H18" s="57" t="n">
         <v>5308.85</v>
       </c>
-      <c r="I18" s="59" t="n">
+      <c r="I18" s="57" t="n">
         <v>8110.64</v>
       </c>
-      <c r="J18" s="59" t="n">
+      <c r="J18" s="57" t="n">
         <v>11092.31</v>
       </c>
-      <c r="K18" s="59" t="n">
+      <c r="K18" s="57" t="n">
         <v>12806.21</v>
       </c>
-      <c r="L18" s="62" t="n">
+      <c r="L18" s="60" t="n">
         <f aca="false">(L16-L17)</f>
         <v>13708.5995897903</v>
       </c>
-      <c r="M18" s="62" t="n">
+      <c r="M18" s="60" t="n">
         <f aca="false">(M16-M17)</f>
         <v>16028.6481390641</v>
       </c>
-      <c r="N18" s="62" t="n">
+      <c r="N18" s="60" t="n">
         <f aca="false">(N16-N17)</f>
         <v>19028.3213015241</v>
       </c>
-      <c r="O18" s="62" t="n">
+      <c r="O18" s="60" t="n">
         <f aca="false">(O16-O17)</f>
         <v>22549.4439953228</v>
       </c>
-      <c r="P18" s="62" t="n">
+      <c r="P18" s="60" t="n">
         <f aca="false">(P16-P17)</f>
         <v>25628.1936920596</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B19" s="34" t="n">
         <f aca="false">IFERROR((B18)/(Schedules!B23),0)</f>
@@ -9428,44 +9810,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -9477,18 +9859,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -9508,36 +9890,36 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="B6" s="55" t="n">
+        <v>179</v>
+      </c>
+      <c r="B6" s="53" t="n">
         <v>1976.8</v>
       </c>
-      <c r="C6" s="55" t="n">
+      <c r="C6" s="53" t="n">
         <v>2967.55</v>
       </c>
-      <c r="D6" s="55" t="n">
+      <c r="D6" s="53" t="n">
         <v>5967.3</v>
       </c>
-      <c r="E6" s="55" t="n">
+      <c r="E6" s="53" t="n">
         <v>7313.86</v>
       </c>
-      <c r="F6" s="55" t="n">
+      <c r="F6" s="53" t="n">
         <v>4700.78</v>
       </c>
-      <c r="G6" s="55" t="n">
+      <c r="G6" s="53" t="n">
         <v>10667.41</v>
       </c>
-      <c r="H6" s="55" t="n">
+      <c r="H6" s="53" t="n">
         <v>4334.31</v>
       </c>
-      <c r="I6" s="55" t="n">
+      <c r="I6" s="53" t="n">
         <v>7631.88</v>
       </c>
-      <c r="J6" s="55" t="n">
+      <c r="J6" s="53" t="n">
         <v>6605.97</v>
       </c>
-      <c r="K6" s="55" t="n">
+      <c r="K6" s="53" t="n">
         <v>8483.51</v>
       </c>
       <c r="L6" s="33" t="n">
@@ -9563,36 +9945,36 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="55" t="n">
+        <v>180</v>
+      </c>
+      <c r="B7" s="53" t="n">
         <v>2692.99</v>
       </c>
-      <c r="C7" s="55" t="n">
+      <c r="C7" s="53" t="n">
         <v>4309.91</v>
       </c>
-      <c r="D7" s="55" t="n">
+      <c r="D7" s="53" t="n">
         <v>2789.66</v>
       </c>
-      <c r="E7" s="55" t="n">
+      <c r="E7" s="53" t="n">
         <v>3202.14</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="53" t="n">
         <v>2925.71</v>
       </c>
-      <c r="G7" s="55" t="n">
+      <c r="G7" s="53" t="n">
         <v>2521.14</v>
       </c>
-      <c r="H7" s="55" t="n">
+      <c r="H7" s="53" t="n">
         <v>3957.07</v>
       </c>
-      <c r="I7" s="55" t="n">
+      <c r="I7" s="53" t="n">
         <v>3666.94</v>
       </c>
-      <c r="J7" s="55" t="n">
+      <c r="J7" s="53" t="n">
         <v>4432.36</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="53" t="n">
         <v>6382.54</v>
       </c>
       <c r="L7" s="33" t="n">
@@ -9618,36 +10000,36 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="55" t="n">
+        <v>181</v>
+      </c>
+      <c r="B8" s="53" t="n">
         <v>657.09</v>
       </c>
-      <c r="C8" s="55" t="n">
+      <c r="C8" s="53" t="n">
         <v>520.29</v>
       </c>
-      <c r="D8" s="55" t="n">
+      <c r="D8" s="53" t="n">
         <v>806.68</v>
       </c>
-      <c r="E8" s="55" t="n">
+      <c r="E8" s="53" t="n">
         <v>288.28</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="53" t="n">
         <v>991.85</v>
       </c>
-      <c r="G8" s="55" t="n">
+      <c r="G8" s="53" t="n">
         <v>395.64</v>
       </c>
-      <c r="H8" s="55" t="n">
+      <c r="H8" s="53" t="n">
         <v>451.97</v>
       </c>
-      <c r="I8" s="55" t="n">
+      <c r="I8" s="53" t="n">
         <v>437.51</v>
       </c>
-      <c r="J8" s="55" t="n">
+      <c r="J8" s="53" t="n">
         <v>521.8</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="53" t="n">
         <v>685</v>
       </c>
       <c r="L8" s="33" t="n">
@@ -9673,36 +10055,36 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="B9" s="55" t="n">
+        <v>182</v>
+      </c>
+      <c r="B9" s="53" t="n">
         <v>11313.66</v>
       </c>
-      <c r="C9" s="55" t="n">
+      <c r="C9" s="53" t="n">
         <v>11140.58</v>
       </c>
-      <c r="D9" s="55" t="n">
+      <c r="D9" s="53" t="n">
         <v>13360.59</v>
       </c>
-      <c r="E9" s="55" t="n">
+      <c r="E9" s="53" t="n">
         <v>14003.58</v>
       </c>
-      <c r="F9" s="55" t="n">
+      <c r="F9" s="53" t="n">
         <v>11739.35</v>
       </c>
-      <c r="G9" s="55" t="n">
+      <c r="G9" s="53" t="n">
         <v>15007.24</v>
       </c>
-      <c r="H9" s="55" t="n">
+      <c r="H9" s="53" t="n">
         <v>17527.69</v>
       </c>
-      <c r="I9" s="55" t="n">
+      <c r="I9" s="53" t="n">
         <v>14890.31</v>
       </c>
-      <c r="J9" s="55" t="n">
+      <c r="J9" s="53" t="n">
         <v>15900.65</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="53" t="n">
         <v>17757.28</v>
       </c>
       <c r="L9" s="33" t="n">
@@ -9728,36 +10110,36 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="B10" s="55" t="n">
+        <v>183</v>
+      </c>
+      <c r="B10" s="53" t="n">
         <v>21053.5</v>
       </c>
-      <c r="C10" s="55" t="n">
+      <c r="C10" s="53" t="n">
         <v>22670.01</v>
       </c>
-      <c r="D10" s="55" t="n">
+      <c r="D10" s="53" t="n">
         <v>28121.42</v>
       </c>
-      <c r="E10" s="55" t="n">
+      <c r="E10" s="53" t="n">
         <v>32714.51</v>
       </c>
-      <c r="F10" s="55" t="n">
+      <c r="F10" s="53" t="n">
         <v>48290.96</v>
       </c>
-      <c r="G10" s="55" t="n">
+      <c r="G10" s="53" t="n">
         <v>62552.92</v>
       </c>
-      <c r="H10" s="55" t="n">
+      <c r="H10" s="53" t="n">
         <v>72223.73</v>
       </c>
-      <c r="I10" s="55" t="n">
+      <c r="I10" s="53" t="n">
         <v>75147.81</v>
       </c>
-      <c r="J10" s="55" t="n">
+      <c r="J10" s="53" t="n">
         <v>89616.32</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="53" t="n">
         <v>131652.5</v>
       </c>
       <c r="L10" s="33" t="n">
@@ -9783,36 +10165,36 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="B11" s="55" t="n">
+        <v>184</v>
+      </c>
+      <c r="B11" s="53" t="n">
         <v>4513.97</v>
       </c>
-      <c r="C11" s="55" t="n">
+      <c r="C11" s="53" t="n">
         <v>4545.46</v>
       </c>
-      <c r="D11" s="55" t="n">
+      <c r="D11" s="53" t="n">
         <v>4483.48</v>
       </c>
-      <c r="E11" s="55" t="n">
+      <c r="E11" s="53" t="n">
         <v>3216.33</v>
       </c>
-      <c r="F11" s="55" t="n">
+      <c r="F11" s="53" t="n">
         <v>3697.13</v>
       </c>
-      <c r="G11" s="55" t="n">
+      <c r="G11" s="53" t="n">
         <v>4022.9</v>
       </c>
-      <c r="H11" s="55" t="n">
+      <c r="H11" s="53" t="n">
         <v>6636.77</v>
       </c>
-      <c r="I11" s="55" t="n">
+      <c r="I11" s="53" t="n">
         <v>10936.09</v>
       </c>
-      <c r="J11" s="55" t="n">
+      <c r="J11" s="53" t="n">
         <v>11706.1</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="53" t="n">
         <v>12689.05</v>
       </c>
       <c r="L11" s="33" t="n">
@@ -9838,127 +10220,127 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="B12" s="55" t="n">
+        <v>185</v>
+      </c>
+      <c r="B12" s="53" t="n">
         <v>1161.36</v>
       </c>
-      <c r="C12" s="55" t="n">
+      <c r="C12" s="53" t="n">
         <v>1078.92</v>
       </c>
-      <c r="D12" s="55" t="n">
+      <c r="D12" s="53" t="n">
         <v>782.3</v>
       </c>
-      <c r="E12" s="55" t="n">
+      <c r="E12" s="53" t="n">
         <v>1178</v>
       </c>
-      <c r="F12" s="55" t="n">
+      <c r="F12" s="53" t="n">
         <v>2236.15</v>
       </c>
-      <c r="G12" s="55" t="n">
+      <c r="G12" s="53" t="n">
         <v>3160.74</v>
       </c>
-      <c r="H12" s="55" t="n">
+      <c r="H12" s="53" t="n">
         <v>7431.65</v>
       </c>
-      <c r="I12" s="55" t="n">
+      <c r="I12" s="53" t="n">
         <v>4288.66</v>
       </c>
-      <c r="J12" s="55" t="n">
+      <c r="J12" s="53" t="n">
         <v>4659.45</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="53" t="n">
         <v>5448.65</v>
       </c>
-      <c r="L12" s="58" t="n">
+      <c r="L12" s="56" t="n">
         <f aca="false">K12</f>
         <v>5448.65</v>
       </c>
-      <c r="M12" s="58" t="n">
+      <c r="M12" s="56" t="n">
         <f aca="false">L12</f>
         <v>5448.65</v>
       </c>
-      <c r="N12" s="58" t="n">
+      <c r="N12" s="56" t="n">
         <f aca="false">M12</f>
         <v>5448.65</v>
       </c>
-      <c r="O12" s="58" t="n">
+      <c r="O12" s="56" t="n">
         <f aca="false">N12</f>
         <v>5448.65</v>
       </c>
-      <c r="P12" s="58" t="n">
+      <c r="P12" s="56" t="n">
         <f aca="false">O12</f>
         <v>5448.65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B13" s="61" t="n">
+        <v>186</v>
+      </c>
+      <c r="B13" s="59" t="n">
         <f aca="false">((((((B6+B7)+B8)+B9)+B10)+B11)+B12)</f>
         <v>43369.37</v>
       </c>
-      <c r="C13" s="61" t="n">
+      <c r="C13" s="59" t="n">
         <f aca="false">((((((C6+C7)+C8)+C9)+C10)+C11)+C12)</f>
         <v>47232.72</v>
       </c>
-      <c r="D13" s="61" t="n">
+      <c r="D13" s="59" t="n">
         <f aca="false">((((((D6+D7)+D8)+D9)+D10)+D11)+D12)</f>
         <v>56311.43</v>
       </c>
-      <c r="E13" s="61" t="n">
+      <c r="E13" s="59" t="n">
         <f aca="false">((((((E6+E7)+E8)+E9)+E10)+E11)+E12)</f>
         <v>61916.7</v>
       </c>
-      <c r="F13" s="61" t="n">
+      <c r="F13" s="59" t="n">
         <f aca="false">((((((F6+F7)+F8)+F9)+F10)+F11)+F12)</f>
         <v>74581.93</v>
       </c>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="59" t="n">
         <f aca="false">((((((G6+G7)+G8)+G9)+G10)+G11)+G12)</f>
         <v>98327.99</v>
       </c>
-      <c r="H13" s="61" t="n">
+      <c r="H13" s="59" t="n">
         <f aca="false">((((((H6+H7)+H8)+H9)+H10)+H11)+H12)</f>
         <v>112563.19</v>
       </c>
-      <c r="I13" s="61" t="n">
+      <c r="I13" s="59" t="n">
         <f aca="false">((((((I6+I7)+I8)+I9)+I10)+I11)+I12)</f>
         <v>116999.2</v>
       </c>
-      <c r="J13" s="61" t="n">
+      <c r="J13" s="59" t="n">
         <f aca="false">((((((J6+J7)+J8)+J9)+J10)+J11)+J12)</f>
         <v>133442.65</v>
       </c>
-      <c r="K13" s="61" t="n">
+      <c r="K13" s="59" t="n">
         <f aca="false">((((((K6+K7)+K8)+K9)+K10)+K11)+K12)</f>
         <v>183098.53</v>
       </c>
-      <c r="L13" s="62" t="n">
+      <c r="L13" s="60" t="n">
         <f aca="false">((((((L6+L7)+L8)+L9)+L10)+L11)+L12)</f>
         <v>204584.572061723</v>
       </c>
-      <c r="M13" s="62" t="n">
+      <c r="M13" s="60" t="n">
         <f aca="false">((((((M6+M7)+M8)+M9)+M10)+M11)+M12)</f>
         <v>226631.569922777</v>
       </c>
-      <c r="N13" s="62" t="n">
+      <c r="N13" s="60" t="n">
         <f aca="false">((((((N6+N7)+N8)+N9)+N10)+N11)+N12)</f>
         <v>252519.873533982</v>
       </c>
-      <c r="O13" s="62" t="n">
+      <c r="O13" s="60" t="n">
         <f aca="false">((((((O6+O7)+O8)+O9)+O10)+O11)+O12)</f>
         <v>282562.910646897</v>
       </c>
-      <c r="P13" s="62" t="n">
+      <c r="P13" s="60" t="n">
         <f aca="false">((((((P6+P7)+P8)+P9)+P10)+P11)+P12)</f>
         <v>315238.204387873</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
@@ -9978,91 +10360,91 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="55" t="n">
+        <v>188</v>
+      </c>
+      <c r="B15" s="53" t="n">
         <v>414.19</v>
       </c>
-      <c r="C15" s="55" t="n">
+      <c r="C15" s="53" t="n">
         <v>414.19</v>
       </c>
-      <c r="D15" s="55" t="n">
+      <c r="D15" s="53" t="n">
         <v>414.19</v>
       </c>
-      <c r="E15" s="55" t="n">
+      <c r="E15" s="53" t="n">
         <v>406.35</v>
       </c>
-      <c r="F15" s="55" t="n">
+      <c r="F15" s="53" t="n">
         <v>406.35</v>
       </c>
-      <c r="G15" s="55" t="n">
+      <c r="G15" s="53" t="n">
         <v>422.47</v>
       </c>
-      <c r="H15" s="55" t="n">
+      <c r="H15" s="53" t="n">
         <v>432.03</v>
       </c>
-      <c r="I15" s="55" t="n">
+      <c r="I15" s="53" t="n">
         <v>432.03</v>
       </c>
-      <c r="J15" s="55" t="n">
+      <c r="J15" s="53" t="n">
         <v>432.03</v>
       </c>
-      <c r="K15" s="55" t="n">
+      <c r="K15" s="53" t="n">
         <v>460.79</v>
       </c>
-      <c r="L15" s="58" t="n">
+      <c r="L15" s="56" t="n">
         <f aca="false">K15</f>
         <v>460.79</v>
       </c>
-      <c r="M15" s="58" t="n">
+      <c r="M15" s="56" t="n">
         <f aca="false">L15</f>
         <v>460.79</v>
       </c>
-      <c r="N15" s="58" t="n">
+      <c r="N15" s="56" t="n">
         <f aca="false">M15</f>
         <v>460.79</v>
       </c>
-      <c r="O15" s="58" t="n">
+      <c r="O15" s="56" t="n">
         <f aca="false">N15</f>
         <v>460.79</v>
       </c>
-      <c r="P15" s="58" t="n">
+      <c r="P15" s="56" t="n">
         <f aca="false">O15</f>
         <v>460.79</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" s="55" t="n">
+        <v>189</v>
+      </c>
+      <c r="B16" s="53" t="n">
         <v>17111.79</v>
       </c>
-      <c r="C16" s="55" t="n">
+      <c r="C16" s="53" t="n">
         <v>20488.76</v>
       </c>
-      <c r="D16" s="55" t="n">
+      <c r="D16" s="53" t="n">
         <v>23958.13</v>
       </c>
-      <c r="E16" s="55" t="n">
+      <c r="E16" s="53" t="n">
         <v>25050.61</v>
       </c>
-      <c r="F16" s="55" t="n">
+      <c r="F16" s="53" t="n">
         <v>30035.38</v>
       </c>
-      <c r="G16" s="55" t="n">
+      <c r="G16" s="53" t="n">
         <v>41399.22</v>
       </c>
-      <c r="H16" s="55" t="n">
+      <c r="H16" s="53" t="n">
         <v>44957.36</v>
       </c>
-      <c r="I16" s="55" t="n">
+      <c r="I16" s="53" t="n">
         <v>52346.21</v>
       </c>
-      <c r="J16" s="55" t="n">
+      <c r="J16" s="53" t="n">
         <v>61836.83</v>
       </c>
-      <c r="K16" s="55" t="n">
+      <c r="K16" s="53" t="n">
         <v>95497.98</v>
       </c>
       <c r="L16" s="33" t="n">
@@ -10088,36 +10470,36 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="B17" s="55" t="n">
+        <v>190</v>
+      </c>
+      <c r="B17" s="53" t="n">
         <v>22214.26</v>
       </c>
-      <c r="C17" s="55" t="n">
+      <c r="C17" s="53" t="n">
         <v>22370.04</v>
       </c>
-      <c r="D17" s="55" t="n">
+      <c r="D17" s="53" t="n">
         <v>27711.54</v>
       </c>
-      <c r="E17" s="55" t="n">
+      <c r="E17" s="53" t="n">
         <v>30242.32</v>
       </c>
-      <c r="F17" s="55" t="n">
+      <c r="F17" s="53" t="n">
         <v>35855.33</v>
       </c>
-      <c r="G17" s="55" t="n">
+      <c r="G17" s="53" t="n">
         <v>47934.75</v>
       </c>
-      <c r="H17" s="55" t="n">
+      <c r="H17" s="53" t="n">
         <v>53434.22</v>
       </c>
-      <c r="I17" s="55" t="n">
+      <c r="I17" s="53" t="n">
         <v>49470.24</v>
       </c>
-      <c r="J17" s="55" t="n">
+      <c r="J17" s="53" t="n">
         <v>51620.73</v>
       </c>
-      <c r="K17" s="55" t="n">
+      <c r="K17" s="53" t="n">
         <v>63565.52</v>
       </c>
       <c r="L17" s="33" t="n">
@@ -10143,36 +10525,36 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="B18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="55" t="n">
+        <v>191</v>
+      </c>
+      <c r="B18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="53" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="33" t="n">
@@ -10198,101 +10580,101 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="B19" s="52" t="n">
+        <v>192</v>
+      </c>
+      <c r="B19" s="50" t="n">
         <f aca="false">(B17+B18)</f>
         <v>22214.26</v>
       </c>
-      <c r="C19" s="52" t="n">
+      <c r="C19" s="50" t="n">
         <f aca="false">(C17+C18)</f>
         <v>22370.04</v>
       </c>
-      <c r="D19" s="52" t="n">
+      <c r="D19" s="50" t="n">
         <f aca="false">(D17+D18)</f>
         <v>27711.54</v>
       </c>
-      <c r="E19" s="52" t="n">
+      <c r="E19" s="50" t="n">
         <f aca="false">(E17+E18)</f>
         <v>30242.32</v>
       </c>
-      <c r="F19" s="52" t="n">
+      <c r="F19" s="50" t="n">
         <f aca="false">(F17+F18)</f>
         <v>35855.33</v>
       </c>
-      <c r="G19" s="52" t="n">
+      <c r="G19" s="50" t="n">
         <f aca="false">(G17+G18)</f>
         <v>47934.75</v>
       </c>
-      <c r="H19" s="52" t="n">
+      <c r="H19" s="50" t="n">
         <f aca="false">(H17+H18)</f>
         <v>53434.22</v>
       </c>
-      <c r="I19" s="52" t="n">
+      <c r="I19" s="50" t="n">
         <f aca="false">(I17+I18)</f>
         <v>49470.24</v>
       </c>
-      <c r="J19" s="52" t="n">
+      <c r="J19" s="50" t="n">
         <f aca="false">(J17+J18)</f>
         <v>51620.73</v>
       </c>
-      <c r="K19" s="52" t="n">
+      <c r="K19" s="50" t="n">
         <f aca="false">(K17+K18)</f>
         <v>63565.52</v>
       </c>
-      <c r="L19" s="58" t="n">
+      <c r="L19" s="56" t="n">
         <f aca="false">(L17+L18)</f>
         <v>67817.67189488</v>
       </c>
-      <c r="M19" s="58" t="n">
+      <c r="M19" s="56" t="n">
         <f aca="false">(M17+M18)</f>
         <v>72354.2672386161</v>
       </c>
-      <c r="N19" s="58" t="n">
+      <c r="N19" s="56" t="n">
         <f aca="false">(N17+N18)</f>
         <v>77194.3335912761</v>
       </c>
-      <c r="O19" s="58" t="n">
+      <c r="O19" s="56" t="n">
         <f aca="false">(O17+O18)</f>
         <v>82358.1713425309</v>
       </c>
-      <c r="P19" s="58" t="n">
+      <c r="P19" s="56" t="n">
         <f aca="false">(P17+P18)</f>
         <v>87867.4388563182</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="B20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="55" t="n">
+        <v>193</v>
+      </c>
+      <c r="B20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="53" t="n">
         <v>2720.5</v>
       </c>
-      <c r="K20" s="55" t="n">
+      <c r="K20" s="53" t="n">
         <v>2736.24</v>
       </c>
       <c r="L20" s="33" t="n">
@@ -10318,36 +10700,36 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="B21" s="55" t="n">
+        <v>194</v>
+      </c>
+      <c r="B21" s="53" t="n">
         <v>3629.13</v>
       </c>
-      <c r="C21" s="55" t="n">
+      <c r="C21" s="53" t="n">
         <v>3959.73</v>
       </c>
-      <c r="D21" s="55" t="n">
+      <c r="D21" s="53" t="n">
         <v>4227.57</v>
       </c>
-      <c r="E21" s="55" t="n">
+      <c r="E21" s="53" t="n">
         <v>6217.42</v>
       </c>
-      <c r="F21" s="55" t="n">
+      <c r="F21" s="53" t="n">
         <v>8284.87</v>
       </c>
-      <c r="G21" s="55" t="n">
+      <c r="G21" s="53" t="n">
         <v>8571.55</v>
       </c>
-      <c r="H21" s="55" t="n">
+      <c r="H21" s="53" t="n">
         <v>13739.58</v>
       </c>
-      <c r="I21" s="55" t="n">
+      <c r="I21" s="53" t="n">
         <v>14750.72</v>
       </c>
-      <c r="J21" s="55" t="n">
+      <c r="J21" s="53" t="n">
         <v>16832.56</v>
       </c>
-      <c r="K21" s="55" t="n">
+      <c r="K21" s="53" t="n">
         <v>20838</v>
       </c>
       <c r="L21" s="33" t="n">
@@ -10373,65 +10755,65 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B22" s="61" t="n">
+        <v>195</v>
+      </c>
+      <c r="B22" s="59" t="n">
         <f aca="false">((((B15+B16)+B19)+B20)+B21)</f>
         <v>43369.37</v>
       </c>
-      <c r="C22" s="61" t="n">
+      <c r="C22" s="59" t="n">
         <f aca="false">((((C15+C16)+C19)+C20)+C21)</f>
         <v>47232.72</v>
       </c>
-      <c r="D22" s="61" t="n">
+      <c r="D22" s="59" t="n">
         <f aca="false">((((D15+D16)+D19)+D20)+D21)</f>
         <v>56311.43</v>
       </c>
-      <c r="E22" s="61" t="n">
+      <c r="E22" s="59" t="n">
         <f aca="false">((((E15+E16)+E19)+E20)+E21)</f>
         <v>61916.7</v>
       </c>
-      <c r="F22" s="61" t="n">
+      <c r="F22" s="59" t="n">
         <f aca="false">((((F15+F16)+F19)+F20)+F21)</f>
         <v>74581.93</v>
       </c>
-      <c r="G22" s="61" t="n">
+      <c r="G22" s="59" t="n">
         <f aca="false">((((G15+G16)+G19)+G20)+G21)</f>
         <v>98327.99</v>
       </c>
-      <c r="H22" s="61" t="n">
+      <c r="H22" s="59" t="n">
         <f aca="false">((((H15+H16)+H19)+H20)+H21)</f>
         <v>112563.19</v>
       </c>
-      <c r="I22" s="61" t="n">
+      <c r="I22" s="59" t="n">
         <f aca="false">((((I15+I16)+I19)+I20)+I21)</f>
         <v>116999.2</v>
       </c>
-      <c r="J22" s="61" t="n">
+      <c r="J22" s="59" t="n">
         <f aca="false">((((J15+J16)+J19)+J20)+J21)</f>
         <v>133442.65</v>
       </c>
-      <c r="K22" s="61" t="n">
+      <c r="K22" s="59" t="n">
         <f aca="false">((((K15+K16)+K19)+K20)+K21)</f>
         <v>183098.53</v>
       </c>
-      <c r="L22" s="62" t="n">
+      <c r="L22" s="60" t="n">
         <f aca="false">((((L15+L16)+L19)+L20)+L21)</f>
         <v>204584.572061723</v>
       </c>
-      <c r="M22" s="62" t="n">
+      <c r="M22" s="60" t="n">
         <f aca="false">((((M15+M16)+M19)+M20)+M21)</f>
         <v>226631.569922777</v>
       </c>
-      <c r="N22" s="62" t="n">
+      <c r="N22" s="60" t="n">
         <f aca="false">((((N15+N16)+N19)+N20)+N21)</f>
         <v>252519.873533982</v>
       </c>
-      <c r="O22" s="62" t="n">
+      <c r="O22" s="60" t="n">
         <f aca="false">((((O15+O16)+O19)+O20)+O21)</f>
         <v>282562.910646897</v>
       </c>
-      <c r="P22" s="62" t="n">
+      <c r="P22" s="60" t="n">
         <f aca="false">((((P15+P16)+P19)+P20)+P21)</f>
         <v>315238.204387873</v>
       </c>
@@ -10462,44 +10844,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -10511,18 +10893,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -10542,7 +10924,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">'Income Statement'!B18</f>
@@ -10607,7 +10989,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">'Income Statement'!B11</f>
@@ -10672,7 +11054,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">-(Schedules!B12)</f>
@@ -10737,72 +11119,72 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="61" t="n">
+        <v>200</v>
+      </c>
+      <c r="B9" s="59" t="n">
         <f aca="false">((B6+B7)+B8)</f>
         <v>-5962.9</v>
       </c>
-      <c r="C9" s="61" t="n">
+      <c r="C9" s="59" t="n">
         <f aca="false">((C6+C7)+C8)</f>
         <v>3885.55</v>
       </c>
-      <c r="D9" s="61" t="n">
+      <c r="D9" s="59" t="n">
         <f aca="false">((D6+D7)+D8)</f>
         <v>4645.39</v>
       </c>
-      <c r="E9" s="61" t="n">
+      <c r="E9" s="59" t="n">
         <f aca="false">((E6+E7)+E8)</f>
         <v>6896.19</v>
       </c>
-      <c r="F9" s="61" t="n">
+      <c r="F9" s="59" t="n">
         <f aca="false">((F6+F7)+F8)</f>
         <v>11006.18</v>
       </c>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="59" t="n">
         <f aca="false">((G6+G7)+G8)</f>
         <v>6004.9</v>
       </c>
-      <c r="H9" s="61" t="n">
+      <c r="H9" s="59" t="n">
         <f aca="false">((H6+H7)+H8)</f>
         <v>9888.88</v>
       </c>
-      <c r="I9" s="61" t="n">
+      <c r="I9" s="59" t="n">
         <f aca="false">((I6+I7)+I8)</f>
         <v>15952.21</v>
       </c>
-      <c r="J9" s="61" t="n">
+      <c r="J9" s="59" t="n">
         <f aca="false">((J6+J7)+J8)</f>
         <v>18413.53</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="59" t="n">
         <f aca="false">((K6+K7)+K8)</f>
         <v>18374.76</v>
       </c>
-      <c r="L9" s="62" t="n">
+      <c r="L9" s="60" t="n">
         <f aca="false">((L6+L7)+L8)</f>
         <v>19244.3939067476</v>
       </c>
-      <c r="M9" s="62" t="n">
+      <c r="M9" s="60" t="n">
         <f aca="false">((M6+M7)+M8)</f>
         <v>23618.5122156429</v>
       </c>
-      <c r="N9" s="62" t="n">
+      <c r="N9" s="60" t="n">
         <f aca="false">((N6+N7)+N8)</f>
         <v>26965.3844400563</v>
       </c>
-      <c r="O9" s="62" t="n">
+      <c r="O9" s="60" t="n">
         <f aca="false">((O6+O7)+O8)</f>
         <v>30923.1096120272</v>
       </c>
-      <c r="P9" s="62" t="n">
+      <c r="P9" s="60" t="n">
         <f aca="false">((P6+P7)+P8)</f>
         <v>34652.3382657155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -10822,7 +11204,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">(-(Schedules!B7)-('Balance Sheet'!B11-0))</f>
@@ -10887,7 +11269,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">-(('Balance Sheet'!B12-0))</f>
@@ -10952,72 +11334,72 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="61" t="n">
+        <v>203</v>
+      </c>
+      <c r="B13" s="59" t="n">
         <f aca="false">(B11+B12)</f>
         <v>-5675.33</v>
       </c>
-      <c r="C13" s="61" t="n">
+      <c r="C13" s="59" t="n">
         <f aca="false">(C11+C12)</f>
         <v>-2753.93</v>
       </c>
-      <c r="D13" s="61" t="n">
+      <c r="D13" s="59" t="n">
         <f aca="false">(D11+D12)</f>
         <v>-6466.29</v>
       </c>
-      <c r="E13" s="61" t="n">
+      <c r="E13" s="59" t="n">
         <f aca="false">(E11+E12)</f>
         <v>-5401.92</v>
       </c>
-      <c r="F13" s="61" t="n">
+      <c r="F13" s="59" t="n">
         <f aca="false">(F11+F12)</f>
         <v>-19222.74</v>
       </c>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="59" t="n">
         <f aca="false">(G11+G12)</f>
         <v>-18611.62</v>
       </c>
-      <c r="H13" s="61" t="n">
+      <c r="H13" s="59" t="n">
         <f aca="false">(H11+H12)</f>
         <v>-19980.3</v>
       </c>
-      <c r="I13" s="61" t="n">
+      <c r="I13" s="59" t="n">
         <f aca="false">(I11+I12)</f>
         <v>-7968.87</v>
       </c>
-      <c r="J13" s="61" t="n">
+      <c r="J13" s="59" t="n">
         <f aca="false">(J11+J12)</f>
         <v>-19988.24</v>
       </c>
-      <c r="K13" s="61" t="n">
+      <c r="K13" s="59" t="n">
         <f aca="false">(K11+K12)</f>
         <v>-49325.71</v>
       </c>
-      <c r="L13" s="62" t="n">
+      <c r="L13" s="60" t="n">
         <f aca="false">(L11+L12)</f>
         <v>-19459.8710096519</v>
       </c>
-      <c r="M13" s="62" t="n">
+      <c r="M13" s="60" t="n">
         <f aca="false">(M11+M12)</f>
         <v>-18230.9730770904</v>
       </c>
-      <c r="N13" s="62" t="n">
+      <c r="N13" s="60" t="n">
         <f aca="false">(N11+N12)</f>
         <v>-20515.4592614869</v>
       </c>
-      <c r="O13" s="62" t="n">
+      <c r="O13" s="60" t="n">
         <f aca="false">(O11+O12)</f>
         <v>-22922.8952457225</v>
       </c>
-      <c r="P13" s="62" t="n">
+      <c r="P13" s="60" t="n">
         <f aca="false">(P11+P12)</f>
         <v>-23510.1722895453</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
@@ -11037,7 +11419,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">('Balance Sheet'!B17-0)</f>
@@ -11102,7 +11484,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">('Balance Sheet'!B18-0)</f>
@@ -11167,7 +11549,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">-(Schedules!B22)</f>
@@ -11232,7 +11614,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">Drivers!B27</f>
@@ -11297,72 +11679,72 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B19" s="61" t="n">
+        <v>208</v>
+      </c>
+      <c r="B19" s="59" t="n">
         <f aca="false">(((B15+B16)+B17)+B18)</f>
         <v>21945.04</v>
       </c>
-      <c r="C19" s="61" t="n">
+      <c r="C19" s="59" t="n">
         <f aca="false">(((C15+C16)+C17)+C18)</f>
         <v>-258.409999999998</v>
       </c>
-      <c r="D19" s="61" t="n">
+      <c r="D19" s="59" t="n">
         <f aca="false">(((D15+D16)+D17)+D18)</f>
         <v>5300.08</v>
       </c>
-      <c r="E19" s="61" t="n">
+      <c r="E19" s="59" t="n">
         <f aca="false">(((E15+E16)+E17)+E18)</f>
         <v>1880.62</v>
       </c>
-      <c r="F19" s="61" t="n">
+      <c r="F19" s="59" t="n">
         <f aca="false">(((F15+F16)+F17)+F18)</f>
         <v>4597.13</v>
       </c>
-      <c r="G19" s="61" t="n">
+      <c r="G19" s="59" t="n">
         <f aca="false">(((G15+G16)+G17)+G18)</f>
         <v>11023.24</v>
       </c>
-      <c r="H19" s="61" t="n">
+      <c r="H19" s="59" t="n">
         <f aca="false">(((H15+H16)+H17)+H18)</f>
         <v>4419.39</v>
       </c>
-      <c r="I19" s="61" t="n">
+      <c r="I19" s="59" t="n">
         <f aca="false">(((I15+I16)+I17)+I18)</f>
         <v>-5260.07</v>
       </c>
-      <c r="J19" s="61" t="n">
+      <c r="J19" s="59" t="n">
         <f aca="false">(((J15+J16)+J17)+J18)</f>
         <v>638.390000000005</v>
       </c>
-      <c r="K19" s="61" t="n">
+      <c r="K19" s="59" t="n">
         <f aca="false">(((K15+K16)+K17)+K18)</f>
         <v>10216.83</v>
       </c>
-      <c r="L19" s="62" t="n">
+      <c r="L19" s="60" t="n">
         <f aca="false">(((L15+L16)+L17)+L18)</f>
         <v>2282.44547142057</v>
       </c>
-      <c r="M19" s="62" t="n">
+      <c r="M19" s="60" t="n">
         <f aca="false">(((M15+M16)+M17)+M18)</f>
         <v>2233.53506452281</v>
       </c>
-      <c r="N19" s="62" t="n">
+      <c r="N19" s="60" t="n">
         <f aca="false">(((N15+N16)+N17)+N18)</f>
         <v>2106.0010347718</v>
       </c>
-      <c r="O19" s="62" t="n">
+      <c r="O19" s="60" t="n">
         <f aca="false">(((O15+O16)+O17)+O18)</f>
         <v>1923.84344023086</v>
       </c>
-      <c r="P19" s="62" t="n">
+      <c r="P19" s="60" t="n">
         <f aca="false">(((P15+P16)+P17)+P18)</f>
         <v>1826.90613133737</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
@@ -11382,74 +11764,74 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B21" s="63" t="n">
+        <v>210</v>
+      </c>
+      <c r="B21" s="61" t="n">
         <f aca="false">((B9+B13)+B19)</f>
         <v>10306.81</v>
       </c>
-      <c r="C21" s="63" t="n">
+      <c r="C21" s="61" t="n">
         <f aca="false">((C9+C13)+C19)</f>
         <v>873.210000000003</v>
       </c>
-      <c r="D21" s="63" t="n">
+      <c r="D21" s="61" t="n">
         <f aca="false">((D9+D13)+D19)</f>
         <v>3479.18</v>
       </c>
-      <c r="E21" s="63" t="n">
+      <c r="E21" s="61" t="n">
         <f aca="false">((E9+E13)+E19)</f>
         <v>3374.89</v>
       </c>
-      <c r="F21" s="63" t="n">
+      <c r="F21" s="61" t="n">
         <f aca="false">((F9+F13)+F19)</f>
         <v>-3619.43</v>
       </c>
-      <c r="G21" s="63" t="n">
+      <c r="G21" s="61" t="n">
         <f aca="false">((G9+G13)+G19)</f>
         <v>-1583.48</v>
       </c>
-      <c r="H21" s="63" t="n">
+      <c r="H21" s="61" t="n">
         <f aca="false">((H9+H13)+H19)</f>
         <v>-5672.03</v>
       </c>
-      <c r="I21" s="63" t="n">
+      <c r="I21" s="61" t="n">
         <f aca="false">((I9+I13)+I19)</f>
         <v>2723.27</v>
       </c>
-      <c r="J21" s="63" t="n">
+      <c r="J21" s="61" t="n">
         <f aca="false">((J9+J13)+J19)</f>
         <v>-936.31999999999</v>
       </c>
-      <c r="K21" s="63" t="n">
+      <c r="K21" s="61" t="n">
         <f aca="false">((K9+K13)+K19)</f>
         <v>-20734.12</v>
       </c>
-      <c r="L21" s="64" t="n">
+      <c r="L21" s="62" t="n">
         <f aca="false">((L9+L13)+L19)</f>
         <v>2066.9683685162</v>
       </c>
-      <c r="M21" s="64" t="n">
+      <c r="M21" s="62" t="n">
         <f aca="false">((M9+M13)+M19)</f>
         <v>7621.07420307529</v>
       </c>
-      <c r="N21" s="64" t="n">
+      <c r="N21" s="62" t="n">
         <f aca="false">((N9+N13)+N19)</f>
         <v>8555.92621334119</v>
       </c>
-      <c r="O21" s="64" t="n">
+      <c r="O21" s="62" t="n">
         <f aca="false">((O9+O13)+O19)</f>
         <v>9924.05780653557</v>
       </c>
-      <c r="P21" s="64" t="n">
+      <c r="P21" s="62" t="n">
         <f aca="false">((P9+P13)+P19)</f>
         <v>12969.0721075076</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="B22" s="52" t="n">
+        <v>211</v>
+      </c>
+      <c r="B22" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
@@ -11512,72 +11894,72 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B23" s="61" t="n">
+        <v>212</v>
+      </c>
+      <c r="B23" s="59" t="n">
         <f aca="false">(B22+B21)</f>
         <v>10306.81</v>
       </c>
-      <c r="C23" s="61" t="n">
+      <c r="C23" s="59" t="n">
         <f aca="false">(C22+C21)</f>
         <v>2850.01</v>
       </c>
-      <c r="D23" s="61" t="n">
+      <c r="D23" s="59" t="n">
         <f aca="false">(D22+D21)</f>
         <v>6446.73</v>
       </c>
-      <c r="E23" s="61" t="n">
+      <c r="E23" s="59" t="n">
         <f aca="false">(E22+E21)</f>
         <v>9342.19</v>
       </c>
-      <c r="F23" s="61" t="n">
+      <c r="F23" s="59" t="n">
         <f aca="false">(F22+F21)</f>
         <v>3694.43</v>
       </c>
-      <c r="G23" s="61" t="n">
+      <c r="G23" s="59" t="n">
         <f aca="false">(G22+G21)</f>
         <v>3117.3</v>
       </c>
-      <c r="H23" s="61" t="n">
+      <c r="H23" s="59" t="n">
         <f aca="false">(H22+H21)</f>
         <v>4995.38</v>
       </c>
-      <c r="I23" s="61" t="n">
+      <c r="I23" s="59" t="n">
         <f aca="false">(I22+I21)</f>
         <v>7057.58</v>
       </c>
-      <c r="J23" s="61" t="n">
+      <c r="J23" s="59" t="n">
         <f aca="false">(J22+J21)</f>
         <v>6695.56000000001</v>
       </c>
-      <c r="K23" s="61" t="n">
+      <c r="K23" s="59" t="n">
         <f aca="false">(K22+K21)</f>
         <v>-14128.15</v>
       </c>
-      <c r="L23" s="62" t="n">
+      <c r="L23" s="60" t="n">
         <f aca="false">(L22+L21)</f>
         <v>10550.4783685162</v>
       </c>
-      <c r="M23" s="62" t="n">
+      <c r="M23" s="60" t="n">
         <f aca="false">(M22+M21)</f>
         <v>18171.5525715915</v>
       </c>
-      <c r="N23" s="62" t="n">
+      <c r="N23" s="60" t="n">
         <f aca="false">(N22+N21)</f>
         <v>26727.4787849327</v>
       </c>
-      <c r="O23" s="62" t="n">
+      <c r="O23" s="60" t="n">
         <f aca="false">(O22+O21)</f>
         <v>36651.5365914683</v>
       </c>
-      <c r="P23" s="62" t="n">
+      <c r="P23" s="60" t="n">
         <f aca="false">(P22+P21)</f>
         <v>49620.6086989759</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
@@ -11597,230 +11979,230 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="B25" s="55" t="n">
+        <v>214</v>
+      </c>
+      <c r="B25" s="53" t="n">
         <v>4062.57</v>
       </c>
-      <c r="C25" s="55" t="n">
+      <c r="C25" s="53" t="n">
         <v>5608.14</v>
       </c>
-      <c r="D25" s="55" t="n">
+      <c r="D25" s="53" t="n">
         <v>6029.4</v>
       </c>
-      <c r="E25" s="55" t="n">
+      <c r="E25" s="53" t="n">
         <v>7401.81</v>
       </c>
-      <c r="F25" s="55" t="n">
+      <c r="F25" s="53" t="n">
         <v>7555.78</v>
       </c>
-      <c r="G25" s="55" t="n">
+      <c r="G25" s="53" t="n">
         <v>10420.14</v>
       </c>
-      <c r="H25" s="55" t="n">
+      <c r="H25" s="53" t="n">
         <v>11899.5</v>
       </c>
-      <c r="I25" s="55" t="n">
+      <c r="I25" s="53" t="n">
         <v>15017.58</v>
       </c>
-      <c r="J25" s="55" t="n">
+      <c r="J25" s="53" t="n">
         <v>17226.28</v>
       </c>
-      <c r="K25" s="55" t="n">
+      <c r="K25" s="53" t="n">
         <v>20356.25</v>
       </c>
-      <c r="L25" s="58" t="n">
+      <c r="L25" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="M25" s="58" t="n">
+      <c r="M25" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="N25" s="58" t="n">
+      <c r="N25" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="O25" s="58" t="n">
+      <c r="O25" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="P25" s="58" t="n">
+      <c r="P25" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="B26" s="55" t="n">
+        <v>215</v>
+      </c>
+      <c r="B26" s="53" t="n">
         <v>-2629.15</v>
       </c>
-      <c r="C26" s="55" t="n">
+      <c r="C26" s="53" t="n">
         <v>-3845.84</v>
       </c>
-      <c r="D26" s="55" t="n">
+      <c r="D26" s="53" t="n">
         <v>-4368.03</v>
       </c>
-      <c r="E26" s="55" t="n">
+      <c r="E26" s="53" t="n">
         <v>-748.91</v>
       </c>
-      <c r="F26" s="55" t="n">
+      <c r="F26" s="53" t="n">
         <v>-14064.12</v>
       </c>
-      <c r="G26" s="55" t="n">
+      <c r="G26" s="53" t="n">
         <v>-5493.13</v>
       </c>
-      <c r="H26" s="55" t="n">
+      <c r="H26" s="53" t="n">
         <v>-16715.93</v>
       </c>
-      <c r="I26" s="55" t="n">
+      <c r="I26" s="53" t="n">
         <v>-6946.55</v>
       </c>
-      <c r="J26" s="55" t="n">
+      <c r="J26" s="53" t="n">
         <v>-9787.53</v>
       </c>
-      <c r="K26" s="55" t="n">
+      <c r="K26" s="53" t="n">
         <v>-13190.7</v>
       </c>
-      <c r="L26" s="58" t="n">
+      <c r="L26" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="M26" s="58" t="n">
+      <c r="M26" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="N26" s="58" t="n">
+      <c r="N26" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="O26" s="58" t="n">
+      <c r="O26" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="P26" s="58" t="n">
+      <c r="P26" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="B27" s="55" t="n">
+        <v>216</v>
+      </c>
+      <c r="B27" s="53" t="n">
         <v>-1324.71</v>
       </c>
-      <c r="C27" s="55" t="n">
+      <c r="C27" s="53" t="n">
         <v>-1889.03</v>
       </c>
-      <c r="D27" s="55" t="n">
+      <c r="D27" s="53" t="n">
         <v>2313.34</v>
       </c>
-      <c r="E27" s="55" t="n">
+      <c r="E27" s="53" t="n">
         <v>-4255.63</v>
       </c>
-      <c r="F27" s="55" t="n">
+      <c r="F27" s="53" t="n">
         <v>3513.85</v>
       </c>
-      <c r="G27" s="55" t="n">
+      <c r="G27" s="53" t="n">
         <v>-585.77</v>
       </c>
-      <c r="H27" s="55" t="n">
+      <c r="H27" s="53" t="n">
         <v>-2733.8</v>
       </c>
-      <c r="I27" s="55" t="n">
+      <c r="I27" s="53" t="n">
         <v>-7800.11</v>
       </c>
-      <c r="J27" s="55" t="n">
+      <c r="J27" s="53" t="n">
         <v>-6915.52</v>
       </c>
-      <c r="K27" s="55" t="n">
+      <c r="K27" s="53" t="n">
         <v>-5483.4</v>
       </c>
-      <c r="L27" s="58" t="n">
+      <c r="L27" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="M27" s="58" t="n">
+      <c r="M27" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="N27" s="58" t="n">
+      <c r="N27" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="O27" s="58" t="n">
+      <c r="O27" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="P27" s="58" t="n">
+      <c r="P27" s="56" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="B28" s="65" t="n">
+        <v>217</v>
+      </c>
+      <c r="B28" s="63" t="n">
         <f aca="false">(B9-B25)</f>
         <v>-10025.47</v>
       </c>
-      <c r="C28" s="65" t="n">
+      <c r="C28" s="63" t="n">
         <f aca="false">(C9-C25)</f>
         <v>-1722.59</v>
       </c>
-      <c r="D28" s="65" t="n">
+      <c r="D28" s="63" t="n">
         <f aca="false">(D9-D25)</f>
         <v>-1384.01</v>
       </c>
-      <c r="E28" s="65" t="n">
+      <c r="E28" s="63" t="n">
         <f aca="false">(E9-E25)</f>
         <v>-505.62</v>
       </c>
-      <c r="F28" s="65" t="n">
+      <c r="F28" s="63" t="n">
         <f aca="false">(F9-F25)</f>
         <v>3450.4</v>
       </c>
-      <c r="G28" s="65" t="n">
+      <c r="G28" s="63" t="n">
         <f aca="false">(G9-G25)</f>
         <v>-4415.24</v>
       </c>
-      <c r="H28" s="65" t="n">
+      <c r="H28" s="63" t="n">
         <f aca="false">(H9-H25)</f>
         <v>-2010.62</v>
       </c>
-      <c r="I28" s="65" t="n">
+      <c r="I28" s="63" t="n">
         <f aca="false">(I9-I25)</f>
         <v>934.630000000001</v>
       </c>
-      <c r="J28" s="65" t="n">
+      <c r="J28" s="63" t="n">
         <f aca="false">(J9-J25)</f>
         <v>1187.25</v>
       </c>
-      <c r="K28" s="65" t="n">
+      <c r="K28" s="63" t="n">
         <f aca="false">(K9-K25)</f>
         <v>-1981.49000000001</v>
       </c>
-      <c r="L28" s="66" t="n">
+      <c r="L28" s="64" t="n">
         <f aca="false">(L9-L25)</f>
         <v>19244.3939067476</v>
       </c>
-      <c r="M28" s="66" t="n">
+      <c r="M28" s="64" t="n">
         <f aca="false">(M9-M25)</f>
         <v>23618.5122156429</v>
       </c>
-      <c r="N28" s="66" t="n">
+      <c r="N28" s="64" t="n">
         <f aca="false">(N9-N25)</f>
         <v>26965.3844400563</v>
       </c>
-      <c r="O28" s="66" t="n">
+      <c r="O28" s="64" t="n">
         <f aca="false">(O9-O25)</f>
         <v>30923.1096120272</v>
       </c>
-      <c r="P28" s="66" t="n">
+      <c r="P28" s="64" t="n">
         <f aca="false">(P9-P25)</f>
         <v>34652.3382657155</v>
       </c>
@@ -11851,44 +12233,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>5</v>
@@ -11900,18 +12282,18 @@
         <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -11931,9 +12313,9 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="B6" s="52" t="n">
+        <v>220</v>
+      </c>
+      <c r="B6" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
@@ -11996,36 +12378,36 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="B7" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="55" t="n">
+        <v>202</v>
+      </c>
+      <c r="B7" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="53" t="n">
         <v>2804.88</v>
       </c>
-      <c r="D7" s="55" t="n">
+      <c r="D7" s="53" t="n">
         <v>6824.89</v>
       </c>
-      <c r="E7" s="55" t="n">
+      <c r="E7" s="53" t="n">
         <v>6273.37</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="53" t="n">
         <v>17683.79</v>
       </c>
-      <c r="G7" s="55" t="n">
+      <c r="G7" s="53" t="n">
         <v>17361.26</v>
       </c>
-      <c r="H7" s="55" t="n">
+      <c r="H7" s="53" t="n">
         <v>13095.52</v>
       </c>
-      <c r="I7" s="55" t="n">
+      <c r="I7" s="53" t="n">
         <v>6812.54</v>
       </c>
-      <c r="J7" s="55" t="n">
+      <c r="J7" s="53" t="n">
         <v>18847.44</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="53" t="n">
         <v>47553.56</v>
       </c>
       <c r="L7" s="33" t="n">
@@ -12051,7 +12433,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Income Statement'!B11</f>
@@ -12116,72 +12498,72 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="B9" s="61" t="n">
+        <v>222</v>
+      </c>
+      <c r="B9" s="59" t="n">
         <f aca="false">((B6+B7)-B8)</f>
         <v>-1160.19</v>
       </c>
-      <c r="C9" s="61" t="n">
+      <c r="C9" s="59" t="n">
         <f aca="false">((C6+C7)-C8)</f>
         <v>22670.01</v>
       </c>
-      <c r="D9" s="61" t="n">
+      <c r="D9" s="59" t="n">
         <f aca="false">((D6+D7)-D8)</f>
         <v>28121.42</v>
       </c>
-      <c r="E9" s="61" t="n">
+      <c r="E9" s="59" t="n">
         <f aca="false">((E6+E7)-E8)</f>
         <v>32714.51</v>
       </c>
-      <c r="F9" s="61" t="n">
+      <c r="F9" s="59" t="n">
         <f aca="false">((F6+F7)-F8)</f>
         <v>48290.96</v>
       </c>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="59" t="n">
         <f aca="false">((G6+G7)-G8)</f>
         <v>62552.92</v>
       </c>
-      <c r="H9" s="61" t="n">
+      <c r="H9" s="59" t="n">
         <f aca="false">((H6+H7)-H8)</f>
         <v>72223.73</v>
       </c>
-      <c r="I9" s="61" t="n">
+      <c r="I9" s="59" t="n">
         <f aca="false">((I6+I7)-I8)</f>
         <v>75147.81</v>
       </c>
-      <c r="J9" s="61" t="n">
+      <c r="J9" s="59" t="n">
         <f aca="false">((J6+J7)-J8)</f>
         <v>89616.32</v>
       </c>
-      <c r="K9" s="61" t="n">
+      <c r="K9" s="59" t="n">
         <f aca="false">((K6+K7)-K8)</f>
         <v>131652.5</v>
       </c>
-      <c r="L9" s="62" t="n">
+      <c r="L9" s="60" t="n">
         <f aca="false">((L6+L7)-L8)</f>
         <v>138607.49234293</v>
       </c>
-      <c r="M9" s="62" t="n">
+      <c r="M9" s="60" t="n">
         <f aca="false">((M6+M7)-M8)</f>
         <v>146526.286735102</v>
       </c>
-      <c r="N9" s="62" t="n">
+      <c r="N9" s="60" t="n">
         <f aca="false">((N6+N7)-N8)</f>
         <v>155685.272967819</v>
       </c>
-      <c r="O9" s="62" t="n">
+      <c r="O9" s="60" t="n">
         <f aca="false">((O6+O7)-O8)</f>
         <v>166228.332603398</v>
       </c>
-      <c r="P9" s="62" t="n">
+      <c r="P9" s="60" t="n">
         <f aca="false">((P6+P7)-P8)</f>
         <v>176959.616310316</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -12201,7 +12583,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B11" s="29" t="n">
         <f aca="false">(((('Balance Sheet'!B7+'Balance Sheet'!B8)+'Balance Sheet'!B9)-'Balance Sheet'!B20)-'Balance Sheet'!B21)</f>
@@ -12266,137 +12648,137 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="B12" s="52" t="n">
+        <v>224</v>
+      </c>
+      <c r="B12" s="50" t="n">
         <f aca="false">(B11-0)</f>
         <v>11034.61</v>
       </c>
-      <c r="C12" s="52" t="n">
+      <c r="C12" s="50" t="n">
         <f aca="false">(C11-B11)</f>
         <v>976.439999999999</v>
       </c>
-      <c r="D12" s="52" t="n">
+      <c r="D12" s="50" t="n">
         <f aca="false">(D11-C11)</f>
         <v>718.310000000001</v>
       </c>
-      <c r="E12" s="52" t="n">
+      <c r="E12" s="50" t="n">
         <f aca="false">(E11-D11)</f>
         <v>-1452.78</v>
       </c>
-      <c r="F12" s="52" t="n">
+      <c r="F12" s="50" t="n">
         <f aca="false">(F11-E11)</f>
         <v>-3904.54</v>
       </c>
-      <c r="G12" s="52" t="n">
+      <c r="G12" s="50" t="n">
         <f aca="false">(G11-F11)</f>
         <v>1980.43</v>
       </c>
-      <c r="H12" s="52" t="n">
+      <c r="H12" s="50" t="n">
         <f aca="false">(H11-G11)</f>
         <v>-1155.32</v>
       </c>
-      <c r="I12" s="52" t="n">
+      <c r="I12" s="50" t="n">
         <f aca="false">(I11-H11)</f>
         <v>-3953.11</v>
       </c>
-      <c r="J12" s="52" t="n">
+      <c r="J12" s="50" t="n">
         <f aca="false">(J11-I11)</f>
         <v>-2942.29</v>
       </c>
-      <c r="K12" s="52" t="n">
+      <c r="K12" s="50" t="n">
         <f aca="false">(K11-J11)</f>
         <v>-51.1699999999946</v>
       </c>
-      <c r="L12" s="58" t="n">
+      <c r="L12" s="56" t="n">
         <f aca="false">(L11-K11)</f>
         <v>2085.83221304273</v>
       </c>
-      <c r="M12" s="58" t="n">
+      <c r="M12" s="56" t="n">
         <f aca="false">(M11-L11)</f>
         <v>434.400870138172</v>
       </c>
-      <c r="N12" s="58" t="n">
+      <c r="N12" s="56" t="n">
         <f aca="false">(N11-M11)</f>
         <v>545.636653136276</v>
       </c>
-      <c r="O12" s="58" t="n">
+      <c r="O12" s="56" t="n">
         <f aca="false">(O11-N11)</f>
         <v>639.266205948567</v>
       </c>
-      <c r="P12" s="58" t="n">
+      <c r="P12" s="56" t="n">
         <f aca="false">(P11-O11)</f>
         <v>599.146057419937</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="B13" s="50" t="n">
+        <v>225</v>
+      </c>
+      <c r="B13" s="48" t="n">
         <f aca="false">(IFERROR((B11)/('Income Statement'!B6),0)*365)</f>
         <v>477.244414557993</v>
       </c>
-      <c r="C13" s="50" t="n">
+      <c r="C13" s="48" t="n">
         <f aca="false">(IFERROR((C11)/('Income Statement'!C6),0)*365)</f>
         <v>387.180847587557</v>
       </c>
-      <c r="D13" s="50" t="n">
+      <c r="D13" s="48" t="n">
         <f aca="false">(IFERROR((D11)/('Income Statement'!D6),0)*365)</f>
         <v>425.265838263722</v>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="48" t="n">
         <f aca="false">(IFERROR((E11)/('Income Statement'!E6),0)*365)</f>
         <v>346.6628007752</v>
       </c>
-      <c r="F13" s="50" t="n">
+      <c r="F13" s="48" t="n">
         <f aca="false">(IFERROR((F11)/('Income Statement'!F6),0)*365)</f>
         <v>214.412778096513</v>
       </c>
-      <c r="G13" s="50" t="n">
+      <c r="G13" s="48" t="n">
         <f aca="false">(IFERROR((G11)/('Income Statement'!G6),0)*365)</f>
         <v>199.409628250595</v>
       </c>
-      <c r="H13" s="50" t="n">
+      <c r="H13" s="48" t="n">
         <f aca="false">(IFERROR((H11)/('Income Statement'!H6),0)*365)</f>
         <v>143.486124292691</v>
       </c>
-      <c r="I13" s="50" t="n">
+      <c r="I13" s="48" t="n">
         <f aca="false">(IFERROR((I11)/('Income Statement'!I6),0)*365)</f>
         <v>57.9948379966575</v>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="J13" s="48" t="n">
         <f aca="false">(IFERROR((J11)/('Income Statement'!J6),0)*365)</f>
         <v>15.5909304345514</v>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="K13" s="48" t="n">
         <f aca="false">(IFERROR((K11)/('Income Statement'!K6),0)*365)</f>
         <v>11.7839841572789</v>
       </c>
-      <c r="L13" s="67" t="n">
+      <c r="L13" s="65" t="n">
         <f aca="false">(IFERROR((L11)/('Income Statement'!L6),0)*365)</f>
         <v>25.89867</v>
       </c>
-      <c r="M13" s="67" t="n">
+      <c r="M13" s="65" t="n">
         <f aca="false">(IFERROR((M11)/('Income Statement'!M6),0)*365)</f>
         <v>25.89867</v>
       </c>
-      <c r="N13" s="67" t="n">
+      <c r="N13" s="65" t="n">
         <f aca="false">(IFERROR((N11)/('Income Statement'!N6),0)*365)</f>
         <v>25.89867</v>
       </c>
-      <c r="O13" s="67" t="n">
+      <c r="O13" s="65" t="n">
         <f aca="false">(IFERROR((O11)/('Income Statement'!O6),0)*365)</f>
         <v>25.89867</v>
       </c>
-      <c r="P13" s="67" t="n">
+      <c r="P13" s="65" t="n">
         <f aca="false">(IFERROR((P11)/('Income Statement'!P6),0)*365)</f>
         <v>25.89867</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
@@ -12416,9 +12798,9 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="B15" s="52" t="n">
+        <v>227</v>
+      </c>
+      <c r="B15" s="50" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
@@ -12481,7 +12863,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">(('Cash Flow'!B15+'Cash Flow'!B17)+'Cash Flow'!B18)</f>
@@ -12546,7 +12928,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">(((0+'Cash Flow'!B9)+'Cash Flow'!B13)+B16)</f>
@@ -12611,7 +12993,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">MAX((Drivers!B29-B17),0)</f>
@@ -12676,7 +13058,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">MIN(0,MAX((B17-Drivers!B29),0))</f>
@@ -12741,7 +13123,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">AVERAGE(0,'Balance Sheet'!B19)</f>
@@ -12806,7 +13188,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
@@ -12826,36 +13208,36 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="B22" s="55" t="n">
+        <v>234</v>
+      </c>
+      <c r="B22" s="53" t="n">
         <v>269.22</v>
       </c>
-      <c r="C22" s="55" t="n">
+      <c r="C22" s="53" t="n">
         <v>414.19</v>
       </c>
-      <c r="D22" s="55" t="n">
+      <c r="D22" s="53" t="n">
         <v>41.42</v>
       </c>
-      <c r="E22" s="55" t="n">
+      <c r="E22" s="53" t="n">
         <v>650.16</v>
       </c>
-      <c r="F22" s="55" t="n">
+      <c r="F22" s="53" t="n">
         <v>1015.88</v>
       </c>
-      <c r="G22" s="55" t="n">
+      <c r="G22" s="53" t="n">
         <v>1056.18</v>
       </c>
-      <c r="H22" s="55" t="n">
+      <c r="H22" s="53" t="n">
         <v>1080.08</v>
       </c>
-      <c r="I22" s="55" t="n">
+      <c r="I22" s="53" t="n">
         <v>1296.09</v>
       </c>
-      <c r="J22" s="55" t="n">
+      <c r="J22" s="53" t="n">
         <v>1512.1</v>
       </c>
-      <c r="K22" s="55" t="n">
+      <c r="K22" s="53" t="n">
         <v>1727.96</v>
       </c>
       <c r="L22" s="33" t="n">
@@ -12881,62 +13263,62 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="B23" s="68" t="n">
+        <v>235</v>
+      </c>
+      <c r="B23" s="66" t="n">
         <v>207.0952</v>
       </c>
-      <c r="C23" s="68" t="n">
+      <c r="C23" s="66" t="n">
         <v>207.0952</v>
       </c>
-      <c r="D23" s="68" t="n">
+      <c r="D23" s="66" t="n">
         <v>207.0952</v>
       </c>
-      <c r="E23" s="68" t="n">
+      <c r="E23" s="66" t="n">
         <v>203.1752</v>
       </c>
-      <c r="F23" s="68" t="n">
+      <c r="F23" s="66" t="n">
         <v>203.1752</v>
       </c>
-      <c r="G23" s="68" t="n">
+      <c r="G23" s="66" t="n">
         <v>211.2373</v>
       </c>
-      <c r="H23" s="68" t="n">
+      <c r="H23" s="66" t="n">
         <v>216.0139</v>
       </c>
-      <c r="I23" s="68" t="n">
+      <c r="I23" s="66" t="n">
         <v>216.0139</v>
       </c>
-      <c r="J23" s="68" t="n">
+      <c r="J23" s="66" t="n">
         <v>216.0139</v>
       </c>
-      <c r="K23" s="68" t="n">
+      <c r="K23" s="66" t="n">
         <v>230.3959</v>
       </c>
-      <c r="L23" s="69" t="n">
+      <c r="L23" s="67" t="n">
         <f aca="false">K23</f>
         <v>230.3959</v>
       </c>
-      <c r="M23" s="69" t="n">
+      <c r="M23" s="67" t="n">
         <f aca="false">L23</f>
         <v>230.3959</v>
       </c>
-      <c r="N23" s="69" t="n">
+      <c r="N23" s="67" t="n">
         <f aca="false">M23</f>
         <v>230.3959</v>
       </c>
-      <c r="O23" s="69" t="n">
+      <c r="O23" s="67" t="n">
         <f aca="false">N23</f>
         <v>230.3959</v>
       </c>
-      <c r="P23" s="69" t="n">
+      <c r="P23" s="67" t="n">
         <f aca="false">O23</f>
         <v>230.3959</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B24" s="29" t="n">
         <f aca="false">('Balance Sheet'!B15+'Balance Sheet'!B16)</f>
@@ -13001,65 +13383,65 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="B25" s="70" t="n">
+        <v>237</v>
+      </c>
+      <c r="B25" s="68" t="n">
         <f aca="false">IFERROR((B24)/(B23),0)</f>
         <v>84.6276495061209</v>
       </c>
-      <c r="C25" s="70" t="n">
+      <c r="C25" s="68" t="n">
         <f aca="false">IFERROR((C24)/(C23),0)</f>
         <v>100.934014887839</v>
       </c>
-      <c r="D25" s="70" t="n">
+      <c r="D25" s="68" t="n">
         <f aca="false">IFERROR((D24)/(D23),0)</f>
         <v>117.686551885317</v>
       </c>
-      <c r="E25" s="70" t="n">
+      <c r="E25" s="68" t="n">
         <f aca="false">IFERROR((E24)/(E23),0)</f>
         <v>125.295606944155</v>
       </c>
-      <c r="F25" s="70" t="n">
+      <c r="F25" s="68" t="n">
         <f aca="false">IFERROR((F24)/(F23),0)</f>
         <v>149.829949718273</v>
       </c>
-      <c r="G25" s="70" t="n">
+      <c r="G25" s="68" t="n">
         <f aca="false">IFERROR((G24)/(G23),0)</f>
         <v>197.984399535499</v>
       </c>
-      <c r="H25" s="70" t="n">
+      <c r="H25" s="68" t="n">
         <f aca="false">IFERROR((H24)/(H23),0)</f>
         <v>210.122543040054</v>
       </c>
-      <c r="I25" s="70" t="n">
+      <c r="I25" s="68" t="n">
         <f aca="false">IFERROR((I24)/(I23),0)</f>
         <v>244.327980745683</v>
       </c>
-      <c r="J25" s="70" t="n">
+      <c r="J25" s="68" t="n">
         <f aca="false">IFERROR((J24)/(J23),0)</f>
         <v>288.26320898794</v>
       </c>
-      <c r="K25" s="70" t="n">
+      <c r="K25" s="68" t="n">
         <f aca="false">IFERROR((K24)/(K23),0)</f>
         <v>416.495128602549</v>
       </c>
-      <c r="L25" s="69" t="n">
+      <c r="L25" s="67" t="n">
         <f aca="false">IFERROR((L24)/(L23),0)</f>
         <v>467.44609242756</v>
       </c>
-      <c r="M25" s="69" t="n">
+      <c r="M25" s="67" t="n">
         <f aca="false">IFERROR((M24)/(M23),0)</f>
         <v>527.020016528861</v>
       </c>
-      <c r="N25" s="69" t="n">
+      <c r="N25" s="67" t="n">
         <f aca="false">IFERROR((N24)/(N23),0)</f>
         <v>597.742872203097</v>
       </c>
-      <c r="O25" s="69" t="n">
+      <c r="O25" s="67" t="n">
         <f aca="false">IFERROR((O24)/(O23),0)</f>
         <v>681.552738977197</v>
       </c>
-      <c r="P25" s="69" t="n">
+      <c r="P25" s="67" t="n">
         <f aca="false">IFERROR((P24)/(P23),0)</f>
         <v>776.805442300519</v>
       </c>

--- a/reports/ADANIPORTS/Adani_Ports_and_Special_Economic_Zone_Ltd_ERIP_Model.xlsx
+++ b/reports/ADANIPORTS/Adani_Ports_and_Special_Economic_Zone_Ltd_ERIP_Model.xlsx
@@ -2024,10 +2024,10 @@
                   <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1144.63376284308</c:v>
+                  <c:v>1144.63373631482</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1616.01193166881</c:v>
+                  <c:v>1616.01190514055</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1695</c:v>
@@ -2038,11 +2038,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="85098675"/>
-        <c:axId val="10175127"/>
+        <c:axId val="13354405"/>
+        <c:axId val="25379532"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85098675"/>
+        <c:axId val="13354405"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2075,7 +2075,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10175127"/>
+        <c:crossAx val="25379532"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2083,7 +2083,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10175127"/>
+        <c:axId val="25379532"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2116,7 +2116,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85098675"/>
+        <c:crossAx val="13354405"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2682,11 +2682,11 @@
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">'Income Statement'!L18</f>
-        <v>13708.5995897903</v>
+        <v>13708.5739659295</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">'Income Statement'!M18</f>
-        <v>16028.6481390641</v>
+        <v>16028.6234032179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2706,11 +2706,11 @@
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">'Income Statement'!L19</f>
-        <v>59.5001889781471</v>
+        <v>59.5000777614946</v>
       </c>
       <c r="G8" s="13" t="n">
         <f aca="false">'Income Statement'!M19</f>
-        <v>69.5700233340269</v>
+        <v>69.5699159716727</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">DCF!B45</f>
-        <v>512.779689751377</v>
+        <v>512.7791828375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B17" s="19" t="n">
         <f aca="false">DCF!B35</f>
-        <v>0.735737962866123</v>
+        <v>0.735737818260356</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">DCF!B34</f>
-        <v>163736.521476244</v>
+        <v>163736.409753871</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">DCF!B43</f>
-        <v>118142.338121989</v>
+        <v>118142.22133111</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B25" s="17" t="n">
         <f aca="false">DCF!B68</f>
-        <v>1144.63376284308</v>
+        <v>1144.63373631482</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B26" s="17" t="n">
         <f aca="false">DCF!B70</f>
-        <v>1616.01193166881</v>
+        <v>1616.01190514055</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3184,23 +3184,23 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Income Statement'!L12</f>
-        <v>19885.863923755</v>
+        <v>19885.8344204023</v>
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">'Income Statement'!M12</f>
-        <v>22798.9831084688</v>
+        <v>22798.9537545156</v>
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false">'Income Statement'!N12</f>
-        <v>26496.5052566821</v>
+        <v>26496.4758274911</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">'Income Statement'!O12</f>
-        <v>30797.4793601757</v>
+        <v>30797.4495821752</v>
       </c>
       <c r="F8" s="9" t="n">
         <f aca="false">'Income Statement'!P12</f>
-        <v>34608.7651418723</v>
+        <v>34608.7347250846</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3234,23 +3234,23 @@
       </c>
       <c r="B10" s="50" t="n">
         <f aca="false">B8*(1-B9)</f>
-        <v>16206.9790978603</v>
+        <v>16206.9550526279</v>
       </c>
       <c r="C10" s="50" t="n">
         <f aca="false">C8*(1-C9)</f>
-        <v>18581.1712334021</v>
+        <v>18581.1473099302</v>
       </c>
       <c r="D10" s="50" t="n">
         <f aca="false">D8*(1-D9)</f>
-        <v>21594.6517841959</v>
+        <v>21594.6277994052</v>
       </c>
       <c r="E10" s="50" t="n">
         <f aca="false">E8*(1-E9)</f>
-        <v>25099.9456785432</v>
+        <v>25099.9214094728</v>
       </c>
       <c r="F10" s="50" t="n">
         <f aca="false">F8*(1-F9)</f>
-        <v>28206.1435906259</v>
+        <v>28206.118800944</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3259,23 +3259,23 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">'Income Statement'!L11</f>
-        <v>7621.62653</v>
+        <v>7621.65603335271</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">'Income Statement'!M11</f>
-        <v>8024.2649467169</v>
+        <v>8024.29430067014</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">'Income Statement'!N11</f>
-        <v>8482.69979166854</v>
+        <v>8482.72922085962</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">'Income Statement'!O11</f>
-        <v>9012.93182265299</v>
+        <v>9012.96160065347</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">'Income Statement'!P11</f>
-        <v>9623.29063107591</v>
+        <v>9623.32104786357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3309,23 +3309,23 @@
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">-Schedules!L12</f>
-        <v>-2085.83221304273</v>
+        <v>-2085.8511002293</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">-Schedules!M12</f>
-        <v>-434.400870138172</v>
+        <v>-434.403329249853</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">-Schedules!N12</f>
-        <v>-545.636653136276</v>
+        <v>-545.639741945626</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">-Schedules!O12</f>
-        <v>-639.266205948567</v>
+        <v>-639.269824788018</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">-Schedules!P12</f>
-        <v>-599.146057419937</v>
+        <v>-599.149449142125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3334,23 +3334,23 @@
       </c>
       <c r="B14" s="61" t="n">
         <f aca="false">B10+B11+B12+B13</f>
-        <v>7166.15454188759</v>
+        <v>7166.14111282128</v>
       </c>
       <c r="C14" s="61" t="n">
         <f aca="false">C10+C11+C12+C13</f>
-        <v>10227.9759710917</v>
+        <v>10227.9789424613</v>
       </c>
       <c r="D14" s="61" t="n">
         <f aca="false">D10+D11+D12+D13</f>
-        <v>11890.0288983426</v>
+        <v>11890.0312539337</v>
       </c>
       <c r="E14" s="61" t="n">
         <f aca="false">E10+E11+E12+E13</f>
-        <v>13917.619837016</v>
+        <v>13917.6217271066</v>
       </c>
       <c r="F14" s="61" t="n">
         <f aca="false">F10+F11+F12+F13</f>
-        <v>16875.713826288</v>
+        <v>16875.7160616716</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3471,23 +3471,23 @@
       </c>
       <c r="B24" s="50" t="n">
         <f aca="false">B14*B21*B23</f>
-        <v>6750.11529676626</v>
+        <v>6750.10264733965</v>
       </c>
       <c r="C24" s="50" t="n">
         <f aca="false">C14*C21*C23</f>
-        <v>8565.23446375993</v>
+        <v>8565.23695208</v>
       </c>
       <c r="D24" s="50" t="n">
         <f aca="false">D14*D21*D23</f>
-        <v>8845.90059758666</v>
+        <v>8845.90235009072</v>
       </c>
       <c r="E24" s="50" t="n">
         <f aca="false">E14*E21*E23</f>
-        <v>9198.85349394267</v>
+        <v>9198.85474319844</v>
       </c>
       <c r="F24" s="50" t="n">
         <f aca="false">F14*F21*F23</f>
-        <v>9909.24286647165</v>
+        <v>9909.2441790655</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="B31" s="50" t="n">
         <f aca="false">SUM(B24:F24)</f>
-        <v>43269.3467185272</v>
+        <v>43269.3408717743</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B32" s="50" t="n">
         <f aca="false">F10*(1+$B$28)*(1-$B$28/$B$29)/($B$27-$B$28)</f>
-        <v>205158.920218951</v>
+        <v>205158.73990985</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B33" s="50" t="n">
         <f aca="false">$B$32/(1+$B$27)^F22</f>
-        <v>120467.174757717</v>
+        <v>120467.068882097</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B34" s="61" t="n">
         <f aca="false">$B$31+$B$33</f>
-        <v>163736.521476244</v>
+        <v>163736.409753871</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="B35" s="15" t="n">
         <f aca="false">$B$33/$B$34</f>
-        <v>0.735737962866123</v>
+        <v>0.735737818260356</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B40" s="50" t="n">
         <f aca="false">$B$34-$B$36-$B$37-$B$38+$B$39</f>
-        <v>113015.181476244</v>
+        <v>113015.069753871</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="B43" s="61" t="n">
         <f aca="false">$B$40*$B$42</f>
-        <v>118142.338121989</v>
+        <v>118142.22133111</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="B45" s="46" t="n">
         <f aca="false">$B$43/$B$44</f>
-        <v>512.779689751377</v>
+        <v>512.7791828375</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="B47" s="15" t="n">
         <f aca="false">$B$45/$B$46-1</f>
-        <v>-0.697475109291223</v>
+        <v>-0.697475408355457</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B52" s="45" t="n">
         <f aca="false">IF($B$50="Exit multiple",$B$68,$B$45)</f>
-        <v>512.779689751377</v>
+        <v>512.7791828375</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B53" s="13" t="n">
         <f aca="false">IFERROR(Schedules!L22/Schedules!L23,0)</f>
-        <v>8.54922515313609</v>
+        <v>8.54921468877721</v>
       </c>
       <c r="C53" s="69" t="s">
         <v>306</v>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B54" s="45" t="n">
         <f aca="false">$B$52*(1+$B$41)^($B$51/12)-$B$53*$B$51/12</f>
-        <v>572.868589969911</v>
+        <v>572.868025667436</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B64" s="82" t="n">
         <f aca="false">$B$32/$B$63</f>
-        <v>4.63824067486421</v>
+        <v>4.6382365984292</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B68" s="46" t="n">
         <f aca="false">($B$31+$B$67-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
-        <v>1144.63376284308</v>
+        <v>1144.63373631482</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B70" s="45" t="n">
         <f aca="false">($B$31+$B$69*$B$63/(1+$B$27)^F22-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
-        <v>1616.01193166881</v>
+        <v>1616.01190514055</v>
       </c>
     </row>
   </sheetData>
@@ -3972,23 +3972,23 @@
       </c>
       <c r="B9" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A9-B$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>636.951049890538</v>
+        <v>636.950438502526</v>
       </c>
       <c r="C9" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A9-C$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>632.413747405703</v>
+        <v>632.413140005414</v>
       </c>
       <c r="D9" s="45" t="n">
         <f aca="false">IF(D$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A9-D$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>626.617252338779</v>
+        <v>626.616650032887</v>
       </c>
       <c r="E9" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A9-E$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>619.249967684149</v>
+        <v>619.249371853181</v>
       </c>
       <c r="F9" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A9)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A9-F$8)/(1+$A9)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>609.888244233744</v>
+        <v>609.887656630563</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3998,23 +3998,23 @@
       </c>
       <c r="B10" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A10-B$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>580.809643434919</v>
+        <v>580.809079036248</v>
       </c>
       <c r="C10" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A10-C$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>573.979710054484</v>
+        <v>573.979151658472</v>
       </c>
       <c r="D10" s="45" t="n">
         <f aca="false">IF(D$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A10-D$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>565.665588926925</v>
+        <v>565.665037837988</v>
       </c>
       <c r="E10" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A10-E$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>555.527992675812</v>
+        <v>555.527450496557</v>
       </c>
       <c r="F10" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A10)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A10-F$8)/(1+$A10)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>543.115688188434</v>
+        <v>543.115156918047</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4024,23 +4024,23 @@
       </c>
       <c r="B11" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A11-B$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>531.276875408261</v>
+        <v>531.276352237665</v>
       </c>
       <c r="C11" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A11-C$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>522.823843890574</v>
+        <v>522.823328149138</v>
       </c>
       <c r="D11" s="46" t="n">
         <f aca="false">IF(D$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A11-D$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>512.779689751377</v>
+        <v>512.7791828375</v>
       </c>
       <c r="E11" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A11-E$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>500.806434287101</v>
+        <v>500.805937896222</v>
       </c>
       <c r="F11" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A11)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A11-F$8)/(1+$A11)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>486.463082260638</v>
+        <v>486.462598475776</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4050,23 +4050,23 @@
       </c>
       <c r="B12" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A12-B$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>487.257658007067</v>
+        <v>487.257171264552</v>
       </c>
       <c r="C12" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A12-C$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>477.670460418578</v>
+        <v>477.669982102013</v>
       </c>
       <c r="D12" s="45" t="n">
         <f aca="false">IF(D$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A12-D$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>466.458902463789</v>
+        <v>466.458434000786</v>
       </c>
       <c r="E12" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A12-E$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>453.300760319635</v>
+        <v>453.300303420998</v>
       </c>
       <c r="F12" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A12)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A12-F$8)/(1+$A12)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>437.782549826056</v>
+        <v>437.78210656599</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4076,23 +4076,23 @@
       </c>
       <c r="B13" s="45" t="n">
         <f aca="false">IF(B$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A13-B$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>447.885992415038</v>
+        <v>447.885538060572</v>
       </c>
       <c r="C13" s="45" t="n">
         <f aca="false">IF(C$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A13-C$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>437.525441123469</v>
+        <v>437.524995874636</v>
       </c>
       <c r="D13" s="45" t="n">
         <f aca="false">IF(D$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A13-D$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>425.553118514876</v>
+        <v>425.552683788221</v>
       </c>
       <c r="E13" s="45" t="n">
         <f aca="false">IF(E$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A13-E$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>411.66912816923</v>
+        <v>411.668705644871</v>
       </c>
       <c r="F13" s="45" t="n">
         <f aca="false">IF(F$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A13)^DCF!$B$22:$F$22)+DCF!$F$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A13-F$8)/(1+$A13)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>395.494253196338</v>
+        <v>395.493844887676</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4132,23 +4132,23 @@
       </c>
       <c r="B17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>706.953796531303</v>
+        <v>706.953770501753</v>
       </c>
       <c r="C17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>952.298488326392</v>
+        <v>952.298462296841</v>
       </c>
       <c r="D17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1197.64318012148</v>
+        <v>1197.64315409193</v>
       </c>
       <c r="E17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1442.98787191657</v>
+        <v>1442.98784588702</v>
       </c>
       <c r="F17" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A17)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A17)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1688.33256371166</v>
+        <v>1688.33253768211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4158,23 +4158,23 @@
       </c>
       <c r="B18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>689.90384782781</v>
+        <v>689.903821545811</v>
       </c>
       <c r="C18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>930.361508228743</v>
+        <v>930.361481946744</v>
       </c>
       <c r="D18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1170.81916862968</v>
+        <v>1170.81914234768</v>
       </c>
       <c r="E18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1411.27682903061</v>
+        <v>1411.27680274861</v>
       </c>
       <c r="F18" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A18)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A18)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1651.73448943154</v>
+        <v>1651.73446314954</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4184,23 +4184,23 @@
       </c>
       <c r="B19" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>673.255594017346</v>
+        <v>673.255567489086</v>
       </c>
       <c r="C19" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>908.944678430213</v>
+        <v>908.944651901953</v>
       </c>
       <c r="D19" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1144.63376284308</v>
+        <v>1144.63373631482</v>
       </c>
       <c r="E19" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1380.32284725595</v>
+        <v>1380.32282072769</v>
       </c>
       <c r="F19" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A19)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A19)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1616.01193166881</v>
+        <v>1616.01190514055</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4210,23 +4210,23 @@
       </c>
       <c r="B20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>656.997743702566</v>
+        <v>656.997716934073</v>
       </c>
       <c r="C20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>888.033329132418</v>
+        <v>888.033302363924</v>
       </c>
       <c r="D20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1119.06891456227</v>
+        <v>1119.06888779378</v>
       </c>
       <c r="E20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1350.10449999212</v>
+        <v>1350.10447322363</v>
       </c>
       <c r="F20" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A20)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A20)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1581.14008542197</v>
+        <v>1581.14005865348</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+B$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>641.119372178411</v>
+        <v>641.119345175556</v>
       </c>
       <c r="C21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+C$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>867.613267921581</v>
+        <v>867.613240918726</v>
       </c>
       <c r="D21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+D$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1094.10716366475</v>
+        <v>1094.1071366619</v>
       </c>
       <c r="E21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+E$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1320.60105940792</v>
+        <v>1320.60103240507</v>
       </c>
       <c r="F21" s="45" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$F$14,DCF!$B$21:$F$21,1/(1+$A21)^DCF!$B$22:$F$22)+F$16*DCF!$B$63/(1+$A21)^DCF!$F$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>1547.09495515109</v>
+        <v>1547.09492814824</v>
       </c>
     </row>
   </sheetData>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C7" s="87" t="n">
         <f aca="false">('Balance Sheet'!C6-'Cash Flow'!C23)</f>
-        <v>117.539999999997</v>
+        <v>117.539999999995</v>
       </c>
       <c r="D7" s="87" t="n">
         <f aca="false">('Balance Sheet'!D6-'Cash Flow'!D23)</f>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J7" s="87" t="n">
         <f aca="false">('Balance Sheet'!J6-'Cash Flow'!J23)</f>
-        <v>-89.5900000000102</v>
+        <v>-89.5899999999956</v>
       </c>
       <c r="K7" s="87" t="n">
         <f aca="false">('Balance Sheet'!K6-'Cash Flow'!K23)</f>
@@ -5057,23 +5057,23 @@
       </c>
       <c r="L11" s="87" t="n">
         <f aca="false">('Balance Sheet'!L6-Drivers!L29)</f>
-        <v>10550.4783685162</v>
+        <v>10550.4609841633</v>
       </c>
       <c r="M11" s="87" t="n">
         <f aca="false">('Balance Sheet'!M6-Drivers!M29)</f>
-        <v>18171.5525715915</v>
+        <v>18171.5238597045</v>
       </c>
       <c r="N11" s="87" t="n">
         <f aca="false">('Balance Sheet'!N6-Drivers!N29)</f>
-        <v>26727.4787849327</v>
+        <v>26727.4367206014</v>
       </c>
       <c r="O11" s="87" t="n">
         <f aca="false">('Balance Sheet'!O6-Drivers!O29)</f>
-        <v>36651.5365914683</v>
+        <v>36651.4790917337</v>
       </c>
       <c r="P11" s="87" t="n">
         <f aca="false">('Balance Sheet'!P6-Drivers!P29)</f>
-        <v>49620.6086989759</v>
+        <v>49620.534087577</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5187,23 +5187,23 @@
       </c>
       <c r="L13" s="87" t="n">
         <f aca="false">'Balance Sheet'!L10</f>
-        <v>138607.49234293</v>
+        <v>138607.462839577</v>
       </c>
       <c r="M13" s="87" t="n">
         <f aca="false">'Balance Sheet'!M10</f>
-        <v>146526.286735102</v>
+        <v>146526.227877796</v>
       </c>
       <c r="N13" s="87" t="n">
         <f aca="false">'Balance Sheet'!N10</f>
-        <v>155685.272967819</v>
+        <v>155685.184681322</v>
       </c>
       <c r="O13" s="87" t="n">
         <f aca="false">'Balance Sheet'!O10</f>
-        <v>166228.332603398</v>
+        <v>166228.2145389</v>
       </c>
       <c r="P13" s="87" t="n">
         <f aca="false">'Balance Sheet'!P10</f>
-        <v>176959.616310316</v>
+        <v>176959.467829031</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5252,23 +5252,23 @@
       </c>
       <c r="L14" s="87" t="n">
         <f aca="false">Schedules!L24</f>
-        <v>107697.663166331</v>
+        <v>107697.639953415</v>
       </c>
       <c r="M14" s="87" t="n">
         <f aca="false">Schedules!M24</f>
-        <v>121423.251026182</v>
+        <v>121423.205145702</v>
       </c>
       <c r="N14" s="87" t="n">
         <f aca="false">Schedules!N24</f>
-        <v>137717.507009818</v>
+        <v>137717.438845142</v>
       </c>
       <c r="O14" s="87" t="n">
         <f aca="false">Schedules!O24</f>
-        <v>157026.956694116</v>
+        <v>157026.866468116</v>
       </c>
       <c r="P14" s="87" t="n">
         <f aca="false">Schedules!P24</f>
-        <v>178972.789003726</v>
+        <v>178972.676940198</v>
       </c>
     </row>
   </sheetData>
@@ -6091,23 +6091,23 @@
       </c>
       <c r="L10" s="33" t="n">
         <f aca="false">'Income Statement'!L12</f>
-        <v>19885.863923755</v>
+        <v>19885.8344204023</v>
       </c>
       <c r="M10" s="33" t="n">
         <f aca="false">'Income Statement'!M12</f>
-        <v>22798.9831084688</v>
+        <v>22798.9537545156</v>
       </c>
       <c r="N10" s="33" t="n">
         <f aca="false">'Income Statement'!N12</f>
-        <v>26496.5052566821</v>
+        <v>26496.4758274911</v>
       </c>
       <c r="O10" s="33" t="n">
         <f aca="false">'Income Statement'!O12</f>
-        <v>30797.4793601757</v>
+        <v>30797.4495821752</v>
       </c>
       <c r="P10" s="33" t="n">
         <f aca="false">'Income Statement'!P12</f>
-        <v>34608.7651418723</v>
+        <v>34608.7347250846</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6156,23 +6156,23 @@
       </c>
       <c r="L11" s="33" t="n">
         <f aca="false">'Income Statement'!L18</f>
-        <v>13708.5995897903</v>
+        <v>13708.5739659295</v>
       </c>
       <c r="M11" s="33" t="n">
         <f aca="false">'Income Statement'!M18</f>
-        <v>16028.6481390641</v>
+        <v>16028.6234032179</v>
       </c>
       <c r="N11" s="33" t="n">
         <f aca="false">'Income Statement'!N18</f>
-        <v>19028.3213015241</v>
+        <v>19028.297338103</v>
       </c>
       <c r="O11" s="33" t="n">
         <f aca="false">'Income Statement'!O18</f>
-        <v>22549.4439953228</v>
+        <v>22549.4206733491</v>
       </c>
       <c r="P11" s="33" t="n">
         <f aca="false">'Income Statement'!P18</f>
-        <v>25628.1936920596</v>
+        <v>25628.1709647251</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6221,23 +6221,23 @@
       </c>
       <c r="L12" s="35" t="n">
         <f aca="false">'Income Statement'!L19</f>
-        <v>59.5001889781471</v>
+        <v>59.5000777614946</v>
       </c>
       <c r="M12" s="35" t="n">
         <f aca="false">'Income Statement'!M19</f>
-        <v>69.5700233340269</v>
+        <v>69.5699159716727</v>
       </c>
       <c r="N12" s="35" t="n">
         <f aca="false">'Income Statement'!N19</f>
-        <v>82.5896697880651</v>
+        <v>82.5895657783105</v>
       </c>
       <c r="O12" s="35" t="n">
         <f aca="false">'Income Statement'!O19</f>
-        <v>97.8725923305179</v>
+        <v>97.8724911048727</v>
       </c>
       <c r="P12" s="35" t="n">
         <f aca="false">'Income Statement'!P19</f>
-        <v>111.235459016673</v>
+        <v>111.235360371973</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="J14" s="29" t="n">
         <f aca="false">(((('Income Statement'!J12*(1-Drivers!J22))+'Income Statement'!J11)-Schedules!J7)-Schedules!J12)</f>
-        <v>428.318784431169</v>
+        <v>428.318784431156</v>
       </c>
       <c r="K14" s="29" t="n">
         <f aca="false">(((('Income Statement'!K12*(1-Drivers!K22))+'Income Statement'!K11)-Schedules!K7)-Schedules!K12)</f>
@@ -6306,23 +6306,23 @@
       </c>
       <c r="L14" s="30" t="n">
         <f aca="false">(((('Income Statement'!L12*(1-Drivers!L22))+'Income Statement'!L11)-Schedules!L7)-Schedules!L12)</f>
-        <v>7166.15454188759</v>
+        <v>7166.14111282128</v>
       </c>
       <c r="M14" s="30" t="n">
         <f aca="false">(((('Income Statement'!M12*(1-Drivers!M22))+'Income Statement'!M11)-Schedules!M7)-Schedules!M12)</f>
-        <v>10227.9759710917</v>
+        <v>10227.9789424613</v>
       </c>
       <c r="N14" s="30" t="n">
         <f aca="false">(((('Income Statement'!N12*(1-Drivers!N22))+'Income Statement'!N11)-Schedules!N7)-Schedules!N12)</f>
-        <v>11890.0288983426</v>
+        <v>11890.0312539337</v>
       </c>
       <c r="O14" s="30" t="n">
         <f aca="false">(((('Income Statement'!O12*(1-Drivers!O22))+'Income Statement'!O11)-Schedules!O7)-Schedules!O12)</f>
-        <v>13917.619837016</v>
+        <v>13917.6217271066</v>
       </c>
       <c r="P14" s="30" t="n">
         <f aca="false">(((('Income Statement'!P12*(1-Drivers!P22))+'Income Statement'!P11)-Schedules!P7)-Schedules!P12)</f>
-        <v>16875.713826288</v>
+        <v>16875.7160616716</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">(((('Income Statement'!C18+'Income Statement'!C11)-Schedules!C7)-Schedules!C12)+('Balance Sheet'!C19-'Balance Sheet'!B19))</f>
-        <v>1236.45</v>
+        <v>1236.45000000001</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">(((('Income Statement'!D18+'Income Statement'!D11)-Schedules!D7)-Schedules!D12)+('Balance Sheet'!D19-'Balance Sheet'!C19))</f>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="J15" s="9" t="n">
         <f aca="false">(((('Income Statement'!J18+'Income Statement'!J11)-Schedules!J7)-Schedules!J12)+('Balance Sheet'!J19-'Balance Sheet'!I19))</f>
-        <v>1716.58000000001</v>
+        <v>1716.58</v>
       </c>
       <c r="K15" s="9" t="n">
         <f aca="false">(((('Income Statement'!K18+'Income Statement'!K11)-Schedules!K7)-Schedules!K12)+('Balance Sheet'!K19-'Balance Sheet'!J19))</f>
@@ -6371,23 +6371,23 @@
       </c>
       <c r="L15" s="33" t="n">
         <f aca="false">(((('Income Statement'!L18+'Income Statement'!L11)-Schedules!L7)-Schedules!L12)+('Balance Sheet'!L19-'Balance Sheet'!K19))</f>
-        <v>8919.92692869756</v>
+        <v>8919.89704291674</v>
       </c>
       <c r="M15" s="33" t="n">
         <f aca="false">(((('Income Statement'!M18+'Income Statement'!M11)-Schedules!M7)-Schedules!M12)+('Balance Sheet'!M19-'Balance Sheet'!L19))</f>
-        <v>12212.0482204898</v>
+        <v>12212.033510893</v>
       </c>
       <c r="N15" s="33" t="n">
         <f aca="false">(((('Income Statement'!N18+'Income Statement'!N11)-Schedules!N7)-Schedules!N12)+('Balance Sheet'!N19-'Balance Sheet'!M19))</f>
-        <v>14163.7647683307</v>
+        <v>14163.7480864644</v>
       </c>
       <c r="O15" s="33" t="n">
         <f aca="false">(((('Income Statement'!O18+'Income Statement'!O11)-Schedules!O7)-Schedules!O12)+('Balance Sheet'!O19-'Balance Sheet'!N19))</f>
-        <v>16530.9559050504</v>
+        <v>16530.9372756326</v>
       </c>
       <c r="P15" s="33" t="n">
         <f aca="false">(((('Income Statement'!P18+'Income Statement'!P11)-Schedules!P7)-Schedules!P12)+('Balance Sheet'!P19-'Balance Sheet'!O19))</f>
-        <v>19807.0314415089</v>
+        <v>19807.0116280096</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6396,11 +6396,11 @@
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">IFERROR((B14)/('Income Statement'!B10),0)</f>
-        <v>-1.08684847808636</v>
+        <v>-1.08684847808635</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">IFERROR((C14)/('Income Statement'!C10),0)</f>
-        <v>0.223002268796023</v>
+        <v>0.223002268796024</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">IFERROR((D14)/('Income Statement'!D10),0)</f>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="J16" s="19" t="n">
         <f aca="false">IFERROR((J14)/('Income Statement'!J10),0)</f>
-        <v>0.0232511905700373</v>
+        <v>0.0232511905700367</v>
       </c>
       <c r="K16" s="19" t="n">
         <f aca="false">IFERROR((K14)/('Income Statement'!K10),0)</f>
@@ -6436,23 +6436,23 @@
       </c>
       <c r="L16" s="32" t="n">
         <f aca="false">IFERROR((L14)/('Income Statement'!L10),0)</f>
-        <v>0.26051647837287</v>
+        <v>0.260515990176161</v>
       </c>
       <c r="M16" s="32" t="n">
         <f aca="false">IFERROR((M14)/('Income Statement'!M10),0)</f>
-        <v>0.331826676824569</v>
+        <v>0.331826773224847</v>
       </c>
       <c r="N16" s="32" t="n">
         <f aca="false">IFERROR((N14)/('Income Statement'!N10),0)</f>
-        <v>0.339917070210927</v>
+        <v>0.339917137553539</v>
       </c>
       <c r="O16" s="32" t="n">
         <f aca="false">IFERROR((O14)/('Income Statement'!O10),0)</f>
-        <v>0.349597490292163</v>
+        <v>0.349597537769458</v>
       </c>
       <c r="P16" s="32" t="n">
         <f aca="false">IFERROR((P14)/('Income Statement'!P10),0)</f>
-        <v>0.381526780326792</v>
+        <v>0.381526830864428</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6521,23 +6521,23 @@
       </c>
       <c r="L18" s="33" t="n">
         <f aca="false">(('Balance Sheet'!L19-'Balance Sheet'!L6)-'Balance Sheet'!L12)</f>
-        <v>51818.5435263638</v>
+        <v>51818.5460326305</v>
       </c>
       <c r="M18" s="33" t="n">
         <f aca="false">(('Balance Sheet'!M19-'Balance Sheet'!M6)-'Balance Sheet'!M12)</f>
-        <v>48734.0646670246</v>
+        <v>48734.0616322332</v>
       </c>
       <c r="N18" s="33" t="n">
         <f aca="false">(('Balance Sheet'!N19-'Balance Sheet'!N6)-'Balance Sheet'!N12)</f>
-        <v>45018.2048063434</v>
+        <v>45018.1960651693</v>
       </c>
       <c r="O18" s="33" t="n">
         <f aca="false">(('Balance Sheet'!O19-'Balance Sheet'!O6)-'Balance Sheet'!O12)</f>
-        <v>40257.9847510626</v>
+        <v>40257.9699786866</v>
       </c>
       <c r="P18" s="33" t="n">
         <f aca="false">(('Balance Sheet'!P19-'Balance Sheet'!P6)-'Balance Sheet'!P12)</f>
-        <v>32798.1801573423</v>
+        <v>32798.1583854004</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6586,23 +6586,23 @@
       </c>
       <c r="L19" s="37" t="n">
         <f aca="false">IFERROR((L18)/('Income Statement'!L10),0)</f>
-        <v>1.88379756464807</v>
+        <v>1.88379765576023</v>
       </c>
       <c r="M19" s="37" t="n">
         <f aca="false">IFERROR((M18)/('Income Statement'!M10),0)</f>
-        <v>1.58108141555268</v>
+        <v>1.58108131709481</v>
       </c>
       <c r="N19" s="37" t="n">
         <f aca="false">IFERROR((N18)/('Income Statement'!N10),0)</f>
-        <v>1.28699908257252</v>
+        <v>1.28699883267622</v>
       </c>
       <c r="O19" s="37" t="n">
         <f aca="false">IFERROR((O18)/('Income Statement'!O10),0)</f>
-        <v>1.0112426261105</v>
+        <v>1.01124225504234</v>
       </c>
       <c r="P19" s="37" t="n">
         <f aca="false">IFERROR((P18)/('Income Statement'!P10),0)</f>
-        <v>0.741502505009076</v>
+        <v>0.741502012788185</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6651,23 +6651,23 @@
       </c>
       <c r="L20" s="37" t="n">
         <f aca="false">IFERROR(('Income Statement'!L12)/('Income Statement'!L14),0)</f>
-        <v>3.78394367592807</v>
+        <v>3.78393849043939</v>
       </c>
       <c r="M20" s="37" t="n">
         <f aca="false">IFERROR(('Income Statement'!M12)/('Income Statement'!M14),0)</f>
-        <v>4.06625306916024</v>
+        <v>4.06624918635086</v>
       </c>
       <c r="N20" s="37" t="n">
         <f aca="false">IFERROR(('Income Statement'!N12)/('Income Statement'!N14),0)</f>
-        <v>4.42941376743826</v>
+        <v>4.42941129284338</v>
       </c>
       <c r="O20" s="37" t="n">
         <f aca="false">IFERROR(('Income Statement'!O12)/('Income Statement'!O14),0)</f>
-        <v>4.82560260851946</v>
+        <v>4.82560166509044</v>
       </c>
       <c r="P20" s="37" t="n">
         <f aca="false">IFERROR(('Income Statement'!P12)/('Income Statement'!P14),0)</f>
-        <v>5.08277883413725</v>
+        <v>5.08277940290456</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6716,23 +6716,23 @@
       </c>
       <c r="L21" s="33" t="n">
         <f aca="false">((('Balance Sheet'!L15+'Balance Sheet'!L16)+'Balance Sheet'!L19)-'Balance Sheet'!L6)</f>
-        <v>164964.856692695</v>
+        <v>164964.835986046</v>
       </c>
       <c r="M21" s="33" t="n">
         <f aca="false">((('Balance Sheet'!M15+'Balance Sheet'!M16)+'Balance Sheet'!M19)-'Balance Sheet'!M6)</f>
-        <v>175605.965693206</v>
+        <v>175605.916777935</v>
       </c>
       <c r="N21" s="33" t="n">
         <f aca="false">((('Balance Sheet'!N15+'Balance Sheet'!N16)+'Balance Sheet'!N19)-'Balance Sheet'!N6)</f>
-        <v>188184.361816161</v>
+        <v>188184.284910311</v>
       </c>
       <c r="O21" s="33" t="n">
         <f aca="false">((('Balance Sheet'!O15+'Balance Sheet'!O16)+'Balance Sheet'!O19)-'Balance Sheet'!O6)</f>
-        <v>202733.591445179</v>
+        <v>202733.486446803</v>
       </c>
       <c r="P21" s="33" t="n">
         <f aca="false">((('Balance Sheet'!P15+'Balance Sheet'!P16)+'Balance Sheet'!P19)-'Balance Sheet'!P6)</f>
-        <v>217219.619161068</v>
+        <v>217219.485325598</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6781,23 +6781,23 @@
       </c>
       <c r="L22" s="32" t="n">
         <f aca="false">IFERROR((('Income Statement'!L12*(1-Drivers!L22)))/(AVERAGE(K21,L21)),0)</f>
-        <v>0.102573987397706</v>
+        <v>0.10257384193668</v>
       </c>
       <c r="M22" s="32" t="n">
         <f aca="false">IFERROR((('Income Statement'!M12*(1-Drivers!M22)))/(AVERAGE(L21,M21)),0)</f>
-        <v>0.109117810523109</v>
+        <v>0.10911769233929</v>
       </c>
       <c r="N22" s="32" t="n">
         <f aca="false">IFERROR((('Income Statement'!N12*(1-Drivers!N22)))/(AVERAGE(M21,N21)),0)</f>
-        <v>0.118720318552944</v>
+        <v>0.118720227753198</v>
       </c>
       <c r="O22" s="32" t="n">
         <f aca="false">IFERROR((('Income Statement'!O12*(1-Drivers!O22)))/(AVERAGE(N21,O21)),0)</f>
-        <v>0.128415415404384</v>
+        <v>0.128415350994843</v>
       </c>
       <c r="P22" s="32" t="n">
         <f aca="false">IFERROR((('Income Statement'!P12*(1-Drivers!P22)))/(AVERAGE(O21,P21)),0)</f>
-        <v>0.134329934279618</v>
+        <v>0.134329892615836</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6846,23 +6846,23 @@
       </c>
       <c r="L23" s="32" t="n">
         <f aca="false">IFERROR(('Income Statement'!L18)/(AVERAGE(Schedules!K24,Schedules!L24)),0)</f>
-        <v>0.134624763643918</v>
+        <v>0.134624527350406</v>
       </c>
       <c r="M23" s="32" t="n">
         <f aca="false">IFERROR(('Income Statement'!M18)/(AVERAGE(Schedules!L24,Schedules!M24)),0)</f>
-        <v>0.139914317255181</v>
+        <v>0.139914143527918</v>
       </c>
       <c r="N23" s="32" t="n">
         <f aca="false">IFERROR(('Income Statement'!N18)/(AVERAGE(Schedules!M24,Schedules!N24)),0)</f>
-        <v>0.146857032029525</v>
+        <v>0.146856911714516</v>
       </c>
       <c r="O23" s="32" t="n">
         <f aca="false">IFERROR(('Income Statement'!O18)/(AVERAGE(Schedules!N24,Schedules!O24)),0)</f>
-        <v>0.153010127565777</v>
+        <v>0.153010051538626</v>
       </c>
       <c r="P23" s="32" t="n">
         <f aca="false">IFERROR(('Income Statement'!P18)/(AVERAGE(Schedules!O24,Schedules!P24)),0)</f>
-        <v>0.152548887433424</v>
+        <v>0.152548843994</v>
       </c>
     </row>
   </sheetData>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="B45" s="44" t="n">
         <f aca="false">DCF!B45</f>
-        <v>512.779689751377</v>
+        <v>512.7791828375</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7765,19 +7765,19 @@
         <v>0.0555489151241863</v>
       </c>
       <c r="L9" s="47" t="n">
-        <v>0.046571</v>
+        <v>0.0465709461501931</v>
       </c>
       <c r="M9" s="47" t="n">
-        <v>0.046571</v>
+        <v>0.0465709461501931</v>
       </c>
       <c r="N9" s="47" t="n">
-        <v>0.046571</v>
+        <v>0.0465709461501931</v>
       </c>
       <c r="O9" s="47" t="n">
-        <v>0.046571</v>
+        <v>0.0465709461501931</v>
       </c>
       <c r="P9" s="47" t="n">
-        <v>0.046571</v>
+        <v>0.0465709461501931</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="J11" s="19" t="n">
         <f aca="false">IFERROR((Schedules!J7)/('Income Statement'!J6),0)</f>
-        <v>0.618449086523427</v>
+        <v>0.618449086523428</v>
       </c>
       <c r="K11" s="19" t="n">
         <f aca="false">IFERROR((Schedules!K7)/('Income Statement'!K6),0)</f>
@@ -7910,19 +7910,19 @@
         <v>0.0615666878532839</v>
       </c>
       <c r="L12" s="47" t="n">
-        <v>0.057892</v>
+        <v>0.0578922241002086</v>
       </c>
       <c r="M12" s="47" t="n">
-        <v>0.057892</v>
+        <v>0.0578922241002086</v>
       </c>
       <c r="N12" s="47" t="n">
-        <v>0.057892</v>
+        <v>0.0578922241002086</v>
       </c>
       <c r="O12" s="47" t="n">
-        <v>0.057892</v>
+        <v>0.0578922241002086</v>
       </c>
       <c r="P12" s="47" t="n">
-        <v>0.057892</v>
+        <v>0.0578922241002086</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8030,19 +8030,19 @@
         <v>0.327579650540056</v>
       </c>
       <c r="L14" s="47" t="n">
-        <v>0.373709</v>
+        <v>0.373708785406367</v>
       </c>
       <c r="M14" s="47" t="n">
-        <v>0.373709</v>
+        <v>0.373708785406367</v>
       </c>
       <c r="N14" s="47" t="n">
-        <v>0.373709</v>
+        <v>0.373708785406367</v>
       </c>
       <c r="O14" s="47" t="n">
-        <v>0.373709</v>
+        <v>0.373708785406367</v>
       </c>
       <c r="P14" s="47" t="n">
-        <v>0.373709</v>
+        <v>0.373708785406367</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8290,19 +8290,19 @@
         <v>0.458420731019417</v>
       </c>
       <c r="L19" s="47" t="n">
-        <v>0.512548</v>
+        <v>0.512548190513461</v>
       </c>
       <c r="M19" s="47" t="n">
-        <v>0.512548</v>
+        <v>0.512548190513461</v>
       </c>
       <c r="N19" s="47" t="n">
-        <v>0.512548</v>
+        <v>0.512548190513461</v>
       </c>
       <c r="O19" s="47" t="n">
-        <v>0.512548</v>
+        <v>0.512548190513461</v>
       </c>
       <c r="P19" s="47" t="n">
-        <v>0.512548</v>
+        <v>0.512548190513461</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8350,19 +8350,19 @@
         <v>0.537952388709454</v>
       </c>
       <c r="L20" s="47" t="n">
-        <v>0.54751</v>
+        <v>0.5475097888409</v>
       </c>
       <c r="M20" s="47" t="n">
-        <v>0.54751</v>
+        <v>0.5475097888409</v>
       </c>
       <c r="N20" s="47" t="n">
-        <v>0.54751</v>
+        <v>0.5475097888409</v>
       </c>
       <c r="O20" s="47" t="n">
-        <v>0.54751</v>
+        <v>0.5475097888409</v>
       </c>
       <c r="P20" s="47" t="n">
-        <v>0.54751</v>
+        <v>0.5475097888409</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8615,19 +8615,19 @@
         <v>0.231395216611621</v>
       </c>
       <c r="L25" s="47" t="n">
-        <v>0.066894</v>
+        <v>0.0668937659409345</v>
       </c>
       <c r="M25" s="47" t="n">
-        <v>0.066894</v>
+        <v>0.0668937659409345</v>
       </c>
       <c r="N25" s="47" t="n">
-        <v>0.066894</v>
+        <v>0.0668937659409345</v>
       </c>
       <c r="O25" s="47" t="n">
-        <v>0.066894</v>
+        <v>0.0668937659409345</v>
       </c>
       <c r="P25" s="47" t="n">
-        <v>0.066894</v>
+        <v>0.0668937659409345</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8795,19 +8795,19 @@
         <v>0.134931412182059</v>
       </c>
       <c r="L28" s="47" t="n">
-        <v>0.143684</v>
+        <v>0.143684092700629</v>
       </c>
       <c r="M28" s="47" t="n">
-        <v>0.143684</v>
+        <v>0.143684092700629</v>
       </c>
       <c r="N28" s="47" t="n">
-        <v>0.143684</v>
+        <v>0.143684092700629</v>
       </c>
       <c r="O28" s="47" t="n">
-        <v>0.143684</v>
+        <v>0.143684092700629</v>
       </c>
       <c r="P28" s="47" t="n">
-        <v>0.143684</v>
+        <v>0.143684092700629</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9305,23 +9305,23 @@
       </c>
       <c r="L11" s="33" t="n">
         <f aca="false">MIN((Drivers!L12*'Balance Sheet'!K10),('Balance Sheet'!K10+Schedules!L7))</f>
-        <v>7621.62653</v>
+        <v>7621.65603335271</v>
       </c>
       <c r="M11" s="33" t="n">
         <f aca="false">MIN((Drivers!M12*'Balance Sheet'!L10),('Balance Sheet'!L10+Schedules!M7))</f>
-        <v>8024.2649467169</v>
+        <v>8024.29430067014</v>
       </c>
       <c r="N11" s="33" t="n">
         <f aca="false">MIN((Drivers!N12*'Balance Sheet'!M10),('Balance Sheet'!M10+Schedules!N7))</f>
-        <v>8482.69979166854</v>
+        <v>8482.72922085962</v>
       </c>
       <c r="O11" s="33" t="n">
         <f aca="false">MIN((Drivers!O12*'Balance Sheet'!N10),('Balance Sheet'!N10+Schedules!O7))</f>
-        <v>9012.93182265299</v>
+        <v>9012.96160065347</v>
       </c>
       <c r="P11" s="33" t="n">
         <f aca="false">MIN((Drivers!P12*'Balance Sheet'!O10),('Balance Sheet'!O10+Schedules!P7))</f>
-        <v>9623.29063107591</v>
+        <v>9623.32104786357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9370,23 +9370,23 @@
       </c>
       <c r="L12" s="60" t="n">
         <f aca="false">(L10-L11)</f>
-        <v>19885.863923755</v>
+        <v>19885.8344204023</v>
       </c>
       <c r="M12" s="60" t="n">
         <f aca="false">(M10-M11)</f>
-        <v>22798.9831084688</v>
+        <v>22798.9537545156</v>
       </c>
       <c r="N12" s="60" t="n">
         <f aca="false">(N10-N11)</f>
-        <v>26496.5052566821</v>
+        <v>26496.4758274911</v>
       </c>
       <c r="O12" s="60" t="n">
         <f aca="false">(O10-O11)</f>
-        <v>30797.4793601757</v>
+        <v>30797.4495821752</v>
       </c>
       <c r="P12" s="60" t="n">
         <f aca="false">(P10-P11)</f>
-        <v>34608.7651418723</v>
+        <v>34608.7347250846</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9425,23 +9425,23 @@
       </c>
       <c r="L13" s="33" t="n">
         <f aca="false">((L6*Drivers!L9)+(Drivers!L24*AVERAGE('Balance Sheet'!K6,'Balance Sheet'!L6)))</f>
-        <v>2189.83134687491</v>
+        <v>2189.82881478423</v>
       </c>
       <c r="M13" s="33" t="n">
         <f aca="false">((M6*Drivers!M9)+(Drivers!M24*AVERAGE('Balance Sheet'!L6,'Balance Sheet'!M6)))</f>
-        <v>2474.94738823803</v>
+        <v>2474.94452646914</v>
       </c>
       <c r="N13" s="33" t="n">
         <f aca="false">((N6*Drivers!N9)+(Drivers!N24*AVERAGE('Balance Sheet'!M6,'Balance Sheet'!N6)))</f>
-        <v>2833.07227531607</v>
+        <v>2833.06899944922</v>
       </c>
       <c r="O13" s="33" t="n">
         <f aca="false">((O6*Drivers!O9)+(Drivers!O24*AVERAGE('Balance Sheet'!N6,'Balance Sheet'!O6)))</f>
-        <v>3252.65027929038</v>
+        <v>3252.64651826765</v>
       </c>
       <c r="P13" s="33" t="n">
         <f aca="false">((P6*Drivers!P9)+(Drivers!P24*AVERAGE('Balance Sheet'!O6,'Balance Sheet'!P6)))</f>
-        <v>3645.89569805659</v>
+        <v>3645.89148232621</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9480,23 +9480,23 @@
       </c>
       <c r="L14" s="33" t="n">
         <f aca="false">(Drivers!L23*AVERAGE('Balance Sheet'!K19,'Balance Sheet'!L19))</f>
-        <v>5255.3276757952</v>
+        <v>5255.32708067175</v>
       </c>
       <c r="M14" s="33" t="n">
         <f aca="false">(Drivers!M23*AVERAGE('Balance Sheet'!L19,'Balance Sheet'!M19))</f>
-        <v>5606.87756533984</v>
+        <v>5606.87570034926</v>
       </c>
       <c r="N14" s="33" t="n">
         <f aca="false">(Drivers!N23*AVERAGE('Balance Sheet'!M19,'Balance Sheet'!N19))</f>
-        <v>5981.94403319569</v>
+        <v>5981.94073110834</v>
       </c>
       <c r="O14" s="33" t="n">
         <f aca="false">(Drivers!O23*AVERAGE('Balance Sheet'!N19,'Balance Sheet'!O19))</f>
-        <v>6382.10019735228</v>
+        <v>6382.09527424764</v>
       </c>
       <c r="P14" s="33" t="n">
         <f aca="false">(Drivers!P23*AVERAGE('Balance Sheet'!O19,'Balance Sheet'!P19))</f>
-        <v>6809.02440795396</v>
+        <v>6809.01766173591</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9590,23 +9590,23 @@
       </c>
       <c r="L16" s="60" t="n">
         <f aca="false">(((L12+L13)-L14)+L15)</f>
-        <v>16820.3675948347</v>
+        <v>16820.3361545148</v>
       </c>
       <c r="M16" s="60" t="n">
         <f aca="false">(((M12+M13)-M14)+M15)</f>
-        <v>19667.052931367</v>
+        <v>19667.0225806355</v>
       </c>
       <c r="N16" s="60" t="n">
         <f aca="false">(((N12+N13)-N14)+N15)</f>
-        <v>23347.6334988025</v>
+        <v>23347.604095832</v>
       </c>
       <c r="O16" s="60" t="n">
         <f aca="false">(((O12+O13)-O14)+O15)</f>
-        <v>27668.0294421138</v>
+        <v>27668.0008261953</v>
       </c>
       <c r="P16" s="60" t="n">
         <f aca="false">(((P12+P13)-P14)+P15)</f>
-        <v>31445.6364319749</v>
+        <v>31445.6085456749</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9629,7 +9629,7 @@
         <v>1297.71</v>
       </c>
       <c r="G17" s="53" t="n">
-        <v>831.11</v>
+        <v>831.110000000001</v>
       </c>
       <c r="H17" s="53" t="n">
         <v>178.04</v>
@@ -9645,23 +9645,23 @@
       </c>
       <c r="L17" s="33" t="n">
         <f aca="false">(L16*Drivers!L22)</f>
-        <v>3111.76800504442</v>
+        <v>3111.76218858523</v>
       </c>
       <c r="M17" s="33" t="n">
         <f aca="false">(M16*Drivers!M22)</f>
-        <v>3638.4047923029</v>
+        <v>3638.39917741756</v>
       </c>
       <c r="N17" s="33" t="n">
         <f aca="false">(N16*Drivers!N22)</f>
-        <v>4319.31219727847</v>
+        <v>4319.30675772891</v>
       </c>
       <c r="O17" s="33" t="n">
         <f aca="false">(O16*Drivers!O22)</f>
-        <v>5118.58544679106</v>
+        <v>5118.58015284612</v>
       </c>
       <c r="P17" s="33" t="n">
         <f aca="false">(P16*Drivers!P22)</f>
-        <v>5817.44273991536</v>
+        <v>5817.43758094986</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9700,23 +9700,23 @@
       </c>
       <c r="L18" s="60" t="n">
         <f aca="false">(L16-L17)</f>
-        <v>13708.5995897903</v>
+        <v>13708.5739659295</v>
       </c>
       <c r="M18" s="60" t="n">
         <f aca="false">(M16-M17)</f>
-        <v>16028.6481390641</v>
+        <v>16028.6234032179</v>
       </c>
       <c r="N18" s="60" t="n">
         <f aca="false">(N16-N17)</f>
-        <v>19028.3213015241</v>
+        <v>19028.297338103</v>
       </c>
       <c r="O18" s="60" t="n">
         <f aca="false">(O16-O17)</f>
-        <v>22549.4439953228</v>
+        <v>22549.4206733491</v>
       </c>
       <c r="P18" s="60" t="n">
         <f aca="false">(P16-P17)</f>
-        <v>25628.1936920596</v>
+        <v>25628.1709647251</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9765,23 +9765,23 @@
       </c>
       <c r="L19" s="35" t="n">
         <f aca="false">IFERROR((L18)/(Schedules!L23),0)</f>
-        <v>59.5001889781471</v>
+        <v>59.5000777614946</v>
       </c>
       <c r="M19" s="35" t="n">
         <f aca="false">IFERROR((M18)/(Schedules!M23),0)</f>
-        <v>69.5700233340269</v>
+        <v>69.5699159716727</v>
       </c>
       <c r="N19" s="35" t="n">
         <f aca="false">IFERROR((N18)/(Schedules!N23),0)</f>
-        <v>82.5896697880651</v>
+        <v>82.5895657783105</v>
       </c>
       <c r="O19" s="35" t="n">
         <f aca="false">IFERROR((O18)/(Schedules!O23),0)</f>
-        <v>97.8725923305179</v>
+        <v>97.8724911048727</v>
       </c>
       <c r="P19" s="35" t="n">
         <f aca="false">IFERROR((P18)/(Schedules!P23),0)</f>
-        <v>111.235459016673</v>
+        <v>111.235360371973</v>
       </c>
     </row>
   </sheetData>
@@ -9924,23 +9924,23 @@
       </c>
       <c r="L6" s="33" t="n">
         <f aca="false">(K6+'Cash Flow'!L21)</f>
-        <v>10550.4783685162</v>
+        <v>10550.4609841633</v>
       </c>
       <c r="M6" s="33" t="n">
         <f aca="false">(L6+'Cash Flow'!M21)</f>
-        <v>18171.5525715915</v>
+        <v>18171.5238597045</v>
       </c>
       <c r="N6" s="33" t="n">
         <f aca="false">(M6+'Cash Flow'!N21)</f>
-        <v>26727.4787849327</v>
+        <v>26727.4367206014</v>
       </c>
       <c r="O6" s="33" t="n">
         <f aca="false">(N6+'Cash Flow'!O21)</f>
-        <v>36651.5365914683</v>
+        <v>36651.4790917337</v>
       </c>
       <c r="P6" s="33" t="n">
         <f aca="false">(O6+'Cash Flow'!P21)</f>
-        <v>49620.6086989759</v>
+        <v>49620.534087577</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10089,23 +10089,23 @@
       </c>
       <c r="L9" s="33" t="n">
         <f aca="false">('Income Statement'!L6*Drivers!L19)</f>
-        <v>24100.6995163952</v>
+        <v>24100.7084745956</v>
       </c>
       <c r="M9" s="33" t="n">
         <f aca="false">('Income Statement'!M6*Drivers!M19)</f>
-        <v>27238.6105934299</v>
+        <v>27238.6207179879</v>
       </c>
       <c r="N9" s="33" t="n">
         <f aca="false">('Income Statement'!N6*Drivers!N19)</f>
-        <v>31180.0375462992</v>
+        <v>31180.0491358808</v>
       </c>
       <c r="O9" s="33" t="n">
         <f aca="false">('Income Statement'!O6*Drivers!O19)</f>
-        <v>35797.8011069061</v>
+        <v>35797.8144129048</v>
       </c>
       <c r="P9" s="33" t="n">
         <f aca="false">('Income Statement'!P6*Drivers!P19)</f>
-        <v>40125.7552607311</v>
+        <v>40125.7701754249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10144,23 +10144,23 @@
       </c>
       <c r="L10" s="33" t="n">
         <f aca="false">((K10+Schedules!L7)-'Income Statement'!L11)</f>
-        <v>138607.49234293</v>
+        <v>138607.462839577</v>
       </c>
       <c r="M10" s="33" t="n">
         <f aca="false">((L10+Schedules!M7)-'Income Statement'!M11)</f>
-        <v>146526.286735102</v>
+        <v>146526.227877796</v>
       </c>
       <c r="N10" s="33" t="n">
         <f aca="false">((M10+Schedules!N7)-'Income Statement'!N11)</f>
-        <v>155685.272967819</v>
+        <v>155685.184681322</v>
       </c>
       <c r="O10" s="33" t="n">
         <f aca="false">((N10+Schedules!O7)-'Income Statement'!O11)</f>
-        <v>166228.332603398</v>
+        <v>166228.2145389</v>
       </c>
       <c r="P10" s="33" t="n">
         <f aca="false">((O10+Schedules!P7)-'Income Statement'!P11)</f>
-        <v>176959.616310316</v>
+        <v>176959.467829031</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10199,23 +10199,23 @@
       </c>
       <c r="L11" s="33" t="n">
         <f aca="false">('Income Statement'!L6*Drivers!L14)</f>
-        <v>17572.3021367219</v>
+        <v>17572.2920462394</v>
       </c>
       <c r="M11" s="33" t="n">
         <f aca="false">('Income Statement'!M6*Drivers!M14)</f>
-        <v>19860.2158749231</v>
+        <v>19860.2044706597</v>
       </c>
       <c r="N11" s="33" t="n">
         <f aca="false">('Income Statement'!N6*Drivers!N14)</f>
-        <v>22733.9891120245</v>
+        <v>22733.9760575642</v>
       </c>
       <c r="O11" s="33" t="n">
         <f aca="false">('Income Statement'!O6*Drivers!O14)</f>
-        <v>26100.8928995153</v>
+        <v>26100.8779116894</v>
       </c>
       <c r="P11" s="33" t="n">
         <f aca="false">('Income Statement'!P6*Drivers!P14)</f>
-        <v>29256.4908510667</v>
+        <v>29256.4740512127</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10319,23 +10319,23 @@
       </c>
       <c r="L13" s="60" t="n">
         <f aca="false">((((((L6+L7)+L8)+L9)+L10)+L11)+L12)</f>
-        <v>204584.572061723</v>
+        <v>204584.524041735</v>
       </c>
       <c r="M13" s="60" t="n">
         <f aca="false">((((((M6+M7)+M8)+M9)+M10)+M11)+M12)</f>
-        <v>226631.569922777</v>
+        <v>226631.481073879</v>
       </c>
       <c r="N13" s="60" t="n">
         <f aca="false">((((((N6+N7)+N8)+N9)+N10)+N11)+N12)</f>
-        <v>252519.873533982</v>
+        <v>252519.741718275</v>
       </c>
       <c r="O13" s="60" t="n">
         <f aca="false">((((((O6+O7)+O8)+O9)+O10)+O11)+O12)</f>
-        <v>282562.910646897</v>
+        <v>282562.733400837</v>
       </c>
       <c r="P13" s="60" t="n">
         <f aca="false">((((((P6+P7)+P8)+P9)+P10)+P11)+P12)</f>
-        <v>315238.204387873</v>
+        <v>315237.979410029</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10449,23 +10449,23 @@
       </c>
       <c r="L16" s="33" t="n">
         <f aca="false">(((K16+'Income Statement'!L18)-Schedules!L22)+Drivers!L27)</f>
-        <v>107236.873166331</v>
+        <v>107236.849953415</v>
       </c>
       <c r="M16" s="33" t="n">
         <f aca="false">(((L16+'Income Statement'!M18)-Schedules!M22)+Drivers!M27)</f>
-        <v>120962.461026182</v>
+        <v>120962.415145702</v>
       </c>
       <c r="N16" s="33" t="n">
         <f aca="false">(((M16+'Income Statement'!N18)-Schedules!N22)+Drivers!N27)</f>
-        <v>137256.717009818</v>
+        <v>137256.648845142</v>
       </c>
       <c r="O16" s="33" t="n">
         <f aca="false">(((N16+'Income Statement'!O18)-Schedules!O22)+Drivers!O27)</f>
-        <v>156566.166694116</v>
+        <v>156566.076468116</v>
       </c>
       <c r="P16" s="33" t="n">
         <f aca="false">(((O16+'Income Statement'!P18)-Schedules!P22)+Drivers!P27)</f>
-        <v>178511.999003726</v>
+        <v>178511.886940198</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10504,23 +10504,23 @@
       </c>
       <c r="L17" s="33" t="n">
         <f aca="false">MAX(((K17*(1+Drivers!L25))-Drivers!L26),0)</f>
-        <v>67817.67189488</v>
+        <v>67817.6570167938</v>
       </c>
       <c r="M17" s="33" t="n">
         <f aca="false">MAX(((L17*(1+Drivers!M25))-Drivers!M26),0)</f>
-        <v>72354.2672386161</v>
+        <v>72354.2354919378</v>
       </c>
       <c r="N17" s="33" t="n">
         <f aca="false">MAX(((M17*(1+Drivers!N25))-Drivers!N26),0)</f>
-        <v>77194.3335912761</v>
+        <v>77194.2827857707</v>
       </c>
       <c r="O17" s="33" t="n">
         <f aca="false">MAX(((N17*(1+Drivers!O25))-Drivers!O26),0)</f>
-        <v>82358.1713425309</v>
+        <v>82358.0990704204</v>
       </c>
       <c r="P17" s="33" t="n">
         <f aca="false">MAX(((O17*(1+Drivers!P25))-Drivers!P26),0)</f>
-        <v>87867.4388563182</v>
+        <v>87867.3424729774</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10624,23 +10624,23 @@
       </c>
       <c r="L19" s="56" t="n">
         <f aca="false">(L17+L18)</f>
-        <v>67817.67189488</v>
+        <v>67817.6570167938</v>
       </c>
       <c r="M19" s="56" t="n">
         <f aca="false">(M17+M18)</f>
-        <v>72354.2672386161</v>
+        <v>72354.2354919378</v>
       </c>
       <c r="N19" s="56" t="n">
         <f aca="false">(N17+N18)</f>
-        <v>77194.3335912761</v>
+        <v>77194.2827857707</v>
       </c>
       <c r="O19" s="56" t="n">
         <f aca="false">(O17+O18)</f>
-        <v>82358.1713425309</v>
+        <v>82358.0990704204</v>
       </c>
       <c r="P19" s="56" t="n">
         <f aca="false">(P17+P18)</f>
-        <v>87867.4388563182</v>
+        <v>87867.3424729774</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10734,23 +10734,23 @@
       </c>
       <c r="L21" s="33" t="n">
         <f aca="false">('Income Statement'!L6*Drivers!L20)</f>
-        <v>25744.6599971545</v>
+        <v>25744.6500681683</v>
       </c>
       <c r="M21" s="33" t="n">
         <f aca="false">('Income Statement'!M6*Drivers!M20)</f>
-        <v>29096.6147287841</v>
+        <v>29096.6035070438</v>
       </c>
       <c r="N21" s="33" t="n">
         <f aca="false">('Income Statement'!N6*Drivers!N20)</f>
-        <v>33306.8948800391</v>
+        <v>33306.8820345131</v>
       </c>
       <c r="O21" s="33" t="n">
         <f aca="false">('Income Statement'!O6*Drivers!O20)</f>
-        <v>38239.6460117729</v>
+        <v>38239.6312638245</v>
       </c>
       <c r="P21" s="33" t="n">
         <f aca="false">('Income Statement'!P6*Drivers!P20)</f>
-        <v>42862.8192145962</v>
+        <v>42862.8026836209</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10799,23 +10799,23 @@
       </c>
       <c r="L22" s="60" t="n">
         <f aca="false">((((L15+L16)+L19)+L20)+L21)</f>
-        <v>204584.572061723</v>
+        <v>204584.524041735</v>
       </c>
       <c r="M22" s="60" t="n">
         <f aca="false">((((M15+M16)+M19)+M20)+M21)</f>
-        <v>226631.569922777</v>
+        <v>226631.481073879</v>
       </c>
       <c r="N22" s="60" t="n">
         <f aca="false">((((N15+N16)+N19)+N20)+N21)</f>
-        <v>252519.873533982</v>
+        <v>252519.741718275</v>
       </c>
       <c r="O22" s="60" t="n">
         <f aca="false">((((O15+O16)+O19)+O20)+O21)</f>
-        <v>282562.910646897</v>
+        <v>282562.733400837</v>
       </c>
       <c r="P22" s="60" t="n">
         <f aca="false">((((P15+P16)+P19)+P20)+P21)</f>
-        <v>315238.204387873</v>
+        <v>315237.979410029</v>
       </c>
     </row>
   </sheetData>
@@ -10968,23 +10968,23 @@
       </c>
       <c r="L6" s="33" t="n">
         <f aca="false">'Income Statement'!L18</f>
-        <v>13708.5995897903</v>
+        <v>13708.5739659295</v>
       </c>
       <c r="M6" s="33" t="n">
         <f aca="false">'Income Statement'!M18</f>
-        <v>16028.6481390641</v>
+        <v>16028.6234032179</v>
       </c>
       <c r="N6" s="33" t="n">
         <f aca="false">'Income Statement'!N18</f>
-        <v>19028.3213015241</v>
+        <v>19028.297338103</v>
       </c>
       <c r="O6" s="33" t="n">
         <f aca="false">'Income Statement'!O18</f>
-        <v>22549.4439953228</v>
+        <v>22549.4206733491</v>
       </c>
       <c r="P6" s="33" t="n">
         <f aca="false">'Income Statement'!P18</f>
-        <v>25628.1936920596</v>
+        <v>25628.1709647251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11033,23 +11033,23 @@
       </c>
       <c r="L7" s="33" t="n">
         <f aca="false">'Income Statement'!L11</f>
-        <v>7621.62653</v>
+        <v>7621.65603335271</v>
       </c>
       <c r="M7" s="33" t="n">
         <f aca="false">'Income Statement'!M11</f>
-        <v>8024.2649467169</v>
+        <v>8024.29430067014</v>
       </c>
       <c r="N7" s="33" t="n">
         <f aca="false">'Income Statement'!N11</f>
-        <v>8482.69979166854</v>
+        <v>8482.72922085962</v>
       </c>
       <c r="O7" s="33" t="n">
         <f aca="false">'Income Statement'!O11</f>
-        <v>9012.93182265299</v>
+        <v>9012.96160065347</v>
       </c>
       <c r="P7" s="33" t="n">
         <f aca="false">'Income Statement'!P11</f>
-        <v>9623.29063107591</v>
+        <v>9623.32104786357</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11098,23 +11098,23 @@
       </c>
       <c r="L8" s="33" t="n">
         <f aca="false">-(Schedules!L12)</f>
-        <v>-2085.83221304273</v>
+        <v>-2085.8511002293</v>
       </c>
       <c r="M8" s="33" t="n">
         <f aca="false">-(Schedules!M12)</f>
-        <v>-434.400870138172</v>
+        <v>-434.403329249853</v>
       </c>
       <c r="N8" s="33" t="n">
         <f aca="false">-(Schedules!N12)</f>
-        <v>-545.636653136276</v>
+        <v>-545.639741945626</v>
       </c>
       <c r="O8" s="33" t="n">
         <f aca="false">-(Schedules!O12)</f>
-        <v>-639.266205948567</v>
+        <v>-639.269824788018</v>
       </c>
       <c r="P8" s="33" t="n">
         <f aca="false">-(Schedules!P12)</f>
-        <v>-599.146057419937</v>
+        <v>-599.149449142125</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11163,23 +11163,23 @@
       </c>
       <c r="L9" s="60" t="n">
         <f aca="false">((L6+L7)+L8)</f>
-        <v>19244.3939067476</v>
+        <v>19244.378899053</v>
       </c>
       <c r="M9" s="60" t="n">
         <f aca="false">((M6+M7)+M8)</f>
-        <v>23618.5122156429</v>
+        <v>23618.5143746382</v>
       </c>
       <c r="N9" s="60" t="n">
         <f aca="false">((N6+N7)+N8)</f>
-        <v>26965.3844400563</v>
+        <v>26965.386817017</v>
       </c>
       <c r="O9" s="60" t="n">
         <f aca="false">((O6+O7)+O8)</f>
-        <v>30923.1096120272</v>
+        <v>30923.1124492146</v>
       </c>
       <c r="P9" s="60" t="n">
         <f aca="false">((P6+P7)+P8)</f>
-        <v>34652.3382657155</v>
+        <v>34652.3425634465</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11248,23 +11248,23 @@
       </c>
       <c r="L11" s="33" t="n">
         <f aca="false">(-(Schedules!L7)-('Balance Sheet'!L11-'Balance Sheet'!K11))</f>
-        <v>-19459.8710096519</v>
+        <v>-19459.8609191694</v>
       </c>
       <c r="M11" s="33" t="n">
         <f aca="false">(-(Schedules!M7)-('Balance Sheet'!M11-'Balance Sheet'!L11))</f>
-        <v>-18230.9730770904</v>
+        <v>-18230.9717633095</v>
       </c>
       <c r="N11" s="33" t="n">
         <f aca="false">(-(Schedules!N7)-('Balance Sheet'!N11-'Balance Sheet'!M11))</f>
-        <v>-20515.4592614869</v>
+        <v>-20515.45761129</v>
       </c>
       <c r="O11" s="33" t="n">
         <f aca="false">(-(Schedules!O7)-('Balance Sheet'!O11-'Balance Sheet'!N11))</f>
-        <v>-22922.8952457225</v>
+        <v>-22922.8933123569</v>
       </c>
       <c r="P11" s="33" t="n">
         <f aca="false">(-(Schedules!P7)-('Balance Sheet'!P11-'Balance Sheet'!O11))</f>
-        <v>-23510.1722895453</v>
+        <v>-23510.1704775171</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11378,23 +11378,23 @@
       </c>
       <c r="L13" s="60" t="n">
         <f aca="false">(L11+L12)</f>
-        <v>-19459.8710096519</v>
+        <v>-19459.8609191694</v>
       </c>
       <c r="M13" s="60" t="n">
         <f aca="false">(M11+M12)</f>
-        <v>-18230.9730770904</v>
+        <v>-18230.9717633095</v>
       </c>
       <c r="N13" s="60" t="n">
         <f aca="false">(N11+N12)</f>
-        <v>-20515.4592614869</v>
+        <v>-20515.45761129</v>
       </c>
       <c r="O13" s="60" t="n">
         <f aca="false">(O11+O12)</f>
-        <v>-22922.8952457225</v>
+        <v>-22922.8933123569</v>
       </c>
       <c r="P13" s="60" t="n">
         <f aca="false">(P11+P12)</f>
-        <v>-23510.1722895453</v>
+        <v>-23510.1704775171</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11463,23 +11463,23 @@
       </c>
       <c r="L15" s="33" t="n">
         <f aca="false">('Balance Sheet'!L17-'Balance Sheet'!K17)</f>
-        <v>4252.15189488</v>
+        <v>4252.13701679379</v>
       </c>
       <c r="M15" s="33" t="n">
         <f aca="false">('Balance Sheet'!M17-'Balance Sheet'!L17)</f>
-        <v>4536.5953437361</v>
+        <v>4536.57847514398</v>
       </c>
       <c r="N15" s="33" t="n">
         <f aca="false">('Balance Sheet'!N17-'Balance Sheet'!M17)</f>
-        <v>4840.06635265998</v>
+        <v>4840.04729383295</v>
       </c>
       <c r="O15" s="33" t="n">
         <f aca="false">('Balance Sheet'!O17-'Balance Sheet'!N17)</f>
-        <v>5163.83775125482</v>
+        <v>5163.81628464966</v>
       </c>
       <c r="P15" s="33" t="n">
         <f aca="false">('Balance Sheet'!P17-'Balance Sheet'!O17)</f>
-        <v>5509.26751378726</v>
+        <v>5509.243402557</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11593,23 +11593,23 @@
       </c>
       <c r="L17" s="33" t="n">
         <f aca="false">-(Schedules!L22)</f>
-        <v>-1969.70642345943</v>
+        <v>-1969.70401251405</v>
       </c>
       <c r="M17" s="33" t="n">
         <f aca="false">-(Schedules!M22)</f>
-        <v>-2303.06027921329</v>
+        <v>-2303.05821093143</v>
       </c>
       <c r="N17" s="33" t="n">
         <f aca="false">-(Schedules!N22)</f>
-        <v>-2734.06531788818</v>
+        <v>-2734.06363866313</v>
       </c>
       <c r="O17" s="33" t="n">
         <f aca="false">-(Schedules!O22)</f>
-        <v>-3239.99431102396</v>
+        <v>-3239.99305037497</v>
       </c>
       <c r="P17" s="33" t="n">
         <f aca="false">-(Schedules!P22)</f>
-        <v>-3682.36138244989</v>
+        <v>-3682.36049264312</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11723,23 +11723,23 @@
       </c>
       <c r="L19" s="60" t="n">
         <f aca="false">(((L15+L16)+L17)+L18)</f>
-        <v>2282.44547142057</v>
+        <v>2282.43300427975</v>
       </c>
       <c r="M19" s="60" t="n">
         <f aca="false">(((M15+M16)+M17)+M18)</f>
-        <v>2233.53506452281</v>
+        <v>2233.52026421255</v>
       </c>
       <c r="N19" s="60" t="n">
         <f aca="false">(((N15+N16)+N17)+N18)</f>
-        <v>2106.0010347718</v>
+        <v>2105.98365516982</v>
       </c>
       <c r="O19" s="60" t="n">
         <f aca="false">(((O15+O16)+O17)+O18)</f>
-        <v>1923.84344023086</v>
+        <v>1923.82323427468</v>
       </c>
       <c r="P19" s="60" t="n">
         <f aca="false">(((P15+P16)+P17)+P18)</f>
-        <v>1826.90613133737</v>
+        <v>1826.88290991388</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="C21" s="61" t="n">
         <f aca="false">((C9+C13)+C19)</f>
-        <v>873.210000000003</v>
+        <v>873.210000000006</v>
       </c>
       <c r="D21" s="61" t="n">
         <f aca="false">((D9+D13)+D19)</f>
@@ -11800,7 +11800,7 @@
       </c>
       <c r="J21" s="61" t="n">
         <f aca="false">((J9+J13)+J19)</f>
-        <v>-936.31999999999</v>
+        <v>-936.320000000005</v>
       </c>
       <c r="K21" s="61" t="n">
         <f aca="false">((K9+K13)+K19)</f>
@@ -11808,23 +11808,23 @@
       </c>
       <c r="L21" s="62" t="n">
         <f aca="false">((L9+L13)+L19)</f>
-        <v>2066.9683685162</v>
+        <v>2066.95098416334</v>
       </c>
       <c r="M21" s="62" t="n">
         <f aca="false">((M9+M13)+M19)</f>
-        <v>7621.07420307529</v>
+        <v>7621.06287554121</v>
       </c>
       <c r="N21" s="62" t="n">
         <f aca="false">((N9+N13)+N19)</f>
-        <v>8555.92621334119</v>
+        <v>8555.91286089683</v>
       </c>
       <c r="O21" s="62" t="n">
         <f aca="false">((O9+O13)+O19)</f>
-        <v>9924.05780653557</v>
+        <v>9924.04237113236</v>
       </c>
       <c r="P21" s="62" t="n">
         <f aca="false">((P9+P13)+P19)</f>
-        <v>12969.0721075076</v>
+        <v>12969.0549958433</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11877,19 +11877,19 @@
       </c>
       <c r="M22" s="33" t="n">
         <f aca="false">'Balance Sheet'!L6</f>
-        <v>10550.4783685162</v>
+        <v>10550.4609841633</v>
       </c>
       <c r="N22" s="33" t="n">
         <f aca="false">'Balance Sheet'!M6</f>
-        <v>18171.5525715915</v>
+        <v>18171.5238597045</v>
       </c>
       <c r="O22" s="33" t="n">
         <f aca="false">'Balance Sheet'!N6</f>
-        <v>26727.4787849327</v>
+        <v>26727.4367206014</v>
       </c>
       <c r="P22" s="33" t="n">
         <f aca="false">'Balance Sheet'!O6</f>
-        <v>36651.5365914683</v>
+        <v>36651.4790917337</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="C23" s="59" t="n">
         <f aca="false">(C22+C21)</f>
-        <v>2850.01</v>
+        <v>2850.01000000001</v>
       </c>
       <c r="D23" s="59" t="n">
         <f aca="false">(D22+D21)</f>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="J23" s="59" t="n">
         <f aca="false">(J22+J21)</f>
-        <v>6695.56000000001</v>
+        <v>6695.56</v>
       </c>
       <c r="K23" s="59" t="n">
         <f aca="false">(K22+K21)</f>
@@ -11938,23 +11938,23 @@
       </c>
       <c r="L23" s="60" t="n">
         <f aca="false">(L22+L21)</f>
-        <v>10550.4783685162</v>
+        <v>10550.4609841633</v>
       </c>
       <c r="M23" s="60" t="n">
         <f aca="false">(M22+M21)</f>
-        <v>18171.5525715915</v>
+        <v>18171.5238597045</v>
       </c>
       <c r="N23" s="60" t="n">
         <f aca="false">(N22+N21)</f>
-        <v>26727.4787849327</v>
+        <v>26727.4367206014</v>
       </c>
       <c r="O23" s="60" t="n">
         <f aca="false">(O22+O21)</f>
-        <v>36651.5365914683</v>
+        <v>36651.4790917337</v>
       </c>
       <c r="P23" s="60" t="n">
         <f aca="false">(P22+P21)</f>
-        <v>49620.6086989759</v>
+        <v>49620.534087577</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12188,23 +12188,23 @@
       </c>
       <c r="L28" s="64" t="n">
         <f aca="false">(L9-L25)</f>
-        <v>19244.3939067476</v>
+        <v>19244.378899053</v>
       </c>
       <c r="M28" s="64" t="n">
         <f aca="false">(M9-M25)</f>
-        <v>23618.5122156429</v>
+        <v>23618.5143746382</v>
       </c>
       <c r="N28" s="64" t="n">
         <f aca="false">(N9-N25)</f>
-        <v>26965.3844400563</v>
+        <v>26965.386817017</v>
       </c>
       <c r="O28" s="64" t="n">
         <f aca="false">(O9-O25)</f>
-        <v>30923.1096120272</v>
+        <v>30923.1124492146</v>
       </c>
       <c r="P28" s="64" t="n">
         <f aca="false">(P9-P25)</f>
-        <v>34652.3382657155</v>
+        <v>34652.3425634465</v>
       </c>
     </row>
   </sheetData>
@@ -12361,19 +12361,19 @@
       </c>
       <c r="M6" s="33" t="n">
         <f aca="false">'Balance Sheet'!L10</f>
-        <v>138607.49234293</v>
+        <v>138607.462839577</v>
       </c>
       <c r="N6" s="33" t="n">
         <f aca="false">'Balance Sheet'!M10</f>
-        <v>146526.286735102</v>
+        <v>146526.227877796</v>
       </c>
       <c r="O6" s="33" t="n">
         <f aca="false">'Balance Sheet'!N10</f>
-        <v>155685.272967819</v>
+        <v>155685.184681322</v>
       </c>
       <c r="P6" s="33" t="n">
         <f aca="false">'Balance Sheet'!O10</f>
-        <v>166228.332603398</v>
+        <v>166228.2145389</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12477,23 +12477,23 @@
       </c>
       <c r="L8" s="33" t="n">
         <f aca="false">'Income Statement'!L11</f>
-        <v>7621.62653</v>
+        <v>7621.65603335271</v>
       </c>
       <c r="M8" s="33" t="n">
         <f aca="false">'Income Statement'!M11</f>
-        <v>8024.2649467169</v>
+        <v>8024.29430067014</v>
       </c>
       <c r="N8" s="33" t="n">
         <f aca="false">'Income Statement'!N11</f>
-        <v>8482.69979166854</v>
+        <v>8482.72922085962</v>
       </c>
       <c r="O8" s="33" t="n">
         <f aca="false">'Income Statement'!O11</f>
-        <v>9012.93182265299</v>
+        <v>9012.96160065347</v>
       </c>
       <c r="P8" s="33" t="n">
         <f aca="false">'Income Statement'!P11</f>
-        <v>9623.29063107591</v>
+        <v>9623.32104786357</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12542,23 +12542,23 @@
       </c>
       <c r="L9" s="60" t="n">
         <f aca="false">((L6+L7)-L8)</f>
-        <v>138607.49234293</v>
+        <v>138607.462839577</v>
       </c>
       <c r="M9" s="60" t="n">
         <f aca="false">((M6+M7)-M8)</f>
-        <v>146526.286735102</v>
+        <v>146526.227877796</v>
       </c>
       <c r="N9" s="60" t="n">
         <f aca="false">((N6+N7)-N8)</f>
-        <v>155685.272967819</v>
+        <v>155685.184681322</v>
       </c>
       <c r="O9" s="60" t="n">
         <f aca="false">((O6+O7)-O8)</f>
-        <v>166228.332603398</v>
+        <v>166228.2145389</v>
       </c>
       <c r="P9" s="60" t="n">
         <f aca="false">((P6+P7)-P8)</f>
-        <v>176959.616310316</v>
+        <v>176959.467829031</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12627,23 +12627,23 @@
       </c>
       <c r="L11" s="30" t="n">
         <f aca="false">(((('Balance Sheet'!L7+'Balance Sheet'!L8)+'Balance Sheet'!L9)-'Balance Sheet'!L20)-'Balance Sheet'!L21)</f>
-        <v>3336.41221304274</v>
+        <v>3336.4311002293</v>
       </c>
       <c r="M11" s="30" t="n">
         <f aca="false">(((('Balance Sheet'!M7+'Balance Sheet'!M8)+'Balance Sheet'!M9)-'Balance Sheet'!M20)-'Balance Sheet'!M21)</f>
-        <v>3770.81308318091</v>
+        <v>3770.83442947915</v>
       </c>
       <c r="N11" s="30" t="n">
         <f aca="false">(((('Balance Sheet'!N7+'Balance Sheet'!N8)+'Balance Sheet'!N9)-'Balance Sheet'!N20)-'Balance Sheet'!N21)</f>
-        <v>4316.44973631718</v>
+        <v>4316.47417142478</v>
       </c>
       <c r="O11" s="30" t="n">
         <f aca="false">(((('Balance Sheet'!O7+'Balance Sheet'!O8)+'Balance Sheet'!O9)-'Balance Sheet'!O20)-'Balance Sheet'!O21)</f>
-        <v>4955.71594226575</v>
+        <v>4955.7439962128</v>
       </c>
       <c r="P11" s="30" t="n">
         <f aca="false">(((('Balance Sheet'!P7+'Balance Sheet'!P8)+'Balance Sheet'!P9)-'Balance Sheet'!P20)-'Balance Sheet'!P21)</f>
-        <v>5554.86199968569</v>
+        <v>5554.89344535492</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12692,23 +12692,23 @@
       </c>
       <c r="L12" s="56" t="n">
         <f aca="false">(L11-K11)</f>
-        <v>2085.83221304273</v>
+        <v>2085.8511002293</v>
       </c>
       <c r="M12" s="56" t="n">
         <f aca="false">(M11-L11)</f>
-        <v>434.400870138172</v>
+        <v>434.403329249853</v>
       </c>
       <c r="N12" s="56" t="n">
         <f aca="false">(N11-M11)</f>
-        <v>545.636653136276</v>
+        <v>545.639741945626</v>
       </c>
       <c r="O12" s="56" t="n">
         <f aca="false">(O11-N11)</f>
-        <v>639.266205948567</v>
+        <v>639.269824788018</v>
       </c>
       <c r="P12" s="56" t="n">
         <f aca="false">(P11-O11)</f>
-        <v>599.146057419937</v>
+        <v>599.149449142125</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12757,23 +12757,23 @@
       </c>
       <c r="L13" s="65" t="n">
         <f aca="false">(IFERROR((L11)/('Income Statement'!L6),0)*365)</f>
-        <v>25.89867</v>
+        <v>25.8988166104848</v>
       </c>
       <c r="M13" s="65" t="n">
         <f aca="false">(IFERROR((M11)/('Income Statement'!M6),0)*365)</f>
-        <v>25.89867</v>
+        <v>25.8988166104848</v>
       </c>
       <c r="N13" s="65" t="n">
         <f aca="false">(IFERROR((N11)/('Income Statement'!N6),0)*365)</f>
-        <v>25.89867</v>
+        <v>25.8988166104847</v>
       </c>
       <c r="O13" s="65" t="n">
         <f aca="false">(IFERROR((O11)/('Income Statement'!O6),0)*365)</f>
-        <v>25.89867</v>
+        <v>25.8988166104848</v>
       </c>
       <c r="P13" s="65" t="n">
         <f aca="false">(IFERROR((P11)/('Income Statement'!P6),0)*365)</f>
-        <v>25.89867</v>
+        <v>25.8988166104848</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12846,19 +12846,19 @@
       </c>
       <c r="M15" s="33" t="n">
         <f aca="false">'Balance Sheet'!L17</f>
-        <v>67817.67189488</v>
+        <v>67817.6570167938</v>
       </c>
       <c r="N15" s="33" t="n">
         <f aca="false">'Balance Sheet'!M17</f>
-        <v>72354.2672386161</v>
+        <v>72354.2354919378</v>
       </c>
       <c r="O15" s="33" t="n">
         <f aca="false">'Balance Sheet'!N17</f>
-        <v>77194.3335912761</v>
+        <v>77194.2827857707</v>
       </c>
       <c r="P15" s="33" t="n">
         <f aca="false">'Balance Sheet'!O17</f>
-        <v>82358.1713425309</v>
+        <v>82358.0990704204</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12907,23 +12907,23 @@
       </c>
       <c r="L16" s="33" t="n">
         <f aca="false">(('Cash Flow'!L15+'Cash Flow'!L17)+'Cash Flow'!L18)</f>
-        <v>2282.44547142057</v>
+        <v>2282.43300427975</v>
       </c>
       <c r="M16" s="33" t="n">
         <f aca="false">(('Cash Flow'!M15+'Cash Flow'!M17)+'Cash Flow'!M18)</f>
-        <v>2233.53506452281</v>
+        <v>2233.52026421255</v>
       </c>
       <c r="N16" s="33" t="n">
         <f aca="false">(('Cash Flow'!N15+'Cash Flow'!N17)+'Cash Flow'!N18)</f>
-        <v>2106.0010347718</v>
+        <v>2105.98365516982</v>
       </c>
       <c r="O16" s="33" t="n">
         <f aca="false">(('Cash Flow'!O15+'Cash Flow'!O17)+'Cash Flow'!O18)</f>
-        <v>1923.84344023086</v>
+        <v>1923.82323427468</v>
       </c>
       <c r="P16" s="33" t="n">
         <f aca="false">(('Cash Flow'!P15+'Cash Flow'!P17)+'Cash Flow'!P18)</f>
-        <v>1826.90613133737</v>
+        <v>1826.88290991388</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="C17" s="9" t="n">
         <f aca="false">((('Balance Sheet'!B6+'Cash Flow'!C9)+'Cash Flow'!C13)+C16)</f>
-        <v>2850.01</v>
+        <v>2850.01000000001</v>
       </c>
       <c r="D17" s="9" t="n">
         <f aca="false">((('Balance Sheet'!C6+'Cash Flow'!D9)+'Cash Flow'!D13)+D16)</f>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="J17" s="9" t="n">
         <f aca="false">((('Balance Sheet'!I6+'Cash Flow'!J9)+'Cash Flow'!J13)+J16)</f>
-        <v>6695.56000000001</v>
+        <v>6695.56</v>
       </c>
       <c r="K17" s="9" t="n">
         <f aca="false">((('Balance Sheet'!J6+'Cash Flow'!K9)+'Cash Flow'!K13)+K16)</f>
@@ -12972,23 +12972,23 @@
       </c>
       <c r="L17" s="33" t="n">
         <f aca="false">((('Balance Sheet'!K6+'Cash Flow'!L9)+'Cash Flow'!L13)+L16)</f>
-        <v>10550.4783685162</v>
+        <v>10550.4609841633</v>
       </c>
       <c r="M17" s="33" t="n">
         <f aca="false">((('Balance Sheet'!L6+'Cash Flow'!M9)+'Cash Flow'!M13)+M16)</f>
-        <v>18171.5525715915</v>
+        <v>18171.5238597046</v>
       </c>
       <c r="N17" s="33" t="n">
         <f aca="false">((('Balance Sheet'!M6+'Cash Flow'!N9)+'Cash Flow'!N13)+N16)</f>
-        <v>26727.4787849327</v>
+        <v>26727.4367206014</v>
       </c>
       <c r="O17" s="33" t="n">
         <f aca="false">((('Balance Sheet'!N6+'Cash Flow'!O9)+'Cash Flow'!O13)+O16)</f>
-        <v>36651.5365914683</v>
+        <v>36651.4790917337</v>
       </c>
       <c r="P17" s="33" t="n">
         <f aca="false">((('Balance Sheet'!O6+'Cash Flow'!P9)+'Cash Flow'!P13)+P16)</f>
-        <v>49620.6086989759</v>
+        <v>49620.534087577</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13167,23 +13167,23 @@
       </c>
       <c r="L20" s="33" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!K19,'Balance Sheet'!L19)</f>
-        <v>65691.59594744</v>
+        <v>65691.5885083969</v>
       </c>
       <c r="M20" s="33" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!L19,'Balance Sheet'!M19)</f>
-        <v>70085.969566748</v>
+        <v>70085.9462543658</v>
       </c>
       <c r="N20" s="33" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!M19,'Balance Sheet'!N19)</f>
-        <v>74774.3004149461</v>
+        <v>74774.2591388543</v>
       </c>
       <c r="O20" s="33" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!N19,'Balance Sheet'!O19)</f>
-        <v>79776.2524669035</v>
+        <v>79776.1909280955</v>
       </c>
       <c r="P20" s="33" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!O19,'Balance Sheet'!P19)</f>
-        <v>85112.8050994245</v>
+        <v>85112.7207716989</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13242,23 +13242,23 @@
       </c>
       <c r="L22" s="33" t="n">
         <f aca="false">('Income Statement'!L18*Drivers!L28)</f>
-        <v>1969.70642345943</v>
+        <v>1969.70401251405</v>
       </c>
       <c r="M22" s="33" t="n">
         <f aca="false">('Income Statement'!M18*Drivers!M28)</f>
-        <v>2303.06027921329</v>
+        <v>2303.05821093143</v>
       </c>
       <c r="N22" s="33" t="n">
         <f aca="false">('Income Statement'!N18*Drivers!N28)</f>
-        <v>2734.06531788818</v>
+        <v>2734.06363866313</v>
       </c>
       <c r="O22" s="33" t="n">
         <f aca="false">('Income Statement'!O18*Drivers!O28)</f>
-        <v>3239.99431102396</v>
+        <v>3239.99305037497</v>
       </c>
       <c r="P22" s="33" t="n">
         <f aca="false">('Income Statement'!P18*Drivers!P28)</f>
-        <v>3682.36138244989</v>
+        <v>3682.36049264312</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13362,23 +13362,23 @@
       </c>
       <c r="L24" s="30" t="n">
         <f aca="false">('Balance Sheet'!L15+'Balance Sheet'!L16)</f>
-        <v>107697.663166331</v>
+        <v>107697.639953415</v>
       </c>
       <c r="M24" s="30" t="n">
         <f aca="false">('Balance Sheet'!M15+'Balance Sheet'!M16)</f>
-        <v>121423.251026182</v>
+        <v>121423.205145702</v>
       </c>
       <c r="N24" s="30" t="n">
         <f aca="false">('Balance Sheet'!N15+'Balance Sheet'!N16)</f>
-        <v>137717.507009818</v>
+        <v>137717.438845142</v>
       </c>
       <c r="O24" s="30" t="n">
         <f aca="false">('Balance Sheet'!O15+'Balance Sheet'!O16)</f>
-        <v>157026.956694116</v>
+        <v>157026.866468116</v>
       </c>
       <c r="P24" s="30" t="n">
         <f aca="false">('Balance Sheet'!P15+'Balance Sheet'!P16)</f>
-        <v>178972.789003726</v>
+        <v>178972.676940198</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13427,23 +13427,23 @@
       </c>
       <c r="L25" s="67" t="n">
         <f aca="false">IFERROR((L24)/(L23),0)</f>
-        <v>467.44609242756</v>
+        <v>467.445991675266</v>
       </c>
       <c r="M25" s="67" t="n">
         <f aca="false">IFERROR((M24)/(M23),0)</f>
-        <v>527.020016528861</v>
+        <v>527.01981739129</v>
       </c>
       <c r="N25" s="67" t="n">
         <f aca="false">IFERROR((N24)/(N23),0)</f>
-        <v>597.742872203097</v>
+        <v>597.742576344205</v>
       </c>
       <c r="O25" s="67" t="n">
         <f aca="false">IFERROR((O24)/(O23),0)</f>
-        <v>681.552738977197</v>
+        <v>681.552347364324</v>
       </c>
       <c r="P25" s="67" t="n">
         <f aca="false">IFERROR((P24)/(P23),0)</f>
-        <v>776.805442300519</v>
+        <v>776.804955905023</v>
       </c>
     </row>
   </sheetData>
